--- a/product_monthly.xlsx
+++ b/product_monthly.xlsx
@@ -564,16 +564,16 @@
         <v>30</v>
       </c>
       <c r="C2">
-        <v>528</v>
+        <v>615</v>
       </c>
       <c r="D2">
-        <v>531</v>
+        <v>619</v>
       </c>
       <c r="E2">
-        <v>531</v>
+        <v>619</v>
       </c>
       <c r="F2">
-        <v>3207.24</v>
+        <v>3738.76</v>
       </c>
       <c r="G2">
         <v>58</v>
@@ -591,10 +591,10 @@
         <v>0.98</v>
       </c>
       <c r="L2">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="M2">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="N2">
         <v>0.02</v>
@@ -1576,16 +1576,16 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>666</v>
+        <v>725</v>
       </c>
       <c r="D25">
-        <v>743</v>
+        <v>804</v>
       </c>
       <c r="E25">
-        <v>748</v>
+        <v>809</v>
       </c>
       <c r="F25">
-        <v>4811</v>
+        <v>5158.09</v>
       </c>
       <c r="G25">
         <v>1242</v>
@@ -1603,13 +1603,13 @@
         <v>9.52</v>
       </c>
       <c r="L25">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="M25">
-        <v>15.92</v>
+        <v>14.71</v>
       </c>
       <c r="N25">
-        <v>2.46</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -2273,16 +2273,16 @@
         <v>30</v>
       </c>
       <c r="C42">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="D42">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="E42">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="F42">
-        <v>2329.32</v>
+        <v>2425.2</v>
       </c>
       <c r="G42">
         <v>632</v>
@@ -2300,13 +2300,13 @@
         <v>10.14</v>
       </c>
       <c r="L42">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="M42">
-        <v>15.52</v>
+        <v>14.9</v>
       </c>
       <c r="N42">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -2449,16 +2449,16 @@
         <v>30</v>
       </c>
       <c r="C46">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="D46">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="E46">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="F46">
-        <v>2735.85</v>
+        <v>2825.55</v>
       </c>
       <c r="G46">
         <v>220</v>
@@ -2476,10 +2476,10 @@
         <v>2.12</v>
       </c>
       <c r="L46">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="M46">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="N46">
         <v>0.17</v>
@@ -2493,13 +2493,13 @@
         <v>30</v>
       </c>
       <c r="C47">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D47">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E47">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -2666,16 +2666,16 @@
         <v>30</v>
       </c>
       <c r="C51">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D51">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E51">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F51">
-        <v>141.9</v>
+        <v>146.63</v>
       </c>
       <c r="G51">
         <v>75</v>
@@ -2693,13 +2693,13 @@
         <v>11.13</v>
       </c>
       <c r="L51">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="M51">
-        <v>27.82</v>
+        <v>26.93</v>
       </c>
       <c r="N51">
-        <v>5.88</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -2836,16 +2836,16 @@
         <v>30</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F55">
-        <v>49.63</v>
+        <v>56.72</v>
       </c>
       <c r="G55">
         <v>7</v>
@@ -2863,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -3035,13 +3035,13 @@
         <v>30</v>
       </c>
       <c r="C60">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D60">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E60">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3062,10 +3062,10 @@
         <v>2.43</v>
       </c>
       <c r="L60">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3120,16 +3120,16 @@
         <v>30</v>
       </c>
       <c r="C62">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D62">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="E62">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="F62">
-        <v>2850.01</v>
+        <v>2974.39</v>
       </c>
       <c r="G62">
         <v>302</v>
@@ -3147,10 +3147,10 @@
         <v>1.64</v>
       </c>
       <c r="L62">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="M62">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N62">
         <v>0.17</v>
@@ -3296,16 +3296,16 @@
         <v>30</v>
       </c>
       <c r="C66">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D66">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E66">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F66">
-        <v>131.22</v>
+        <v>140.94</v>
       </c>
       <c r="G66">
         <v>112</v>
@@ -3323,13 +3323,13 @@
         <v>12.64</v>
       </c>
       <c r="L66">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="M66">
-        <v>52.45</v>
+        <v>48.83</v>
       </c>
       <c r="N66">
-        <v>10.79</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3777,16 +3777,16 @@
         <v>30</v>
       </c>
       <c r="C77">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="D77">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="E77">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="F77">
-        <v>1625.97</v>
+        <v>1691.27</v>
       </c>
       <c r="G77">
         <v>289</v>
@@ -3804,13 +3804,13 @@
         <v>5.83</v>
       </c>
       <c r="L77">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="M77">
-        <v>6.77</v>
+        <v>6.51</v>
       </c>
       <c r="N77">
-        <v>1.04</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/product_monthly.xlsx
+++ b/product_monthly.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="57">
   <si>
     <t>product</t>
   </si>
@@ -113,9 +113,6 @@
   </si>
   <si>
     <t>Hibiscus</t>
-  </si>
-  <si>
-    <t>Lemon Ginger</t>
   </si>
   <si>
     <t>Matcha</t>
@@ -545,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y75"/>
+  <dimension ref="A1:Y69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -630,10 +627,10 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s">
         <v>41</v>
-      </c>
-      <c r="C2" t="s">
-        <v>42</v>
       </c>
       <c r="D2">
         <v>615</v>
@@ -707,10 +704,10 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -784,10 +781,10 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4">
         <v>45</v>
@@ -861,10 +858,10 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <v>20</v>
@@ -938,10 +935,10 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -1015,10 +1012,10 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1092,10 +1089,10 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1169,10 +1166,10 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1237,10 +1234,10 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -1288,7 +1285,7 @@
         <v>388</v>
       </c>
       <c r="S10">
-        <v>15216.21</v>
+        <v>15216.18</v>
       </c>
       <c r="T10">
         <v>58</v>
@@ -1314,10 +1311,10 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D11">
         <v>41</v>
@@ -1391,10 +1388,10 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12">
         <v>432</v>
@@ -1442,7 +1439,7 @@
         <v>1319</v>
       </c>
       <c r="S12">
-        <v>198536.02</v>
+        <v>198426.89</v>
       </c>
       <c r="T12">
         <v>294</v>
@@ -1451,16 +1448,16 @@
         <v>68.09999999999999</v>
       </c>
       <c r="V12">
-        <v>150.52</v>
+        <v>150.44</v>
       </c>
       <c r="W12">
-        <v>450.2</v>
+        <v>449.95</v>
       </c>
       <c r="X12">
         <v>2.99</v>
       </c>
       <c r="Y12">
-        <v>78.39</v>
+        <v>78.34999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1468,10 +1465,10 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13">
         <v>568</v>
@@ -1545,10 +1542,10 @@
         <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14">
         <v>629</v>
@@ -1593,10 +1590,10 @@
         <v>19.52</v>
       </c>
       <c r="R14">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="S14">
-        <v>56897.89</v>
+        <v>56897.63</v>
       </c>
       <c r="T14">
         <v>344</v>
@@ -1605,13 +1602,13 @@
         <v>54.7</v>
       </c>
       <c r="V14">
-        <v>42.4</v>
+        <v>42.49</v>
       </c>
       <c r="W14">
         <v>88.90000000000001</v>
       </c>
       <c r="X14">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Y14">
         <v>15.53</v>
@@ -1622,76 +1619,76 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E15">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F15">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G15">
-        <v>2495.93</v>
+        <v>2484.55</v>
       </c>
       <c r="H15">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I15">
         <v>2151.56</v>
       </c>
       <c r="J15">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K15">
         <v>53.4</v>
       </c>
       <c r="L15">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="M15">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N15">
         <v>2294.51</v>
       </c>
       <c r="O15">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P15">
         <v>58.7</v>
       </c>
       <c r="Q15">
-        <v>4.68</v>
+        <v>4.71</v>
       </c>
       <c r="R15">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="S15">
-        <v>16978.53</v>
+        <v>16978.37</v>
       </c>
       <c r="T15">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U15">
         <v>59.9</v>
       </c>
       <c r="V15">
-        <v>23.68</v>
+        <v>23.81</v>
       </c>
       <c r="W15">
-        <v>39.03</v>
+        <v>39.21</v>
       </c>
       <c r="X15">
         <v>1.65</v>
       </c>
       <c r="Y15">
-        <v>6.8</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1699,10 +1696,10 @@
         <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16">
         <v>733</v>
@@ -1747,7 +1744,7 @@
         <v>31.43</v>
       </c>
       <c r="R16">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="S16">
         <v>24536.34</v>
@@ -1759,13 +1756,13 @@
         <v>55</v>
       </c>
       <c r="V16">
-        <v>26.1</v>
+        <v>26.19</v>
       </c>
       <c r="W16">
         <v>33.02</v>
       </c>
       <c r="X16">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Y16">
         <v>5.79</v>
@@ -1776,10 +1773,10 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17">
         <v>679</v>
@@ -1797,7 +1794,7 @@
         <v>690</v>
       </c>
       <c r="I17">
-        <v>6534.71</v>
+        <v>6534.6</v>
       </c>
       <c r="J17">
         <v>381</v>
@@ -1812,7 +1809,7 @@
         <v>936</v>
       </c>
       <c r="N17">
-        <v>16044.91</v>
+        <v>16044.75</v>
       </c>
       <c r="O17">
         <v>467</v>
@@ -1824,10 +1821,10 @@
         <v>17.14</v>
       </c>
       <c r="R17">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="S17">
-        <v>29055.13</v>
+        <v>29079.51</v>
       </c>
       <c r="T17">
         <v>475</v>
@@ -1836,13 +1833,13 @@
         <v>70</v>
       </c>
       <c r="V17">
-        <v>22.82</v>
+        <v>22.74</v>
       </c>
       <c r="W17">
-        <v>42.48</v>
+        <v>42.51</v>
       </c>
       <c r="X17">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Y17">
         <v>7.43</v>
@@ -1853,76 +1850,76 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D18">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="E18">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="F18">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="G18">
-        <v>8334.860000000001</v>
+        <v>8323.48</v>
       </c>
       <c r="H18">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="I18">
         <v>73400.73</v>
       </c>
       <c r="J18">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="K18">
         <v>64.59999999999999</v>
       </c>
       <c r="L18">
-        <v>41.42</v>
+        <v>41.49</v>
       </c>
       <c r="M18">
-        <v>2739</v>
+        <v>2730</v>
       </c>
       <c r="N18">
         <v>79348.72</v>
       </c>
       <c r="O18">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="P18">
         <v>82.5</v>
       </c>
       <c r="Q18">
-        <v>28.97</v>
+        <v>29.07</v>
       </c>
       <c r="R18">
-        <v>4070</v>
+        <v>4035</v>
       </c>
       <c r="S18">
-        <v>98325.92999999999</v>
+        <v>98300.42999999999</v>
       </c>
       <c r="T18">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="U18">
         <v>83.2</v>
       </c>
       <c r="V18">
-        <v>24.16</v>
+        <v>24.36</v>
       </c>
       <c r="W18">
-        <v>67.20999999999999</v>
+        <v>67.28</v>
       </c>
       <c r="X18">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Y18">
-        <v>11.8</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1930,22 +1927,22 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D19">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="E19">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="F19">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="G19">
-        <v>5596.89</v>
+        <v>5585.51</v>
       </c>
       <c r="H19">
         <v>1924</v>
@@ -1957,7 +1954,7 @@
         <v>757</v>
       </c>
       <c r="K19">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="L19">
         <v>43.27</v>
@@ -1972,34 +1969,34 @@
         <v>833</v>
       </c>
       <c r="P19">
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="Q19">
         <v>37.91</v>
       </c>
       <c r="R19">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="S19">
-        <v>98166.72</v>
+        <v>98166.2</v>
       </c>
       <c r="T19">
         <v>836</v>
       </c>
       <c r="U19">
-        <v>87.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="V19">
-        <v>31.71</v>
+        <v>31.7</v>
       </c>
       <c r="W19">
-        <v>99.86</v>
+        <v>100.07</v>
       </c>
       <c r="X19">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="Y19">
-        <v>17.54</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2007,22 +2004,22 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D20">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E20">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F20">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G20">
-        <v>3897.65</v>
+        <v>3891.96</v>
       </c>
       <c r="H20">
         <v>965</v>
@@ -2034,7 +2031,7 @@
         <v>464</v>
       </c>
       <c r="K20">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="L20">
         <v>15.39</v>
@@ -2043,40 +2040,40 @@
         <v>1484</v>
       </c>
       <c r="N20">
-        <v>19351.97</v>
+        <v>19351.9</v>
       </c>
       <c r="O20">
         <v>590</v>
       </c>
       <c r="P20">
-        <v>89.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="Q20">
         <v>13.04</v>
       </c>
       <c r="R20">
-        <v>1998</v>
+        <v>1989</v>
       </c>
       <c r="S20">
-        <v>32263.31</v>
+        <v>32246.22</v>
       </c>
       <c r="T20">
         <v>599</v>
       </c>
       <c r="U20">
-        <v>90.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V20">
-        <v>16.15</v>
+        <v>16.21</v>
       </c>
       <c r="W20">
-        <v>47.1</v>
+        <v>47.14</v>
       </c>
       <c r="X20">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="Y20">
-        <v>8.279999999999999</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2084,34 +2081,34 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D21">
-        <v>3226</v>
+        <v>3197</v>
       </c>
       <c r="E21">
-        <v>3316</v>
+        <v>3278</v>
       </c>
       <c r="F21">
-        <v>3316</v>
+        <v>3278</v>
       </c>
       <c r="G21">
-        <v>18868.04</v>
+        <v>18651.82</v>
       </c>
       <c r="H21">
         <v>2840</v>
       </c>
       <c r="I21">
-        <v>28289.65</v>
+        <v>28289.48</v>
       </c>
       <c r="J21">
         <v>1508</v>
       </c>
       <c r="K21">
-        <v>46.7</v>
+        <v>47.2</v>
       </c>
       <c r="L21">
         <v>9.960000000000001</v>
@@ -2120,40 +2117,40 @@
         <v>4959</v>
       </c>
       <c r="N21">
-        <v>35178.4</v>
+        <v>35178.16</v>
       </c>
       <c r="O21">
         <v>2292</v>
       </c>
       <c r="P21">
-        <v>71</v>
+        <v>71.7</v>
       </c>
       <c r="Q21">
         <v>7.09</v>
       </c>
       <c r="R21">
-        <v>5479</v>
+        <v>5429</v>
       </c>
       <c r="S21">
-        <v>37631.17</v>
+        <v>37630.23</v>
       </c>
       <c r="T21">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="U21">
-        <v>71.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="V21">
-        <v>6.87</v>
+        <v>6.93</v>
       </c>
       <c r="W21">
-        <v>11.35</v>
+        <v>11.48</v>
       </c>
       <c r="X21">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Y21">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2161,76 +2158,76 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22">
-        <v>2094</v>
+        <v>2077</v>
       </c>
       <c r="E22">
-        <v>2212</v>
+        <v>2193</v>
       </c>
       <c r="F22">
-        <v>2214</v>
+        <v>2195</v>
       </c>
       <c r="G22">
-        <v>12704.59</v>
+        <v>12596.48</v>
       </c>
       <c r="H22">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="I22">
-        <v>6079.1</v>
+        <v>5945.55</v>
       </c>
       <c r="J22">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="K22">
-        <v>42.8</v>
+        <v>43.1</v>
       </c>
       <c r="L22">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="M22">
-        <v>1604</v>
+        <v>1581</v>
       </c>
       <c r="N22">
-        <v>7397.35</v>
+        <v>7263.59</v>
       </c>
       <c r="O22">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="P22">
-        <v>43.9</v>
+        <v>44.2</v>
       </c>
       <c r="Q22">
-        <v>4.61</v>
+        <v>4.59</v>
       </c>
       <c r="R22">
-        <v>2454</v>
+        <v>2327</v>
       </c>
       <c r="S22">
-        <v>25658.71</v>
+        <v>23668.07</v>
       </c>
       <c r="T22">
-        <v>1021</v>
+        <v>1006</v>
       </c>
       <c r="U22">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="V22">
-        <v>10.46</v>
+        <v>10.17</v>
       </c>
       <c r="W22">
-        <v>11.6</v>
+        <v>10.79</v>
       </c>
       <c r="X22">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2238,76 +2235,76 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23">
-        <v>959</v>
+        <v>904</v>
       </c>
       <c r="E23">
-        <v>1037</v>
+        <v>982</v>
       </c>
       <c r="F23">
-        <v>1044</v>
+        <v>989</v>
       </c>
       <c r="G23">
-        <v>8122.31</v>
+        <v>7754.45</v>
       </c>
       <c r="H23">
-        <v>955</v>
+        <v>839</v>
       </c>
       <c r="I23">
-        <v>32921.93</v>
+        <v>32899.95</v>
       </c>
       <c r="J23">
-        <v>484</v>
+        <v>436</v>
       </c>
       <c r="K23">
-        <v>50.5</v>
+        <v>48.2</v>
       </c>
       <c r="L23">
-        <v>34.47</v>
+        <v>39.21</v>
       </c>
       <c r="M23">
-        <v>1467</v>
+        <v>1272</v>
       </c>
       <c r="N23">
-        <v>41990.1</v>
+        <v>41844.01</v>
       </c>
       <c r="O23">
-        <v>589</v>
+        <v>536</v>
       </c>
       <c r="P23">
-        <v>61.4</v>
+        <v>59.3</v>
       </c>
       <c r="Q23">
-        <v>28.62</v>
+        <v>32.9</v>
       </c>
       <c r="R23">
-        <v>2171</v>
+        <v>1966</v>
       </c>
       <c r="S23">
-        <v>69718.83</v>
+        <v>69664.8</v>
       </c>
       <c r="T23">
-        <v>630</v>
+        <v>581</v>
       </c>
       <c r="U23">
-        <v>65.7</v>
+        <v>64.3</v>
       </c>
       <c r="V23">
-        <v>32.11</v>
+        <v>35.43</v>
       </c>
       <c r="W23">
-        <v>67.23</v>
+        <v>70.94</v>
       </c>
       <c r="X23">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Y23">
-        <v>8.58</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2315,76 +2312,76 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D24">
-        <v>377</v>
+        <v>332</v>
       </c>
       <c r="E24">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="F24">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="G24">
-        <v>2413.73</v>
+        <v>2114.42</v>
       </c>
       <c r="H24">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="I24">
-        <v>4202.07</v>
+        <v>4197.09</v>
       </c>
       <c r="J24">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="K24">
-        <v>56.5</v>
+        <v>61.4</v>
       </c>
       <c r="L24">
-        <v>8.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M24">
-        <v>691</v>
+        <v>663</v>
       </c>
       <c r="N24">
-        <v>4923.54</v>
+        <v>4951.87</v>
       </c>
       <c r="O24">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="P24">
-        <v>70</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="Q24">
-        <v>7.13</v>
+        <v>7.47</v>
       </c>
       <c r="R24">
-        <v>715</v>
+        <v>687</v>
       </c>
       <c r="S24">
-        <v>5049.35</v>
+        <v>5077.68</v>
       </c>
       <c r="T24">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="U24">
-        <v>70</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="V24">
-        <v>7.06</v>
+        <v>7.39</v>
       </c>
       <c r="W24">
-        <v>12.29</v>
+        <v>13.91</v>
       </c>
       <c r="X24">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="Y24">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2392,76 +2389,76 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" t="s">
         <v>41</v>
       </c>
-      <c r="C25" t="s">
-        <v>42</v>
-      </c>
       <c r="D25">
-        <v>725</v>
+        <v>653</v>
       </c>
       <c r="E25">
-        <v>804</v>
+        <v>730</v>
       </c>
       <c r="F25">
-        <v>809</v>
+        <v>735</v>
       </c>
       <c r="G25">
-        <v>5158.09</v>
+        <v>4737.03</v>
       </c>
       <c r="H25">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="I25">
-        <v>1884.61</v>
+        <v>1884.35</v>
       </c>
       <c r="J25">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K25">
-        <v>26.6</v>
+        <v>29.2</v>
       </c>
       <c r="L25">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="M25">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="N25">
-        <v>1884.61</v>
+        <v>1884.35</v>
       </c>
       <c r="O25">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="P25">
-        <v>26.6</v>
+        <v>29.2</v>
       </c>
       <c r="Q25">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="R25">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="S25">
-        <v>1884.61</v>
+        <v>1884.35</v>
       </c>
       <c r="T25">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="U25">
-        <v>26.6</v>
+        <v>29.2</v>
       </c>
       <c r="V25">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="W25">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="X25">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="Y25">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2469,19 +2466,19 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D26">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F26">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -2499,57 +2496,63 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>26.97</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>47.1</v>
+      </c>
+      <c r="Q26">
+        <v>2.7</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>26.97</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>52.9</v>
+      </c>
+      <c r="V26">
+        <v>2.25</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="27" spans="1:25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D27">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2591,208 +2594,241 @@
         <v>0</v>
       </c>
       <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D28">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>657.88</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1483.66</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>38.6</v>
+      </c>
+      <c r="L28">
+        <v>17.66</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2174.71</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>54.4</v>
+      </c>
+      <c r="Q28">
+        <v>16.99</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>5133.76</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="V28">
+        <v>20.54</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>44.26</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>2.16</v>
+      </c>
+      <c r="Y28">
+        <v>7.8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>327.12</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>6155.71</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>58.6</v>
+      </c>
+      <c r="L29">
+        <v>107.99</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>7552.59</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="Q29">
+        <v>94.41</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>9311.51</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="V29">
+        <v>60.86</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>160.54</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>2.64</v>
+      </c>
+      <c r="Y29">
+        <v>28.47</v>
       </c>
     </row>
     <row r="30" spans="1:25">
       <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="E30">
+        <v>28</v>
+      </c>
+      <c r="F30">
+        <v>28</v>
+      </c>
+      <c r="G30">
+        <v>157.92</v>
+      </c>
+      <c r="H30">
+        <v>31</v>
+      </c>
+      <c r="I30">
+        <v>1515.84</v>
+      </c>
+      <c r="J30">
+        <v>21</v>
+      </c>
+      <c r="K30">
+        <v>75</v>
+      </c>
+      <c r="L30">
+        <v>48.9</v>
+      </c>
+      <c r="M30">
+        <v>43</v>
+      </c>
+      <c r="N30">
+        <v>2670.93</v>
+      </c>
+      <c r="O30">
+        <v>25</v>
+      </c>
+      <c r="P30">
+        <v>89.3</v>
+      </c>
+      <c r="Q30">
+        <v>62.11</v>
+      </c>
+      <c r="R30">
         <v>57</v>
       </c>
-      <c r="D30">
-        <v>19</v>
-      </c>
-      <c r="E30">
-        <v>19</v>
-      </c>
-      <c r="F30">
-        <v>19</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>10</v>
-      </c>
-      <c r="N30">
-        <v>26.97</v>
-      </c>
-      <c r="O30">
-        <v>8</v>
-      </c>
-      <c r="P30">
-        <v>42.1</v>
-      </c>
-      <c r="Q30">
-        <v>2.7</v>
-      </c>
-      <c r="R30">
-        <v>12</v>
-      </c>
       <c r="S30">
-        <v>26.97</v>
+        <v>3065.86</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="U30">
-        <v>47.4</v>
+        <v>89.3</v>
       </c>
       <c r="V30">
-        <v>2.25</v>
+        <v>53.79</v>
       </c>
       <c r="W30">
-        <v>1.42</v>
+        <v>109.5</v>
       </c>
       <c r="X30">
-        <v>0.63</v>
+        <v>2.04</v>
+      </c>
+      <c r="Y30">
+        <v>19.41</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2800,64 +2836,73 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>11.28</v>
+      </c>
+      <c r="H31">
         <v>1</v>
       </c>
-      <c r="E31">
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
         <v>1</v>
       </c>
-      <c r="F31">
+      <c r="K31">
+        <v>50</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
         <v>1</v>
       </c>
-      <c r="G31">
-        <v>5.64</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
       <c r="N31">
         <v>0</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31">
+        <v>50</v>
+      </c>
+      <c r="Q31">
         <v>0</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S31">
         <v>0</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U31">
+        <v>100</v>
+      </c>
+      <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
         <v>0</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y31">
         <v>0</v>
@@ -2868,76 +2913,76 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D32">
-        <v>114</v>
+        <v>427</v>
       </c>
       <c r="E32">
-        <v>116</v>
+        <v>428</v>
       </c>
       <c r="F32">
-        <v>116</v>
+        <v>428</v>
       </c>
       <c r="G32">
-        <v>657.88</v>
+        <v>2467.5</v>
       </c>
       <c r="H32">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="I32">
-        <v>1483.66</v>
+        <v>14553.27</v>
       </c>
       <c r="J32">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="K32">
-        <v>38.6</v>
+        <v>43.1</v>
       </c>
       <c r="L32">
-        <v>17.66</v>
+        <v>52.16</v>
       </c>
       <c r="M32">
-        <v>128</v>
+        <v>896</v>
       </c>
       <c r="N32">
-        <v>2174.71</v>
+        <v>50978.58</v>
       </c>
       <c r="O32">
-        <v>62</v>
+        <v>378</v>
       </c>
       <c r="P32">
-        <v>54.4</v>
+        <v>88.5</v>
       </c>
       <c r="Q32">
-        <v>16.99</v>
+        <v>56.9</v>
       </c>
       <c r="R32">
-        <v>249</v>
+        <v>1217</v>
       </c>
       <c r="S32">
-        <v>5133.76</v>
+        <v>64836.32</v>
       </c>
       <c r="T32">
-        <v>65</v>
+        <v>385</v>
       </c>
       <c r="U32">
-        <v>57</v>
+        <v>90.2</v>
       </c>
       <c r="V32">
-        <v>20.62</v>
+        <v>53.28</v>
       </c>
       <c r="W32">
-        <v>44.26</v>
+        <v>151.49</v>
       </c>
       <c r="X32">
-        <v>2.15</v>
+        <v>2.84</v>
       </c>
       <c r="Y32">
-        <v>7.8</v>
+        <v>26.28</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2945,76 +2990,76 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D33">
-        <v>58</v>
+        <v>413</v>
       </c>
       <c r="E33">
-        <v>58</v>
+        <v>417</v>
       </c>
       <c r="F33">
-        <v>58</v>
+        <v>417</v>
       </c>
       <c r="G33">
-        <v>327.12</v>
+        <v>2358.65</v>
       </c>
       <c r="H33">
-        <v>57</v>
+        <v>830</v>
       </c>
       <c r="I33">
-        <v>6155.71</v>
+        <v>53790.47</v>
       </c>
       <c r="J33">
-        <v>34</v>
+        <v>355</v>
       </c>
       <c r="K33">
-        <v>58.6</v>
+        <v>86</v>
       </c>
       <c r="L33">
-        <v>107.99</v>
+        <v>64.81</v>
       </c>
       <c r="M33">
-        <v>80</v>
+        <v>971</v>
       </c>
       <c r="N33">
-        <v>7552.59</v>
+        <v>55864.97</v>
       </c>
       <c r="O33">
-        <v>47</v>
+        <v>371</v>
       </c>
       <c r="P33">
-        <v>81</v>
+        <v>89.8</v>
       </c>
       <c r="Q33">
-        <v>94.41</v>
+        <v>57.53</v>
       </c>
       <c r="R33">
-        <v>153</v>
+        <v>1196</v>
       </c>
       <c r="S33">
-        <v>9311.51</v>
+        <v>63974.41</v>
       </c>
       <c r="T33">
-        <v>47</v>
+        <v>374</v>
       </c>
       <c r="U33">
-        <v>81</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V33">
-        <v>60.86</v>
+        <v>53.49</v>
       </c>
       <c r="W33">
-        <v>160.54</v>
+        <v>153.42</v>
       </c>
       <c r="X33">
-        <v>2.64</v>
+        <v>2.87</v>
       </c>
       <c r="Y33">
-        <v>28.47</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3022,76 +3067,76 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D34">
-        <v>28</v>
+        <v>623</v>
       </c>
       <c r="E34">
-        <v>28</v>
+        <v>626</v>
       </c>
       <c r="F34">
-        <v>28</v>
+        <v>626</v>
       </c>
       <c r="G34">
-        <v>157.92</v>
+        <v>3530.64</v>
       </c>
       <c r="H34">
-        <v>31</v>
+        <v>512</v>
       </c>
       <c r="I34">
-        <v>1515.84</v>
+        <v>25290.43</v>
       </c>
       <c r="J34">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="K34">
-        <v>75</v>
+        <v>45.9</v>
       </c>
       <c r="L34">
-        <v>48.9</v>
+        <v>49.4</v>
       </c>
       <c r="M34">
-        <v>43</v>
+        <v>794</v>
       </c>
       <c r="N34">
-        <v>2670.93</v>
+        <v>35867.09</v>
       </c>
       <c r="O34">
-        <v>25</v>
+        <v>356</v>
       </c>
       <c r="P34">
-        <v>89.3</v>
+        <v>57.1</v>
       </c>
       <c r="Q34">
-        <v>62.11</v>
+        <v>45.17</v>
       </c>
       <c r="R34">
-        <v>57</v>
+        <v>1226</v>
       </c>
       <c r="S34">
-        <v>3065.84</v>
+        <v>44858.95</v>
       </c>
       <c r="T34">
-        <v>25</v>
+        <v>374</v>
       </c>
       <c r="U34">
-        <v>89.3</v>
+        <v>60</v>
       </c>
       <c r="V34">
-        <v>53.79</v>
+        <v>36.59</v>
       </c>
       <c r="W34">
-        <v>109.49</v>
+        <v>71.66</v>
       </c>
       <c r="X34">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Y34">
-        <v>19.41</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3099,76 +3144,76 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>341</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>341</v>
       </c>
       <c r="G35">
-        <v>11.28</v>
+        <v>1923.24</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>402</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>18001.66</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>175</v>
       </c>
       <c r="K35">
-        <v>50</v>
+        <v>52.7</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>44.78</v>
       </c>
       <c r="M35">
-        <v>1</v>
+        <v>597</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>20219.27</v>
       </c>
       <c r="O35">
-        <v>1</v>
+        <v>245</v>
       </c>
       <c r="P35">
-        <v>50</v>
+        <v>73.8</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>33.87</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>654</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>20849</v>
       </c>
       <c r="T35">
-        <v>2</v>
+        <v>248</v>
       </c>
       <c r="U35">
-        <v>100</v>
+        <v>74.7</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>31.88</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>61.14</v>
       </c>
       <c r="X35">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3176,943 +3221,931 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
         <v>41</v>
       </c>
-      <c r="C36" t="s">
-        <v>47</v>
-      </c>
       <c r="D36">
-        <v>427</v>
+        <v>332</v>
       </c>
       <c r="E36">
-        <v>428</v>
+        <v>340</v>
       </c>
       <c r="F36">
-        <v>428</v>
+        <v>340</v>
       </c>
       <c r="G36">
-        <v>2467.5</v>
+        <v>1917.6</v>
       </c>
       <c r="H36">
-        <v>279</v>
+        <v>199</v>
       </c>
       <c r="I36">
-        <v>14553.27</v>
+        <v>2255.04</v>
       </c>
       <c r="J36">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="K36">
-        <v>43.1</v>
+        <v>38.9</v>
       </c>
       <c r="L36">
-        <v>52.16</v>
+        <v>11.33</v>
       </c>
       <c r="M36">
-        <v>896</v>
+        <v>199</v>
       </c>
       <c r="N36">
-        <v>50979.29</v>
+        <v>2255.04</v>
       </c>
       <c r="O36">
-        <v>378</v>
+        <v>129</v>
       </c>
       <c r="P36">
-        <v>88.5</v>
+        <v>38.9</v>
       </c>
       <c r="Q36">
-        <v>56.9</v>
+        <v>11.33</v>
       </c>
       <c r="R36">
-        <v>1219</v>
+        <v>199</v>
       </c>
       <c r="S36">
-        <v>64840.49</v>
+        <v>2255.04</v>
       </c>
       <c r="T36">
-        <v>385</v>
+        <v>129</v>
       </c>
       <c r="U36">
-        <v>90.2</v>
+        <v>38.9</v>
       </c>
       <c r="V36">
-        <v>53.19</v>
+        <v>11.33</v>
       </c>
       <c r="W36">
-        <v>151.5</v>
+        <v>6.63</v>
       </c>
       <c r="X36">
-        <v>2.85</v>
+        <v>0.59</v>
       </c>
       <c r="Y36">
-        <v>26.28</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
         <v>48</v>
       </c>
       <c r="D37">
-        <v>415</v>
+        <v>30</v>
       </c>
       <c r="E37">
-        <v>419</v>
+        <v>30</v>
       </c>
       <c r="F37">
-        <v>419</v>
+        <v>30</v>
       </c>
       <c r="G37">
-        <v>2369.93</v>
+        <v>269.1</v>
       </c>
       <c r="H37">
-        <v>830</v>
+        <v>16</v>
       </c>
       <c r="I37">
-        <v>53790.72</v>
+        <v>819.4400000000001</v>
       </c>
       <c r="J37">
-        <v>355</v>
+        <v>8</v>
       </c>
       <c r="K37">
-        <v>85.5</v>
+        <v>26.7</v>
       </c>
       <c r="L37">
-        <v>64.81</v>
+        <v>51.22</v>
       </c>
       <c r="M37">
-        <v>971</v>
+        <v>16</v>
       </c>
       <c r="N37">
-        <v>55865.22</v>
+        <v>819.4400000000001</v>
       </c>
       <c r="O37">
-        <v>371</v>
+        <v>8</v>
       </c>
       <c r="P37">
-        <v>89.40000000000001</v>
+        <v>26.7</v>
       </c>
       <c r="Q37">
-        <v>57.53</v>
+        <v>51.22</v>
       </c>
       <c r="R37">
-        <v>1202</v>
+        <v>129</v>
       </c>
       <c r="S37">
-        <v>63976.89</v>
+        <v>8340.4</v>
       </c>
       <c r="T37">
-        <v>374</v>
+        <v>17</v>
       </c>
       <c r="U37">
-        <v>90.09999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="V37">
-        <v>53.23</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="W37">
-        <v>152.69</v>
+        <v>278.01</v>
       </c>
       <c r="X37">
-        <v>2.87</v>
+        <v>4.3</v>
       </c>
       <c r="Y37">
-        <v>27</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="38" spans="1:25">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D38">
-        <v>771</v>
+        <v>516</v>
       </c>
       <c r="E38">
-        <v>774</v>
+        <v>517</v>
       </c>
       <c r="F38">
-        <v>774</v>
+        <v>517</v>
       </c>
       <c r="G38">
-        <v>4365.36</v>
+        <v>4637.49</v>
       </c>
       <c r="H38">
-        <v>530</v>
+        <v>323</v>
       </c>
       <c r="I38">
-        <v>27562.48</v>
+        <v>3203.56</v>
       </c>
       <c r="J38">
-        <v>288</v>
+        <v>230</v>
       </c>
       <c r="K38">
-        <v>37.4</v>
+        <v>44.6</v>
       </c>
       <c r="L38">
-        <v>52</v>
+        <v>9.92</v>
       </c>
       <c r="M38">
-        <v>827</v>
+        <v>494</v>
       </c>
       <c r="N38">
-        <v>37441.26</v>
+        <v>17344.18</v>
       </c>
       <c r="O38">
-        <v>367</v>
+        <v>285</v>
       </c>
       <c r="P38">
-        <v>47.6</v>
+        <v>55.2</v>
       </c>
       <c r="Q38">
-        <v>45.27</v>
+        <v>35.11</v>
       </c>
       <c r="R38">
-        <v>1264</v>
+        <v>622</v>
       </c>
       <c r="S38">
-        <v>47170.93</v>
+        <v>19052.38</v>
       </c>
       <c r="T38">
-        <v>384</v>
+        <v>296</v>
       </c>
       <c r="U38">
-        <v>49.8</v>
+        <v>57.4</v>
       </c>
       <c r="V38">
-        <v>37.32</v>
+        <v>30.63</v>
       </c>
       <c r="W38">
-        <v>60.94</v>
+        <v>36.85</v>
       </c>
       <c r="X38">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="Y38">
-        <v>10.81</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="39" spans="1:25">
       <c r="A39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39">
+        <v>16</v>
+      </c>
+      <c r="E39">
+        <v>16</v>
+      </c>
+      <c r="F39">
+        <v>16</v>
+      </c>
+      <c r="G39">
+        <v>143.52</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>28</v>
+      </c>
+      <c r="N39">
+        <v>233.34</v>
+      </c>
+      <c r="O39">
+        <v>11</v>
+      </c>
+      <c r="P39">
+        <v>68.8</v>
+      </c>
+      <c r="Q39">
+        <v>8.33</v>
+      </c>
+      <c r="R39">
         <v>29</v>
       </c>
-      <c r="B39" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" t="s">
-        <v>57</v>
-      </c>
-      <c r="D39">
-        <v>482</v>
-      </c>
-      <c r="E39">
-        <v>491</v>
-      </c>
-      <c r="F39">
-        <v>491</v>
-      </c>
-      <c r="G39">
-        <v>2800.47</v>
-      </c>
-      <c r="H39">
-        <v>409</v>
-      </c>
-      <c r="I39">
-        <v>18019.63</v>
-      </c>
-      <c r="J39">
-        <v>179</v>
-      </c>
-      <c r="K39">
-        <v>37.1</v>
-      </c>
-      <c r="L39">
-        <v>44.06</v>
-      </c>
-      <c r="M39">
-        <v>608</v>
-      </c>
-      <c r="N39">
-        <v>20238.09</v>
-      </c>
-      <c r="O39">
-        <v>249</v>
-      </c>
-      <c r="P39">
-        <v>51.7</v>
-      </c>
-      <c r="Q39">
-        <v>33.29</v>
-      </c>
-      <c r="R39">
-        <v>665</v>
-      </c>
       <c r="S39">
-        <v>20867.9</v>
+        <v>233.34</v>
       </c>
       <c r="T39">
-        <v>252</v>
+        <v>12</v>
       </c>
       <c r="U39">
-        <v>52.3</v>
+        <v>75</v>
       </c>
       <c r="V39">
-        <v>31.38</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="W39">
-        <v>42.5</v>
+        <v>14.58</v>
       </c>
       <c r="X39">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="Y39">
-        <v>7.45</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="40" spans="1:25">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>42</v>
-      </c>
       <c r="D40">
-        <v>422</v>
+        <v>313</v>
       </c>
       <c r="E40">
-        <v>430</v>
+        <v>315</v>
       </c>
       <c r="F40">
-        <v>430</v>
+        <v>315</v>
       </c>
       <c r="G40">
-        <v>2425.2</v>
+        <v>2825.55</v>
       </c>
       <c r="H40">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="I40">
-        <v>2255.22</v>
+        <v>203.09</v>
       </c>
       <c r="J40">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="K40">
-        <v>30.3</v>
+        <v>37.4</v>
       </c>
       <c r="L40">
-        <v>11.33</v>
+        <v>1.37</v>
       </c>
       <c r="M40">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="N40">
-        <v>2255.22</v>
+        <v>203.09</v>
       </c>
       <c r="O40">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="P40">
-        <v>30.3</v>
+        <v>37.4</v>
       </c>
       <c r="Q40">
-        <v>11.33</v>
+        <v>1.37</v>
       </c>
       <c r="R40">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="S40">
-        <v>2255.22</v>
+        <v>203.09</v>
       </c>
       <c r="T40">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="U40">
-        <v>30.3</v>
+        <v>37.4</v>
       </c>
       <c r="V40">
-        <v>11.33</v>
+        <v>1.37</v>
       </c>
       <c r="W40">
-        <v>5.24</v>
+        <v>0.64</v>
       </c>
       <c r="X40">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="Y40">
-        <v>0.93</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:25">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
         <v>41</v>
       </c>
-      <c r="C41" t="s">
-        <v>49</v>
-      </c>
       <c r="D41">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E41">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F41">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G41">
-        <v>269.1</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I41">
-        <v>819.6</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K41">
-        <v>26.7</v>
+        <v>50</v>
       </c>
       <c r="L41">
-        <v>51.23</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N41">
-        <v>819.6</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P41">
-        <v>26.7</v>
+        <v>50</v>
       </c>
       <c r="Q41">
-        <v>51.23</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="S41">
-        <v>8342.66</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="U41">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="V41">
-        <v>63.2</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>278.09</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>4.4</v>
-      </c>
-      <c r="Y41">
-        <v>31</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="42" spans="1:25">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D42">
-        <v>516</v>
+        <v>69</v>
       </c>
       <c r="E42">
-        <v>517</v>
+        <v>69</v>
       </c>
       <c r="F42">
-        <v>517</v>
+        <v>69</v>
       </c>
       <c r="G42">
-        <v>4637.49</v>
+        <v>326.37</v>
       </c>
       <c r="H42">
-        <v>365</v>
+        <v>23</v>
       </c>
       <c r="I42">
-        <v>3354.21</v>
+        <v>207.55</v>
       </c>
       <c r="J42">
-        <v>261</v>
+        <v>15</v>
       </c>
       <c r="K42">
-        <v>50.6</v>
+        <v>21.7</v>
       </c>
       <c r="L42">
-        <v>9.19</v>
+        <v>9.02</v>
       </c>
       <c r="M42">
-        <v>550</v>
+        <v>52</v>
       </c>
       <c r="N42">
-        <v>17368.93</v>
+        <v>1093.46</v>
       </c>
       <c r="O42">
-        <v>326</v>
+        <v>27</v>
       </c>
       <c r="P42">
-        <v>63.2</v>
+        <v>39.1</v>
       </c>
       <c r="Q42">
-        <v>31.58</v>
+        <v>21.03</v>
       </c>
       <c r="R42">
-        <v>682</v>
+        <v>135</v>
       </c>
       <c r="S42">
-        <v>19117.96</v>
+        <v>2734.76</v>
       </c>
       <c r="T42">
-        <v>336</v>
+        <v>37</v>
       </c>
       <c r="U42">
-        <v>65.09999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="V42">
-        <v>28.03</v>
+        <v>20.26</v>
       </c>
       <c r="W42">
-        <v>36.98</v>
+        <v>39.63</v>
       </c>
       <c r="X42">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="Y42">
-        <v>4.12</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:25">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D43">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="E43">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="F43">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="G43">
-        <v>143.52</v>
+        <v>600.71</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="I43">
-        <v>15.19</v>
+        <v>3194.31</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="K43">
-        <v>6.2</v>
+        <v>42.5</v>
       </c>
       <c r="L43">
-        <v>15.19</v>
+        <v>37.14</v>
       </c>
       <c r="M43">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="N43">
-        <v>233.37</v>
+        <v>3563.29</v>
       </c>
       <c r="O43">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="P43">
-        <v>68.8</v>
+        <v>51.2</v>
       </c>
       <c r="Q43">
-        <v>8.33</v>
+        <v>28.97</v>
       </c>
       <c r="R43">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="S43">
-        <v>233.37</v>
+        <v>3852.5</v>
       </c>
       <c r="T43">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="U43">
-        <v>75</v>
+        <v>54.3</v>
       </c>
       <c r="V43">
-        <v>8.050000000000001</v>
+        <v>23.49</v>
       </c>
       <c r="W43">
-        <v>14.59</v>
+        <v>30.33</v>
       </c>
       <c r="X43">
-        <v>1.81</v>
+        <v>1.29</v>
       </c>
       <c r="Y43">
-        <v>1.63</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="44" spans="1:25">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D44">
-        <v>313</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>315</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>315</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>2825.55</v>
+        <v>4.73</v>
       </c>
       <c r="H44">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="I44">
-        <v>203.09</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>37.1</v>
-      </c>
-      <c r="L44">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M44">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="N44">
-        <v>203.09</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>37.1</v>
-      </c>
-      <c r="Q44">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>203.09</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>37.1</v>
-      </c>
-      <c r="V44">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:25">
       <c r="A45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45">
         <v>31</v>
       </c>
-      <c r="B45" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" t="s">
-        <v>42</v>
-      </c>
-      <c r="D45">
-        <v>14</v>
-      </c>
       <c r="E45">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F45">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>146.63</v>
       </c>
       <c r="H45">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>50.07</v>
       </c>
       <c r="J45">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K45">
-        <v>50</v>
+        <v>51.6</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>50.07</v>
       </c>
       <c r="O45">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="P45">
-        <v>50</v>
+        <v>51.6</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>50.07</v>
       </c>
       <c r="T45">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="U45">
-        <v>50</v>
+        <v>51.6</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X45">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="Y45">
+        <v>0.34</v>
       </c>
     </row>
     <row r="46" spans="1:25">
       <c r="A46" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D46">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="F46">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="G46">
-        <v>326.37</v>
+        <v>56.72</v>
       </c>
       <c r="H46">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>207.54</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K46">
-        <v>21.7</v>
+        <v>12.5</v>
       </c>
       <c r="L46">
-        <v>9.02</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="N46">
-        <v>1103.4</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>40.6</v>
+        <v>50</v>
       </c>
       <c r="Q46">
-        <v>20.43</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>135</v>
+        <v>5</v>
       </c>
       <c r="S46">
-        <v>2734.86</v>
+        <v>0</v>
       </c>
       <c r="T46">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>55.1</v>
+        <v>50</v>
       </c>
       <c r="V46">
-        <v>20.26</v>
+        <v>0</v>
       </c>
       <c r="W46">
-        <v>39.64</v>
+        <v>0</v>
       </c>
       <c r="X46">
-        <v>1.96</v>
+        <v>0.62</v>
       </c>
       <c r="Y46">
-        <v>8.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:25">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B47" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" t="s">
         <v>41</v>
       </c>
-      <c r="C47" t="s">
-        <v>56</v>
-      </c>
       <c r="D47">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="E47">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="F47">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="G47">
-        <v>600.71</v>
+        <v>56.72</v>
       </c>
       <c r="H47">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>3193.92</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="K47">
-        <v>41.7</v>
+        <v>25</v>
       </c>
       <c r="L47">
-        <v>35.89</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>126</v>
+        <v>3</v>
       </c>
       <c r="N47">
-        <v>3562.9</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="P47">
-        <v>51.2</v>
+        <v>25</v>
       </c>
       <c r="Q47">
-        <v>28.28</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>165</v>
+        <v>3</v>
       </c>
       <c r="S47">
-        <v>3852.11</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="U47">
-        <v>54.3</v>
+        <v>25</v>
       </c>
       <c r="V47">
-        <v>23.35</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>30.33</v>
+        <v>0</v>
       </c>
       <c r="X47">
-        <v>1.3</v>
+        <v>0.38</v>
       </c>
       <c r="Y47">
-        <v>6.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:25">
       <c r="A48" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C48" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -4154,178 +4187,175 @@
         <v>0</v>
       </c>
       <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:25">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C49" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D49">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E49">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F49">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G49">
-        <v>146.63</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>50.07</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>51.6</v>
-      </c>
-      <c r="L49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="N49">
-        <v>50.07</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="P49">
-        <v>51.6</v>
+        <v>27.8</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="S49">
-        <v>50.07</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U49">
-        <v>51.6</v>
+        <v>38.9</v>
       </c>
       <c r="V49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="Y49">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="50" spans="1:25">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" t="s">
         <v>41</v>
       </c>
-      <c r="C50" t="s">
-        <v>49</v>
-      </c>
       <c r="D50">
-        <v>589</v>
+        <v>10</v>
       </c>
       <c r="E50">
-        <v>594</v>
+        <v>10</v>
       </c>
       <c r="F50">
-        <v>594</v>
+        <v>10</v>
       </c>
       <c r="G50">
-        <v>2851.2</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K50">
+        <v>30</v>
+      </c>
+      <c r="L50">
         <v>0</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N50">
         <v>0</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P50">
+        <v>30</v>
+      </c>
+      <c r="Q50">
         <v>0</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S50">
         <v>0</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U50">
+        <v>30</v>
+      </c>
+      <c r="V50">
         <v>0</v>
       </c>
       <c r="W50">
         <v>0</v>
       </c>
       <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="51" spans="1:25">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
         <v>56</v>
       </c>
       <c r="D51">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="E51">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="F51">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="G51">
-        <v>619.2</v>
+        <v>0</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -4340,102 +4370,105 @@
         <v>0</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>36.08</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>37.5</v>
+      </c>
+      <c r="Q51">
+        <v>3.01</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>94.11</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>41.7</v>
+      </c>
+      <c r="V51">
+        <v>5.54</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="X51">
-        <v>0</v>
-      </c>
-      <c r="Y51">
-        <v>0</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="52" spans="1:25">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" t="s">
         <v>41</v>
       </c>
-      <c r="C52" t="s">
-        <v>57</v>
-      </c>
       <c r="D52">
+        <v>15</v>
+      </c>
+      <c r="E52">
+        <v>15</v>
+      </c>
+      <c r="F52">
+        <v>15</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
         <v>8</v>
       </c>
-      <c r="E52">
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>6</v>
+      </c>
+      <c r="K52">
+        <v>40</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
         <v>8</v>
       </c>
-      <c r="F52">
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>6</v>
+      </c>
+      <c r="P52">
+        <v>40</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
         <v>8</v>
       </c>
-      <c r="G52">
-        <v>56.72</v>
-      </c>
-      <c r="H52">
-        <v>3</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>2</v>
-      </c>
-      <c r="K52">
-        <v>25</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>5</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>4</v>
-      </c>
-      <c r="P52">
-        <v>50</v>
-      </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52">
-        <v>5</v>
-      </c>
       <c r="S52">
         <v>0</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U52">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -4444,904 +4477,928 @@
         <v>0</v>
       </c>
       <c r="X52">
-        <v>0.62</v>
-      </c>
-      <c r="Y52">
-        <v>0</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="53" spans="1:25">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D53">
-        <v>8</v>
+        <v>157</v>
       </c>
       <c r="E53">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="F53">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="G53">
-        <v>56.72</v>
+        <v>807.38</v>
       </c>
       <c r="H53">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>150.02</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K53">
-        <v>50</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="M53">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>495.66</v>
       </c>
       <c r="O53">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="P53">
-        <v>50</v>
+        <v>53.5</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R53">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>509.15</v>
       </c>
       <c r="T53">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="U53">
-        <v>50</v>
+        <v>53.5</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X53">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B54" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" t="s">
         <v>41</v>
       </c>
-      <c r="C54" t="s">
-        <v>56</v>
-      </c>
       <c r="D54">
-        <v>3</v>
+        <v>466</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>469</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>469</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>2974.39</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>209.08</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>32.6</v>
+      </c>
+      <c r="L54">
+        <v>1.04</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>209.08</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>32.6</v>
+      </c>
+      <c r="Q54">
+        <v>1.04</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>209.08</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>32.6</v>
+      </c>
+      <c r="V54">
+        <v>1.04</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="Y54">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:25">
       <c r="A55" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C55" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D55">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="E55">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F55">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>303.33</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>546.95</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>16.4</v>
+      </c>
+      <c r="L55">
+        <v>22.79</v>
       </c>
       <c r="M55">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1072.87</v>
       </c>
       <c r="O55">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="P55">
-        <v>27.8</v>
+        <v>23</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>23.84</v>
       </c>
       <c r="R55">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>2669.44</v>
       </c>
       <c r="T55">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="U55">
-        <v>38.9</v>
+        <v>45.9</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>24.05</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>43.06</v>
       </c>
       <c r="X55">
-        <v>0.37</v>
+        <v>1.79</v>
+      </c>
+      <c r="Y55">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:25">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="E56">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="F56">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>694.98</v>
       </c>
       <c r="H56">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>353.37</v>
       </c>
       <c r="J56">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="K56">
-        <v>30</v>
+        <v>39.9</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="M56">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>914.8099999999999</v>
       </c>
       <c r="O56">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="P56">
-        <v>30</v>
+        <v>50.3</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="R56">
-        <v>4</v>
+        <v>183</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1229.27</v>
       </c>
       <c r="T56">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="U56">
-        <v>30</v>
+        <v>55.9</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="X56">
-        <v>0.4</v>
+        <v>1.28</v>
+      </c>
+      <c r="Y56">
+        <v>1.77</v>
       </c>
     </row>
     <row r="57" spans="1:25">
       <c r="A57" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57">
+        <v>73</v>
+      </c>
+      <c r="E57">
+        <v>73</v>
+      </c>
+      <c r="F57">
+        <v>73</v>
+      </c>
+      <c r="G57">
+        <v>354.78</v>
+      </c>
+      <c r="H57">
+        <v>76</v>
+      </c>
+      <c r="I57">
+        <v>2083.16</v>
+      </c>
+      <c r="J57">
         <v>36</v>
       </c>
-      <c r="B57" t="s">
-        <v>41</v>
-      </c>
-      <c r="C57" t="s">
-        <v>57</v>
-      </c>
-      <c r="D57">
-        <v>24</v>
-      </c>
-      <c r="E57">
-        <v>24</v>
-      </c>
-      <c r="F57">
-        <v>24</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
       <c r="K57">
-        <v>0</v>
+        <v>49.3</v>
+      </c>
+      <c r="L57">
+        <v>27.41</v>
       </c>
       <c r="M57">
-        <v>12</v>
+        <v>148</v>
       </c>
       <c r="N57">
-        <v>36.08</v>
+        <v>3451.29</v>
       </c>
       <c r="O57">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="P57">
-        <v>37.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Q57">
-        <v>3.01</v>
+        <v>23.32</v>
       </c>
       <c r="R57">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="S57">
-        <v>94.11</v>
+        <v>3552.83</v>
       </c>
       <c r="T57">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="U57">
-        <v>41.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="V57">
-        <v>5.54</v>
+        <v>22.49</v>
       </c>
       <c r="W57">
-        <v>3.92</v>
+        <v>48.67</v>
       </c>
       <c r="X57">
-        <v>0.71</v>
+        <v>2.16</v>
+      </c>
+      <c r="Y57">
+        <v>10.01</v>
       </c>
     </row>
     <row r="58" spans="1:25">
       <c r="A58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" t="s">
         <v>41</v>
       </c>
-      <c r="C58" t="s">
-        <v>42</v>
-      </c>
       <c r="D58">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E58">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F58">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>140.94</v>
       </c>
       <c r="H58">
         <v>8</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>10.03</v>
       </c>
       <c r="J58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K58">
-        <v>40</v>
+        <v>17.2</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M58">
         <v>8</v>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>10.03</v>
       </c>
       <c r="O58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P58">
-        <v>40</v>
+        <v>17.2</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R58">
         <v>8</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>10.03</v>
       </c>
       <c r="T58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U58">
-        <v>40</v>
+        <v>17.2</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="X58">
-        <v>0.53</v>
+        <v>0.28</v>
+      </c>
+      <c r="Y58">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:25">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
+        <v>40</v>
+      </c>
+      <c r="C59" t="s">
         <v>41</v>
       </c>
-      <c r="C59" t="s">
-        <v>57</v>
-      </c>
       <c r="D59">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="E59">
-        <v>158</v>
+        <v>7</v>
       </c>
       <c r="F59">
-        <v>158</v>
+        <v>7</v>
       </c>
       <c r="G59">
-        <v>807.38</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>150.02</v>
+        <v>0</v>
       </c>
       <c r="J59">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K59">
-        <v>9.6</v>
+        <v>42.9</v>
       </c>
       <c r="L59">
-        <v>5.77</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>148</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>495.66</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="P59">
-        <v>56.7</v>
+        <v>42.9</v>
       </c>
       <c r="Q59">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R59">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="S59">
-        <v>509.15</v>
+        <v>0</v>
       </c>
       <c r="T59">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="U59">
-        <v>56.7</v>
+        <v>42.9</v>
       </c>
       <c r="V59">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="W59">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="X59">
-        <v>0.95</v>
-      </c>
-      <c r="Y59">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="60" spans="1:25">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s">
         <v>42</v>
       </c>
       <c r="D60">
-        <v>466</v>
+        <v>55</v>
       </c>
       <c r="E60">
-        <v>469</v>
+        <v>55</v>
       </c>
       <c r="F60">
-        <v>469</v>
+        <v>55</v>
       </c>
       <c r="G60">
-        <v>2974.39</v>
+        <v>359.15</v>
       </c>
       <c r="H60">
-        <v>212</v>
+        <v>12</v>
       </c>
       <c r="I60">
-        <v>209.08</v>
+        <v>201.44</v>
       </c>
       <c r="J60">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="K60">
-        <v>33.5</v>
+        <v>21.8</v>
       </c>
       <c r="L60">
-        <v>0.99</v>
+        <v>16.79</v>
       </c>
       <c r="M60">
-        <v>212</v>
+        <v>17</v>
       </c>
       <c r="N60">
-        <v>209.08</v>
+        <v>201.44</v>
       </c>
       <c r="O60">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="P60">
-        <v>33.5</v>
+        <v>29.1</v>
       </c>
       <c r="Q60">
-        <v>0.99</v>
+        <v>11.85</v>
       </c>
       <c r="R60">
-        <v>212</v>
+        <v>27</v>
       </c>
       <c r="S60">
-        <v>209.08</v>
+        <v>245.42</v>
       </c>
       <c r="T60">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="U60">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="V60">
-        <v>0.99</v>
+        <v>9.09</v>
       </c>
       <c r="W60">
-        <v>0.45</v>
+        <v>4.46</v>
       </c>
       <c r="X60">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="Y60">
-        <v>0.07000000000000001</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="61" spans="1:25">
       <c r="A61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C61" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D61">
-        <v>61</v>
+        <v>279</v>
       </c>
       <c r="E61">
-        <v>62</v>
+        <v>280</v>
       </c>
       <c r="F61">
-        <v>62</v>
+        <v>280</v>
       </c>
       <c r="G61">
-        <v>303.33</v>
+        <v>1866.55</v>
       </c>
       <c r="H61">
-        <v>24</v>
+        <v>287</v>
       </c>
       <c r="I61">
-        <v>547.03</v>
+        <v>1281.51</v>
       </c>
       <c r="J61">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="K61">
-        <v>16.4</v>
+        <v>57.3</v>
       </c>
       <c r="L61">
-        <v>22.79</v>
+        <v>4.47</v>
       </c>
       <c r="M61">
-        <v>48</v>
+        <v>422</v>
       </c>
       <c r="N61">
-        <v>1117.03</v>
+        <v>1432.42</v>
       </c>
       <c r="O61">
-        <v>14</v>
+        <v>212</v>
       </c>
       <c r="P61">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="Q61">
-        <v>23.27</v>
+        <v>3.39</v>
       </c>
       <c r="R61">
-        <v>116</v>
+        <v>584</v>
       </c>
       <c r="S61">
-        <v>2670.28</v>
+        <v>2363.63</v>
       </c>
       <c r="T61">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="U61">
-        <v>45.9</v>
+        <v>76.7</v>
       </c>
       <c r="V61">
-        <v>23.02</v>
+        <v>4.05</v>
       </c>
       <c r="W61">
-        <v>43.07</v>
+        <v>8.44</v>
       </c>
       <c r="X61">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="Y61">
-        <v>8.800000000000001</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="62" spans="1:25">
       <c r="A62" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C62" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D62">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="E62">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="F62">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G62">
-        <v>694.98</v>
+        <v>1033.26</v>
       </c>
       <c r="H62">
-        <v>102</v>
+        <v>193</v>
       </c>
       <c r="I62">
-        <v>373.38</v>
+        <v>3090.93</v>
       </c>
       <c r="J62">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="K62">
-        <v>46.2</v>
+        <v>79.8</v>
       </c>
       <c r="L62">
-        <v>3.66</v>
+        <v>16.02</v>
       </c>
       <c r="M62">
-        <v>147</v>
+        <v>208</v>
       </c>
       <c r="N62">
-        <v>925.01</v>
+        <v>3136.31</v>
       </c>
       <c r="O62">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="P62">
-        <v>55.9</v>
+        <v>83.3</v>
       </c>
       <c r="Q62">
-        <v>6.29</v>
+        <v>15.08</v>
       </c>
       <c r="R62">
-        <v>199</v>
+        <v>294</v>
       </c>
       <c r="S62">
-        <v>1239.52</v>
+        <v>5479.43</v>
       </c>
       <c r="T62">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="U62">
-        <v>61.5</v>
+        <v>84.2</v>
       </c>
       <c r="V62">
-        <v>6.23</v>
+        <v>18.64</v>
       </c>
       <c r="W62">
-        <v>8.67</v>
+        <v>47.65</v>
       </c>
       <c r="X62">
-        <v>1.39</v>
+        <v>2.56</v>
       </c>
       <c r="Y62">
-        <v>1.78</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="63" spans="1:25">
       <c r="A63" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D63">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="E63">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F63">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="G63">
-        <v>354.78</v>
+        <v>71.83</v>
       </c>
       <c r="H63">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="I63">
-        <v>2084.67</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J63">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="K63">
-        <v>50.7</v>
+        <v>63.6</v>
       </c>
       <c r="L63">
-        <v>26.73</v>
+        <v>2.89</v>
       </c>
       <c r="M63">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="N63">
-        <v>3452.84</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="O63">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="P63">
-        <v>84.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="Q63">
-        <v>22.87</v>
+        <v>2.47</v>
       </c>
       <c r="R63">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="S63">
-        <v>3554.38</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="T63">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="U63">
-        <v>84.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="V63">
-        <v>22.08</v>
+        <v>1.84</v>
       </c>
       <c r="W63">
-        <v>48.69</v>
+        <v>7.87</v>
       </c>
       <c r="X63">
-        <v>2.21</v>
+        <v>4.27</v>
       </c>
       <c r="Y63">
-        <v>10.02</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="64" spans="1:25">
       <c r="A64" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C64" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D64">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E64">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F64">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G64">
-        <v>140.94</v>
+        <v>135.61</v>
       </c>
       <c r="H64">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I64">
-        <v>10.03</v>
+        <v>24.99</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K64">
-        <v>17.2</v>
+        <v>36.8</v>
       </c>
       <c r="L64">
-        <v>1.25</v>
+        <v>3.57</v>
       </c>
       <c r="M64">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="N64">
-        <v>10.03</v>
+        <v>176.72</v>
       </c>
       <c r="O64">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="P64">
-        <v>17.2</v>
+        <v>89.5</v>
       </c>
       <c r="Q64">
-        <v>1.25</v>
+        <v>5.36</v>
       </c>
       <c r="R64">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="S64">
-        <v>10.03</v>
+        <v>176.72</v>
       </c>
       <c r="T64">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="U64">
-        <v>17.2</v>
+        <v>89.5</v>
       </c>
       <c r="V64">
-        <v>1.25</v>
+        <v>5.36</v>
       </c>
       <c r="W64">
-        <v>0.35</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X64">
-        <v>0.28</v>
+        <v>1.74</v>
       </c>
       <c r="Y64">
-        <v>0.07000000000000001</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="65" spans="1:25">
@@ -5349,842 +5406,383 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C65" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D65">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="E65">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="F65">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>916.9400000000001</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>888.63</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="K65">
-        <v>42.9</v>
+        <v>65.7</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>7.86</v>
       </c>
       <c r="M65">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1193.8</v>
       </c>
       <c r="O65">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="P65">
-        <v>42.9</v>
+        <v>78.8</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>255</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>4496.9</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="U65">
-        <v>42.9</v>
+        <v>78.8</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>17.63</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>44.52</v>
       </c>
       <c r="X65">
-        <v>0.43</v>
+        <v>2.52</v>
+      </c>
+      <c r="Y65">
+        <v>4.9</v>
       </c>
     </row>
     <row r="66" spans="1:25">
       <c r="A66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B66" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D66">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="E66">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F66">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="G66">
-        <v>359.15</v>
+        <v>792.16</v>
       </c>
       <c r="H66">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="I66">
-        <v>201.44</v>
+        <v>3812.04</v>
       </c>
       <c r="J66">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="K66">
-        <v>21.8</v>
+        <v>51.1</v>
       </c>
       <c r="L66">
-        <v>16.79</v>
+        <v>54.46</v>
       </c>
       <c r="M66">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="N66">
-        <v>201.44</v>
+        <v>4116.33</v>
       </c>
       <c r="O66">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="P66">
-        <v>29.1</v>
+        <v>53.3</v>
       </c>
       <c r="Q66">
-        <v>11.85</v>
+        <v>52.77</v>
       </c>
       <c r="R66">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="S66">
-        <v>245.42</v>
+        <v>4902.54</v>
       </c>
       <c r="T66">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="U66">
-        <v>34.5</v>
+        <v>66.7</v>
       </c>
       <c r="V66">
-        <v>9.09</v>
+        <v>37.42</v>
       </c>
       <c r="W66">
-        <v>4.46</v>
+        <v>51.61</v>
       </c>
       <c r="X66">
-        <v>0.49</v>
+        <v>1.38</v>
       </c>
       <c r="Y66">
-        <v>0.68</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D67">
-        <v>279</v>
+        <v>36</v>
       </c>
       <c r="E67">
-        <v>280</v>
+        <v>36</v>
       </c>
       <c r="F67">
-        <v>280</v>
+        <v>36</v>
       </c>
       <c r="G67">
-        <v>1866.55</v>
+        <v>235.08</v>
       </c>
       <c r="H67">
-        <v>287</v>
+        <v>17</v>
       </c>
       <c r="I67">
-        <v>1281.55</v>
+        <v>55.21</v>
       </c>
       <c r="J67">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="K67">
-        <v>57.3</v>
+        <v>27.8</v>
       </c>
       <c r="L67">
-        <v>4.47</v>
+        <v>3.25</v>
       </c>
       <c r="M67">
-        <v>422</v>
+        <v>22</v>
       </c>
       <c r="N67">
-        <v>1432.46</v>
+        <v>132.09</v>
       </c>
       <c r="O67">
-        <v>212</v>
+        <v>13</v>
       </c>
       <c r="P67">
-        <v>76</v>
+        <v>36.1</v>
       </c>
       <c r="Q67">
-        <v>3.39</v>
+        <v>6</v>
       </c>
       <c r="R67">
-        <v>585</v>
+        <v>35</v>
       </c>
       <c r="S67">
-        <v>2363.78</v>
+        <v>187.07</v>
       </c>
       <c r="T67">
-        <v>214</v>
+        <v>16</v>
       </c>
       <c r="U67">
-        <v>76.7</v>
+        <v>44.4</v>
       </c>
       <c r="V67">
-        <v>4.04</v>
+        <v>5.34</v>
       </c>
       <c r="W67">
-        <v>8.44</v>
+        <v>5.2</v>
       </c>
       <c r="X67">
-        <v>2.09</v>
+        <v>0.97</v>
       </c>
       <c r="Y67">
-        <v>1.27</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="68" spans="1:25">
       <c r="A68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C68" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D68">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E68">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="F68">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="G68">
-        <v>1033.26</v>
+        <v>869.59</v>
       </c>
       <c r="H68">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="I68">
-        <v>3090.93</v>
+        <v>2275.61</v>
       </c>
       <c r="J68">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="K68">
-        <v>79.8</v>
+        <v>39.8</v>
       </c>
       <c r="L68">
-        <v>16.02</v>
+        <v>23.46</v>
       </c>
       <c r="M68">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="N68">
-        <v>3136.31</v>
+        <v>3422.52</v>
       </c>
       <c r="O68">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P68">
-        <v>83.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Q68">
-        <v>15.08</v>
+        <v>14.5</v>
       </c>
       <c r="R68">
-        <v>295</v>
+        <v>240</v>
       </c>
       <c r="S68">
-        <v>5479.43</v>
+        <v>3442.51</v>
       </c>
       <c r="T68">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="U68">
-        <v>84.2</v>
+        <v>72.7</v>
       </c>
       <c r="V68">
-        <v>18.57</v>
+        <v>14.34</v>
       </c>
       <c r="W68">
-        <v>47.65</v>
+        <v>26.08</v>
       </c>
       <c r="X68">
-        <v>2.57</v>
+        <v>1.82</v>
       </c>
       <c r="Y68">
-        <v>5.3</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="69" spans="1:25">
       <c r="A69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B69" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69" t="s">
         <v>41</v>
       </c>
-      <c r="C69" t="s">
-        <v>46</v>
-      </c>
       <c r="D69">
-        <v>11</v>
+        <v>251</v>
       </c>
       <c r="E69">
-        <v>11</v>
+        <v>257</v>
       </c>
       <c r="F69">
-        <v>11</v>
+        <v>257</v>
       </c>
       <c r="G69">
-        <v>71.83</v>
+        <v>1678.21</v>
       </c>
       <c r="H69">
-        <v>30</v>
+        <v>118</v>
       </c>
       <c r="I69">
-        <v>86.59999999999999</v>
+        <v>369.94</v>
       </c>
       <c r="J69">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="K69">
-        <v>63.6</v>
+        <v>35.9</v>
       </c>
       <c r="L69">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="M69">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="N69">
-        <v>86.59999999999999</v>
+        <v>369.94</v>
       </c>
       <c r="O69">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="P69">
-        <v>81.8</v>
+        <v>35.9</v>
       </c>
       <c r="Q69">
-        <v>2.47</v>
+        <v>3.14</v>
       </c>
       <c r="R69">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="S69">
-        <v>86.59999999999999</v>
+        <v>369.94</v>
       </c>
       <c r="T69">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="U69">
-        <v>81.8</v>
+        <v>35.9</v>
       </c>
       <c r="V69">
-        <v>1.84</v>
+        <v>3.14</v>
       </c>
       <c r="W69">
-        <v>7.87</v>
+        <v>1.44</v>
       </c>
       <c r="X69">
-        <v>4.27</v>
+        <v>0.46</v>
       </c>
       <c r="Y69">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25">
-      <c r="A70" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" t="s">
-        <v>41</v>
-      </c>
-      <c r="C70" t="s">
-        <v>47</v>
-      </c>
-      <c r="D70">
-        <v>19</v>
-      </c>
-      <c r="E70">
-        <v>19</v>
-      </c>
-      <c r="F70">
-        <v>19</v>
-      </c>
-      <c r="G70">
-        <v>135.61</v>
-      </c>
-      <c r="H70">
-        <v>7</v>
-      </c>
-      <c r="I70">
-        <v>24.99</v>
-      </c>
-      <c r="J70">
-        <v>7</v>
-      </c>
-      <c r="K70">
-        <v>36.8</v>
-      </c>
-      <c r="L70">
-        <v>3.57</v>
-      </c>
-      <c r="M70">
-        <v>33</v>
-      </c>
-      <c r="N70">
-        <v>176.72</v>
-      </c>
-      <c r="O70">
-        <v>17</v>
-      </c>
-      <c r="P70">
-        <v>89.5</v>
-      </c>
-      <c r="Q70">
-        <v>5.36</v>
-      </c>
-      <c r="R70">
-        <v>33</v>
-      </c>
-      <c r="S70">
-        <v>176.72</v>
-      </c>
-      <c r="T70">
-        <v>17</v>
-      </c>
-      <c r="U70">
-        <v>89.5</v>
-      </c>
-      <c r="V70">
-        <v>5.36</v>
-      </c>
-      <c r="W70">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="X70">
-        <v>1.74</v>
-      </c>
-      <c r="Y70">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:25">
-      <c r="A71" t="s">
-        <v>40</v>
-      </c>
-      <c r="B71" t="s">
-        <v>41</v>
-      </c>
-      <c r="C71" t="s">
-        <v>48</v>
-      </c>
-      <c r="D71">
-        <v>99</v>
-      </c>
-      <c r="E71">
-        <v>101</v>
-      </c>
-      <c r="F71">
-        <v>101</v>
-      </c>
-      <c r="G71">
-        <v>916.9400000000001</v>
-      </c>
-      <c r="H71">
-        <v>113</v>
-      </c>
-      <c r="I71">
-        <v>888.61</v>
-      </c>
-      <c r="J71">
-        <v>65</v>
-      </c>
-      <c r="K71">
-        <v>65.7</v>
-      </c>
-      <c r="L71">
-        <v>7.86</v>
-      </c>
-      <c r="M71">
-        <v>155</v>
-      </c>
-      <c r="N71">
-        <v>1193.78</v>
-      </c>
-      <c r="O71">
-        <v>78</v>
-      </c>
-      <c r="P71">
-        <v>78.8</v>
-      </c>
-      <c r="Q71">
-        <v>7.7</v>
-      </c>
-      <c r="R71">
-        <v>254</v>
-      </c>
-      <c r="S71">
-        <v>4497.84</v>
-      </c>
-      <c r="T71">
-        <v>78</v>
-      </c>
-      <c r="U71">
-        <v>78.8</v>
-      </c>
-      <c r="V71">
-        <v>17.71</v>
-      </c>
-      <c r="W71">
-        <v>44.53</v>
-      </c>
-      <c r="X71">
-        <v>2.51</v>
-      </c>
-      <c r="Y71">
-        <v>4.91</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25">
-      <c r="A72" t="s">
-        <v>40</v>
-      </c>
-      <c r="B72" t="s">
-        <v>41</v>
-      </c>
-      <c r="C72" t="s">
-        <v>49</v>
-      </c>
-      <c r="D72">
-        <v>90</v>
-      </c>
-      <c r="E72">
-        <v>95</v>
-      </c>
-      <c r="F72">
-        <v>96</v>
-      </c>
-      <c r="G72">
-        <v>792.16</v>
-      </c>
-      <c r="H72">
-        <v>70</v>
-      </c>
-      <c r="I72">
-        <v>3813.18</v>
-      </c>
-      <c r="J72">
-        <v>46</v>
-      </c>
-      <c r="K72">
-        <v>51.1</v>
-      </c>
-      <c r="L72">
-        <v>54.47</v>
-      </c>
-      <c r="M72">
-        <v>79</v>
-      </c>
-      <c r="N72">
-        <v>4117.48</v>
-      </c>
-      <c r="O72">
-        <v>48</v>
-      </c>
-      <c r="P72">
-        <v>53.3</v>
-      </c>
-      <c r="Q72">
-        <v>52.12</v>
-      </c>
-      <c r="R72">
-        <v>135</v>
-      </c>
-      <c r="S72">
-        <v>5154.1</v>
-      </c>
-      <c r="T72">
-        <v>60</v>
-      </c>
-      <c r="U72">
-        <v>66.7</v>
-      </c>
-      <c r="V72">
-        <v>38.18</v>
-      </c>
-      <c r="W72">
-        <v>54.25</v>
-      </c>
-      <c r="X72">
-        <v>1.42</v>
-      </c>
-      <c r="Y72">
-        <v>6.51</v>
-      </c>
-    </row>
-    <row r="73" spans="1:25">
-      <c r="A73" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" t="s">
-        <v>41</v>
-      </c>
-      <c r="C73" t="s">
-        <v>56</v>
-      </c>
-      <c r="D73">
-        <v>36</v>
-      </c>
-      <c r="E73">
-        <v>36</v>
-      </c>
-      <c r="F73">
-        <v>36</v>
-      </c>
-      <c r="G73">
-        <v>235.08</v>
-      </c>
-      <c r="H73">
-        <v>18</v>
-      </c>
-      <c r="I73">
-        <v>55.21</v>
-      </c>
-      <c r="J73">
-        <v>11</v>
-      </c>
-      <c r="K73">
-        <v>30.6</v>
-      </c>
-      <c r="L73">
-        <v>3.07</v>
-      </c>
-      <c r="M73">
-        <v>22</v>
-      </c>
-      <c r="N73">
-        <v>113.1</v>
-      </c>
-      <c r="O73">
-        <v>14</v>
-      </c>
-      <c r="P73">
-        <v>38.9</v>
-      </c>
-      <c r="Q73">
-        <v>5.14</v>
-      </c>
-      <c r="R73">
-        <v>35</v>
-      </c>
-      <c r="S73">
-        <v>168.08</v>
-      </c>
-      <c r="T73">
-        <v>18</v>
-      </c>
-      <c r="U73">
-        <v>50</v>
-      </c>
-      <c r="V73">
-        <v>4.8</v>
-      </c>
-      <c r="W73">
-        <v>4.67</v>
-      </c>
-      <c r="X73">
-        <v>0.97</v>
-      </c>
-      <c r="Y73">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="74" spans="1:25">
-      <c r="A74" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" t="s">
-        <v>41</v>
-      </c>
-      <c r="C74" t="s">
-        <v>57</v>
-      </c>
-      <c r="D74">
-        <v>128</v>
-      </c>
-      <c r="E74">
-        <v>132</v>
-      </c>
-      <c r="F74">
-        <v>132</v>
-      </c>
-      <c r="G74">
-        <v>869.59</v>
-      </c>
-      <c r="H74">
-        <v>98</v>
-      </c>
-      <c r="I74">
-        <v>2277.53</v>
-      </c>
-      <c r="J74">
-        <v>52</v>
-      </c>
-      <c r="K74">
-        <v>40.6</v>
-      </c>
-      <c r="L74">
-        <v>23.24</v>
-      </c>
-      <c r="M74">
-        <v>241</v>
-      </c>
-      <c r="N74">
-        <v>3424.77</v>
-      </c>
-      <c r="O74">
-        <v>93</v>
-      </c>
-      <c r="P74">
-        <v>72.7</v>
-      </c>
-      <c r="Q74">
-        <v>14.21</v>
-      </c>
-      <c r="R74">
-        <v>245</v>
-      </c>
-      <c r="S74">
-        <v>3444.76</v>
-      </c>
-      <c r="T74">
-        <v>94</v>
-      </c>
-      <c r="U74">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="V74">
-        <v>14.06</v>
-      </c>
-      <c r="W74">
-        <v>26.1</v>
-      </c>
-      <c r="X74">
-        <v>1.86</v>
-      </c>
-      <c r="Y74">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="75" spans="1:25">
-      <c r="A75" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" t="s">
-        <v>42</v>
-      </c>
-      <c r="D75">
-        <v>253</v>
-      </c>
-      <c r="E75">
-        <v>259</v>
-      </c>
-      <c r="F75">
-        <v>259</v>
-      </c>
-      <c r="G75">
-        <v>1691.27</v>
-      </c>
-      <c r="H75">
-        <v>119</v>
-      </c>
-      <c r="I75">
-        <v>369.94</v>
-      </c>
-      <c r="J75">
-        <v>91</v>
-      </c>
-      <c r="K75">
-        <v>36</v>
-      </c>
-      <c r="L75">
-        <v>3.11</v>
-      </c>
-      <c r="M75">
-        <v>119</v>
-      </c>
-      <c r="N75">
-        <v>369.94</v>
-      </c>
-      <c r="O75">
-        <v>91</v>
-      </c>
-      <c r="P75">
-        <v>36</v>
-      </c>
-      <c r="Q75">
-        <v>3.11</v>
-      </c>
-      <c r="R75">
-        <v>119</v>
-      </c>
-      <c r="S75">
-        <v>369.94</v>
-      </c>
-      <c r="T75">
-        <v>91</v>
-      </c>
-      <c r="U75">
-        <v>36</v>
-      </c>
-      <c r="V75">
-        <v>3.11</v>
-      </c>
-      <c r="W75">
-        <v>1.43</v>
-      </c>
-      <c r="X75">
-        <v>0.46</v>
-      </c>
-      <c r="Y75">
         <v>0.22</v>
       </c>
     </row>

--- a/product_monthly.xlsx
+++ b/product_monthly.xlsx
@@ -2052,7 +2052,7 @@
         <v>13.04</v>
       </c>
       <c r="R20">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="S20">
         <v>32246.22</v>
@@ -2064,7 +2064,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V20">
-        <v>16.21</v>
+        <v>16.22</v>
       </c>
       <c r="W20">
         <v>47.14</v>
@@ -2129,7 +2129,7 @@
         <v>7.09</v>
       </c>
       <c r="R21">
-        <v>5429</v>
+        <v>5428</v>
       </c>
       <c r="S21">
         <v>37630.23</v>
@@ -2206,7 +2206,7 @@
         <v>4.59</v>
       </c>
       <c r="R22">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="S22">
         <v>23668.07</v>
@@ -2218,7 +2218,7 @@
         <v>48.4</v>
       </c>
       <c r="V22">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="W22">
         <v>10.79</v>
@@ -2253,49 +2253,49 @@
         <v>7754.45</v>
       </c>
       <c r="H23">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="I23">
-        <v>32899.95</v>
+        <v>32784</v>
       </c>
       <c r="J23">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K23">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="L23">
-        <v>39.21</v>
+        <v>39.22</v>
       </c>
       <c r="M23">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="N23">
-        <v>41844.01</v>
+        <v>41728.06</v>
       </c>
       <c r="O23">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="P23">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="Q23">
-        <v>32.9</v>
+        <v>32.88</v>
       </c>
       <c r="R23">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="S23">
         <v>69664.8</v>
       </c>
       <c r="T23">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="U23">
-        <v>64.3</v>
+        <v>64.2</v>
       </c>
       <c r="V23">
-        <v>35.43</v>
+        <v>35.47</v>
       </c>
       <c r="W23">
         <v>70.94</v>
@@ -2360,7 +2360,7 @@
         <v>7.47</v>
       </c>
       <c r="R24">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="S24">
         <v>5077.68</v>
@@ -2372,7 +2372,7 @@
         <v>77.09999999999999</v>
       </c>
       <c r="V24">
-        <v>7.39</v>
+        <v>7.4</v>
       </c>
       <c r="W24">
         <v>13.91</v>
@@ -2653,7 +2653,7 @@
         <v>16.99</v>
       </c>
       <c r="R28">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S28">
         <v>5133.76</v>
@@ -2665,13 +2665,13 @@
         <v>57</v>
       </c>
       <c r="V28">
-        <v>20.54</v>
+        <v>20.62</v>
       </c>
       <c r="W28">
         <v>44.26</v>
       </c>
       <c r="X28">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Y28">
         <v>7.8</v>
@@ -3038,7 +3038,7 @@
         <v>57.53</v>
       </c>
       <c r="R33">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="S33">
         <v>63974.41</v>
@@ -3050,7 +3050,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V33">
-        <v>53.49</v>
+        <v>53.54</v>
       </c>
       <c r="W33">
         <v>153.42</v>
@@ -3085,10 +3085,10 @@
         <v>3530.64</v>
       </c>
       <c r="H34">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I34">
-        <v>25290.43</v>
+        <v>25250.46</v>
       </c>
       <c r="J34">
         <v>286</v>
@@ -3097,10 +3097,10 @@
         <v>45.9</v>
       </c>
       <c r="L34">
-        <v>49.4</v>
+        <v>49.41</v>
       </c>
       <c r="M34">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N34">
         <v>35867.09</v>
@@ -3112,7 +3112,7 @@
         <v>57.1</v>
       </c>
       <c r="Q34">
-        <v>45.17</v>
+        <v>45.12</v>
       </c>
       <c r="R34">
         <v>1226</v>
@@ -3162,10 +3162,10 @@
         <v>1923.24</v>
       </c>
       <c r="H35">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I35">
-        <v>18001.66</v>
+        <v>17917.62</v>
       </c>
       <c r="J35">
         <v>175</v>
@@ -3174,10 +3174,10 @@
         <v>52.7</v>
       </c>
       <c r="L35">
-        <v>44.78</v>
+        <v>44.79</v>
       </c>
       <c r="M35">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="N35">
         <v>20219.27</v>
@@ -3189,10 +3189,10 @@
         <v>73.8</v>
       </c>
       <c r="Q35">
-        <v>33.87</v>
+        <v>33.92</v>
       </c>
       <c r="R35">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="S35">
         <v>20849</v>
@@ -3204,13 +3204,13 @@
         <v>74.7</v>
       </c>
       <c r="V35">
-        <v>31.88</v>
+        <v>31.93</v>
       </c>
       <c r="W35">
         <v>61.14</v>
       </c>
       <c r="X35">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Y35">
         <v>10.84</v>
@@ -3393,7 +3393,7 @@
         <v>4637.49</v>
       </c>
       <c r="H38">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I38">
         <v>3203.56</v>
@@ -3405,10 +3405,10 @@
         <v>44.6</v>
       </c>
       <c r="L38">
-        <v>9.92</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M38">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N38">
         <v>17344.18</v>
@@ -3420,10 +3420,10 @@
         <v>55.2</v>
       </c>
       <c r="Q38">
-        <v>35.11</v>
+        <v>35.04</v>
       </c>
       <c r="R38">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="S38">
         <v>19052.38</v>
@@ -3435,13 +3435,13 @@
         <v>57.4</v>
       </c>
       <c r="V38">
-        <v>30.63</v>
+        <v>30.58</v>
       </c>
       <c r="W38">
         <v>36.85</v>
       </c>
       <c r="X38">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Y38">
         <v>4.11</v>
@@ -4370,19 +4370,19 @@
         <v>0</v>
       </c>
       <c r="M51">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N51">
-        <v>36.08</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P51">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q51">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R51">
         <v>17</v>
@@ -5608,7 +5608,7 @@
         <v>6</v>
       </c>
       <c r="R67">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S67">
         <v>187.07</v>
@@ -5620,13 +5620,13 @@
         <v>44.4</v>
       </c>
       <c r="V67">
-        <v>5.34</v>
+        <v>5.2</v>
       </c>
       <c r="W67">
         <v>5.2</v>
       </c>
       <c r="X67">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="Y67">
         <v>0.8</v>

--- a/product_monthly.xlsx
+++ b/product_monthly.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="58">
   <si>
     <t>product</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>Turmeric Curcumin</t>
+  </si>
+  <si>
+    <t>Turmeric Ginger</t>
   </si>
   <si>
     <t>All segments</t>
@@ -542,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y69"/>
+  <dimension ref="A1:Y80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -627,10 +630,10 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>615</v>
@@ -704,10 +707,10 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -781,10 +784,10 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>45</v>
@@ -858,10 +861,10 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5">
         <v>20</v>
@@ -935,10 +938,10 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -1012,10 +1015,10 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1089,10 +1092,10 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1166,10 +1169,10 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1234,10 +1237,10 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -1311,10 +1314,10 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D11">
         <v>41</v>
@@ -1388,10 +1391,10 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12">
         <v>432</v>
@@ -1465,10 +1468,10 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13">
         <v>568</v>
@@ -1542,10 +1545,10 @@
         <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14">
         <v>629</v>
@@ -1619,10 +1622,10 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15">
         <v>429</v>
@@ -1696,10 +1699,10 @@
         <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16">
         <v>733</v>
@@ -1773,10 +1776,10 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17">
         <v>679</v>
@@ -1850,10 +1853,10 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18">
         <v>1448</v>
@@ -1927,10 +1930,10 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D19">
         <v>958</v>
@@ -2004,10 +2007,10 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D20">
         <v>661</v>
@@ -2081,10 +2084,10 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D21">
         <v>3197</v>
@@ -2158,10 +2161,10 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22">
         <v>2077</v>
@@ -2235,10 +2238,10 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D23">
         <v>904</v>
@@ -2312,10 +2315,10 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D24">
         <v>332</v>
@@ -2389,10 +2392,10 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D25">
         <v>653</v>
@@ -2466,10 +2469,10 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D26">
         <v>17</v>
@@ -2537,10 +2540,10 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2605,10 +2608,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D28">
         <v>114</v>
@@ -2682,10 +2685,10 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D29">
         <v>58</v>
@@ -2759,10 +2762,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30">
         <v>28</v>
@@ -2836,10 +2839,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -2913,10 +2916,10 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D32">
         <v>427</v>
@@ -2990,10 +2993,10 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D33">
         <v>413</v>
@@ -3067,10 +3070,10 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D34">
         <v>623</v>
@@ -3144,10 +3147,10 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D35">
         <v>332</v>
@@ -3221,10 +3224,10 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D36">
         <v>332</v>
@@ -3298,10 +3301,10 @@
         <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D37">
         <v>30</v>
@@ -3375,10 +3378,10 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D38">
         <v>516</v>
@@ -3452,10 +3455,10 @@
         <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>16</v>
@@ -3526,10 +3529,10 @@
         <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D40">
         <v>313</v>
@@ -3603,10 +3606,10 @@
         <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D41">
         <v>14</v>
@@ -3677,10 +3680,10 @@
         <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D42">
         <v>69</v>
@@ -3754,10 +3757,10 @@
         <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D43">
         <v>127</v>
@@ -3831,10 +3834,10 @@
         <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -3899,10 +3902,10 @@
         <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D45">
         <v>31</v>
@@ -3976,10 +3979,10 @@
         <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D46">
         <v>8</v>
@@ -4053,10 +4056,10 @@
         <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D47">
         <v>8</v>
@@ -4130,10 +4133,10 @@
         <v>34</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -4195,10 +4198,10 @@
         <v>34</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D49">
         <v>18</v>
@@ -4266,10 +4269,10 @@
         <v>34</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D50">
         <v>10</v>
@@ -4340,10 +4343,10 @@
         <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D51">
         <v>24</v>
@@ -4411,10 +4414,10 @@
         <v>35</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C52" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D52">
         <v>15</v>
@@ -4485,10 +4488,10 @@
         <v>36</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D53">
         <v>157</v>
@@ -4562,10 +4565,10 @@
         <v>36</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C54" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D54">
         <v>466</v>
@@ -4639,10 +4642,10 @@
         <v>37</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C55" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D55">
         <v>61</v>
@@ -4716,10 +4719,10 @@
         <v>37</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C56" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D56">
         <v>143</v>
@@ -4793,10 +4796,10 @@
         <v>37</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C57" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D57">
         <v>73</v>
@@ -4870,10 +4873,10 @@
         <v>37</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C58" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D58">
         <v>29</v>
@@ -4947,10 +4950,10 @@
         <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C59" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D59">
         <v>7</v>
@@ -5021,10 +5024,10 @@
         <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C60" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D60">
         <v>55</v>
@@ -5098,10 +5101,10 @@
         <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D61">
         <v>279</v>
@@ -5175,10 +5178,10 @@
         <v>39</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D62">
         <v>114</v>
@@ -5252,10 +5255,10 @@
         <v>39</v>
       </c>
       <c r="B63" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C63" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D63">
         <v>11</v>
@@ -5329,10 +5332,10 @@
         <v>39</v>
       </c>
       <c r="B64" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C64" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D64">
         <v>19</v>
@@ -5406,10 +5409,10 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C65" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D65">
         <v>99</v>
@@ -5483,10 +5486,10 @@
         <v>39</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D66">
         <v>90</v>
@@ -5560,10 +5563,10 @@
         <v>39</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C67" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D67">
         <v>36</v>
@@ -5637,10 +5640,10 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C68" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D68">
         <v>128</v>
@@ -5714,10 +5717,10 @@
         <v>39</v>
       </c>
       <c r="B69" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C69" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D69">
         <v>251</v>
@@ -5784,6 +5787,847 @@
       </c>
       <c r="Y69">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25">
+      <c r="A70" t="s">
+        <v>40</v>
+      </c>
+      <c r="B70" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" t="s">
+        <v>52</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>6.68</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>1</v>
+      </c>
+      <c r="P70">
+        <v>100</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>1</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>1</v>
+      </c>
+      <c r="U70">
+        <v>100</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>1</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25">
+      <c r="A71" t="s">
+        <v>40</v>
+      </c>
+      <c r="B71" t="s">
+        <v>41</v>
+      </c>
+      <c r="C71" t="s">
+        <v>53</v>
+      </c>
+      <c r="D71">
+        <v>80</v>
+      </c>
+      <c r="E71">
+        <v>81</v>
+      </c>
+      <c r="F71">
+        <v>81</v>
+      </c>
+      <c r="G71">
+        <v>541.08</v>
+      </c>
+      <c r="H71">
+        <v>125</v>
+      </c>
+      <c r="I71">
+        <v>3354.03</v>
+      </c>
+      <c r="J71">
+        <v>67</v>
+      </c>
+      <c r="K71">
+        <v>83.8</v>
+      </c>
+      <c r="L71">
+        <v>26.83</v>
+      </c>
+      <c r="M71">
+        <v>140</v>
+      </c>
+      <c r="N71">
+        <v>3369.01</v>
+      </c>
+      <c r="O71">
+        <v>69</v>
+      </c>
+      <c r="P71">
+        <v>86.2</v>
+      </c>
+      <c r="Q71">
+        <v>24.06</v>
+      </c>
+      <c r="R71">
+        <v>176</v>
+      </c>
+      <c r="S71">
+        <v>3533</v>
+      </c>
+      <c r="T71">
+        <v>69</v>
+      </c>
+      <c r="U71">
+        <v>86.2</v>
+      </c>
+      <c r="V71">
+        <v>20.07</v>
+      </c>
+      <c r="W71">
+        <v>43.62</v>
+      </c>
+      <c r="X71">
+        <v>2.17</v>
+      </c>
+      <c r="Y71">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25">
+      <c r="A72" t="s">
+        <v>40</v>
+      </c>
+      <c r="B72" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" t="s">
+        <v>54</v>
+      </c>
+      <c r="D72">
+        <v>124</v>
+      </c>
+      <c r="E72">
+        <v>125</v>
+      </c>
+      <c r="F72">
+        <v>125</v>
+      </c>
+      <c r="G72">
+        <v>835</v>
+      </c>
+      <c r="H72">
+        <v>90</v>
+      </c>
+      <c r="I72">
+        <v>241.54</v>
+      </c>
+      <c r="J72">
+        <v>56</v>
+      </c>
+      <c r="K72">
+        <v>45.2</v>
+      </c>
+      <c r="L72">
+        <v>2.68</v>
+      </c>
+      <c r="M72">
+        <v>194</v>
+      </c>
+      <c r="N72">
+        <v>365.69</v>
+      </c>
+      <c r="O72">
+        <v>103</v>
+      </c>
+      <c r="P72">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="Q72">
+        <v>1.89</v>
+      </c>
+      <c r="R72">
+        <v>269</v>
+      </c>
+      <c r="S72">
+        <v>435.55</v>
+      </c>
+      <c r="T72">
+        <v>104</v>
+      </c>
+      <c r="U72">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="V72">
+        <v>1.62</v>
+      </c>
+      <c r="W72">
+        <v>3.48</v>
+      </c>
+      <c r="X72">
+        <v>2.15</v>
+      </c>
+      <c r="Y72">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25">
+      <c r="A73" t="s">
+        <v>40</v>
+      </c>
+      <c r="B73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" t="s">
+        <v>55</v>
+      </c>
+      <c r="D73">
+        <v>95</v>
+      </c>
+      <c r="E73">
+        <v>97</v>
+      </c>
+      <c r="F73">
+        <v>97</v>
+      </c>
+      <c r="G73">
+        <v>647.96</v>
+      </c>
+      <c r="H73">
+        <v>146</v>
+      </c>
+      <c r="I73">
+        <v>611.8200000000001</v>
+      </c>
+      <c r="J73">
+        <v>74</v>
+      </c>
+      <c r="K73">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="L73">
+        <v>4.19</v>
+      </c>
+      <c r="M73">
+        <v>206</v>
+      </c>
+      <c r="N73">
+        <v>738.9</v>
+      </c>
+      <c r="O73">
+        <v>86</v>
+      </c>
+      <c r="P73">
+        <v>90.5</v>
+      </c>
+      <c r="Q73">
+        <v>3.59</v>
+      </c>
+      <c r="R73">
+        <v>251</v>
+      </c>
+      <c r="S73">
+        <v>839.27</v>
+      </c>
+      <c r="T73">
+        <v>86</v>
+      </c>
+      <c r="U73">
+        <v>90.5</v>
+      </c>
+      <c r="V73">
+        <v>3.34</v>
+      </c>
+      <c r="W73">
+        <v>8.65</v>
+      </c>
+      <c r="X73">
+        <v>2.59</v>
+      </c>
+      <c r="Y73">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25">
+      <c r="A74" t="s">
+        <v>40</v>
+      </c>
+      <c r="B74" t="s">
+        <v>41</v>
+      </c>
+      <c r="C74" t="s">
+        <v>43</v>
+      </c>
+      <c r="D74">
+        <v>188</v>
+      </c>
+      <c r="E74">
+        <v>195</v>
+      </c>
+      <c r="F74">
+        <v>195</v>
+      </c>
+      <c r="G74">
+        <v>1302.6</v>
+      </c>
+      <c r="H74">
+        <v>139</v>
+      </c>
+      <c r="I74">
+        <v>54.37</v>
+      </c>
+      <c r="J74">
+        <v>86</v>
+      </c>
+      <c r="K74">
+        <v>45.7</v>
+      </c>
+      <c r="L74">
+        <v>0.39</v>
+      </c>
+      <c r="M74">
+        <v>231</v>
+      </c>
+      <c r="N74">
+        <v>369.15</v>
+      </c>
+      <c r="O74">
+        <v>130</v>
+      </c>
+      <c r="P74">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="Q74">
+        <v>1.6</v>
+      </c>
+      <c r="R74">
+        <v>275</v>
+      </c>
+      <c r="S74">
+        <v>404.4</v>
+      </c>
+      <c r="T74">
+        <v>132</v>
+      </c>
+      <c r="U74">
+        <v>70.2</v>
+      </c>
+      <c r="V74">
+        <v>1.47</v>
+      </c>
+      <c r="W74">
+        <v>2.07</v>
+      </c>
+      <c r="X74">
+        <v>1.41</v>
+      </c>
+      <c r="Y74">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25">
+      <c r="A75" t="s">
+        <v>40</v>
+      </c>
+      <c r="B75" t="s">
+        <v>41</v>
+      </c>
+      <c r="C75" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75">
+        <v>485</v>
+      </c>
+      <c r="E75">
+        <v>486</v>
+      </c>
+      <c r="F75">
+        <v>486</v>
+      </c>
+      <c r="G75">
+        <v>3246.48</v>
+      </c>
+      <c r="H75">
+        <v>400</v>
+      </c>
+      <c r="I75">
+        <v>415.33</v>
+      </c>
+      <c r="J75">
+        <v>270</v>
+      </c>
+      <c r="K75">
+        <v>55.7</v>
+      </c>
+      <c r="L75">
+        <v>1.04</v>
+      </c>
+      <c r="M75">
+        <v>558</v>
+      </c>
+      <c r="N75">
+        <v>415.33</v>
+      </c>
+      <c r="O75">
+        <v>339</v>
+      </c>
+      <c r="P75">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="Q75">
+        <v>0.74</v>
+      </c>
+      <c r="R75">
+        <v>633</v>
+      </c>
+      <c r="S75">
+        <v>483.73</v>
+      </c>
+      <c r="T75">
+        <v>347</v>
+      </c>
+      <c r="U75">
+        <v>71.5</v>
+      </c>
+      <c r="V75">
+        <v>0.76</v>
+      </c>
+      <c r="W75">
+        <v>1</v>
+      </c>
+      <c r="X75">
+        <v>1.3</v>
+      </c>
+      <c r="Y75">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25">
+      <c r="A76" t="s">
+        <v>40</v>
+      </c>
+      <c r="B76" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76">
+        <v>169</v>
+      </c>
+      <c r="E76">
+        <v>169</v>
+      </c>
+      <c r="F76">
+        <v>169</v>
+      </c>
+      <c r="G76">
+        <v>1145.04</v>
+      </c>
+      <c r="H76">
+        <v>294</v>
+      </c>
+      <c r="I76">
+        <v>29.83</v>
+      </c>
+      <c r="J76">
+        <v>131</v>
+      </c>
+      <c r="K76">
+        <v>77.5</v>
+      </c>
+      <c r="L76">
+        <v>0.1</v>
+      </c>
+      <c r="M76">
+        <v>320</v>
+      </c>
+      <c r="N76">
+        <v>69.73999999999999</v>
+      </c>
+      <c r="O76">
+        <v>136</v>
+      </c>
+      <c r="P76">
+        <v>80.5</v>
+      </c>
+      <c r="Q76">
+        <v>0.22</v>
+      </c>
+      <c r="R76">
+        <v>383</v>
+      </c>
+      <c r="S76">
+        <v>89.72</v>
+      </c>
+      <c r="T76">
+        <v>138</v>
+      </c>
+      <c r="U76">
+        <v>81.7</v>
+      </c>
+      <c r="V76">
+        <v>0.23</v>
+      </c>
+      <c r="W76">
+        <v>0.53</v>
+      </c>
+      <c r="X76">
+        <v>2.27</v>
+      </c>
+      <c r="Y76">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25">
+      <c r="A77" t="s">
+        <v>40</v>
+      </c>
+      <c r="B77" t="s">
+        <v>41</v>
+      </c>
+      <c r="C77" t="s">
+        <v>46</v>
+      </c>
+      <c r="D77">
+        <v>12</v>
+      </c>
+      <c r="E77">
+        <v>12</v>
+      </c>
+      <c r="F77">
+        <v>12</v>
+      </c>
+      <c r="G77">
+        <v>116.43</v>
+      </c>
+      <c r="H77">
+        <v>17</v>
+      </c>
+      <c r="I77">
+        <v>47.89</v>
+      </c>
+      <c r="J77">
+        <v>4</v>
+      </c>
+      <c r="K77">
+        <v>33.3</v>
+      </c>
+      <c r="L77">
+        <v>2.82</v>
+      </c>
+      <c r="M77">
+        <v>23</v>
+      </c>
+      <c r="N77">
+        <v>47.89</v>
+      </c>
+      <c r="O77">
+        <v>8</v>
+      </c>
+      <c r="P77">
+        <v>66.7</v>
+      </c>
+      <c r="Q77">
+        <v>2.08</v>
+      </c>
+      <c r="R77">
+        <v>23</v>
+      </c>
+      <c r="S77">
+        <v>47.89</v>
+      </c>
+      <c r="T77">
+        <v>8</v>
+      </c>
+      <c r="U77">
+        <v>66.7</v>
+      </c>
+      <c r="V77">
+        <v>2.08</v>
+      </c>
+      <c r="W77">
+        <v>3.99</v>
+      </c>
+      <c r="X77">
+        <v>1.92</v>
+      </c>
+      <c r="Y77">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25">
+      <c r="A78" t="s">
+        <v>40</v>
+      </c>
+      <c r="B78" t="s">
+        <v>41</v>
+      </c>
+      <c r="C78" t="s">
+        <v>47</v>
+      </c>
+      <c r="D78">
+        <v>8</v>
+      </c>
+      <c r="E78">
+        <v>9</v>
+      </c>
+      <c r="F78">
+        <v>9</v>
+      </c>
+      <c r="G78">
+        <v>80.27</v>
+      </c>
+      <c r="H78">
+        <v>5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2</v>
+      </c>
+      <c r="K78">
+        <v>25</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>5</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>2</v>
+      </c>
+      <c r="P78">
+        <v>25</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>5</v>
+      </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>2</v>
+      </c>
+      <c r="U78">
+        <v>25</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25">
+      <c r="A79" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C79" t="s">
+        <v>57</v>
+      </c>
+      <c r="D79">
+        <v>8</v>
+      </c>
+      <c r="E79">
+        <v>8</v>
+      </c>
+      <c r="F79">
+        <v>8</v>
+      </c>
+      <c r="G79">
+        <v>53.44</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>6</v>
+      </c>
+      <c r="N79">
+        <v>14.29</v>
+      </c>
+      <c r="O79">
+        <v>4</v>
+      </c>
+      <c r="P79">
+        <v>50</v>
+      </c>
+      <c r="Q79">
+        <v>2.38</v>
+      </c>
+      <c r="R79">
+        <v>6</v>
+      </c>
+      <c r="S79">
+        <v>14.29</v>
+      </c>
+      <c r="T79">
+        <v>4</v>
+      </c>
+      <c r="U79">
+        <v>50</v>
+      </c>
+      <c r="V79">
+        <v>2.38</v>
+      </c>
+      <c r="W79">
+        <v>1.79</v>
+      </c>
+      <c r="X79">
+        <v>0.75</v>
+      </c>
+      <c r="Y79">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25">
+      <c r="A80" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" t="s">
+        <v>41</v>
+      </c>
+      <c r="C80" t="s">
+        <v>42</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80">
+        <v>4</v>
+      </c>
+      <c r="F80">
+        <v>4</v>
+      </c>
+      <c r="G80">
+        <v>26.72</v>
+      </c>
+      <c r="H80">
+        <v>4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3</v>
+      </c>
+      <c r="K80">
+        <v>75</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>4</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>3</v>
+      </c>
+      <c r="P80">
+        <v>75</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>4</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>3</v>
+      </c>
+      <c r="U80">
+        <v>75</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80">
+        <v>1</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/product_monthly.xlsx
+++ b/product_monthly.xlsx
@@ -651,7 +651,7 @@
         <v>67</v>
       </c>
       <c r="I2">
-        <v>107.47</v>
+        <v>107.64</v>
       </c>
       <c r="J2">
         <v>50</v>
@@ -660,13 +660,13 @@
         <v>8.1</v>
       </c>
       <c r="L2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M2">
         <v>67</v>
       </c>
       <c r="N2">
-        <v>107.47</v>
+        <v>107.64</v>
       </c>
       <c r="O2">
         <v>50</v>
@@ -675,13 +675,13 @@
         <v>8.1</v>
       </c>
       <c r="Q2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R2">
         <v>67</v>
       </c>
       <c r="S2">
-        <v>107.47</v>
+        <v>107.64</v>
       </c>
       <c r="T2">
         <v>50</v>
@@ -690,7 +690,7 @@
         <v>8.1</v>
       </c>
       <c r="V2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W2">
         <v>0.17</v>
@@ -2135,7 +2135,7 @@
         <v>5428</v>
       </c>
       <c r="S21">
-        <v>37630.23</v>
+        <v>37630.51</v>
       </c>
       <c r="T21">
         <v>2302</v>
@@ -2209,10 +2209,10 @@
         <v>4.59</v>
       </c>
       <c r="R22">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="S22">
-        <v>23668.07</v>
+        <v>23669.5</v>
       </c>
       <c r="T22">
         <v>1006</v>
@@ -2221,7 +2221,7 @@
         <v>48.4</v>
       </c>
       <c r="V22">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="W22">
         <v>10.79</v>
@@ -2259,7 +2259,7 @@
         <v>836</v>
       </c>
       <c r="I23">
-        <v>32784</v>
+        <v>32784.12</v>
       </c>
       <c r="J23">
         <v>435</v>
@@ -2274,7 +2274,7 @@
         <v>1269</v>
       </c>
       <c r="N23">
-        <v>41728.06</v>
+        <v>41728.18</v>
       </c>
       <c r="O23">
         <v>535</v>
@@ -2289,7 +2289,7 @@
         <v>1964</v>
       </c>
       <c r="S23">
-        <v>69664.8</v>
+        <v>69666.07000000001</v>
       </c>
       <c r="T23">
         <v>580</v>
@@ -2351,7 +2351,7 @@
         <v>663</v>
       </c>
       <c r="N24">
-        <v>4951.87</v>
+        <v>4952.07</v>
       </c>
       <c r="O24">
         <v>256</v>
@@ -2366,7 +2366,7 @@
         <v>686</v>
       </c>
       <c r="S24">
-        <v>5077.68</v>
+        <v>5077.88</v>
       </c>
       <c r="T24">
         <v>256</v>
@@ -2410,55 +2410,55 @@
         <v>4737.03</v>
       </c>
       <c r="H25">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="I25">
-        <v>1884.35</v>
+        <v>1884.99</v>
       </c>
       <c r="J25">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K25">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="L25">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="M25">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N25">
-        <v>1884.35</v>
+        <v>1884.99</v>
       </c>
       <c r="O25">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P25">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="Q25">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="R25">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="S25">
-        <v>1884.35</v>
+        <v>1884.99</v>
       </c>
       <c r="T25">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="U25">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="V25">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="W25">
         <v>2.58</v>
       </c>
       <c r="X25">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="Y25">
         <v>0.4</v>
@@ -2502,7 +2502,7 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>26.97</v>
+        <v>27.05</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -2511,13 +2511,13 @@
         <v>47.1</v>
       </c>
       <c r="Q26">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="R26">
         <v>12</v>
       </c>
       <c r="S26">
-        <v>26.97</v>
+        <v>27.05</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -3091,7 +3091,7 @@
         <v>511</v>
       </c>
       <c r="I34">
-        <v>25250.46</v>
+        <v>25250.81</v>
       </c>
       <c r="J34">
         <v>286</v>
@@ -3106,7 +3106,7 @@
         <v>795</v>
       </c>
       <c r="N34">
-        <v>35867.09</v>
+        <v>35867.44</v>
       </c>
       <c r="O34">
         <v>356</v>
@@ -3121,7 +3121,7 @@
         <v>1226</v>
       </c>
       <c r="S34">
-        <v>44858.95</v>
+        <v>44859.78</v>
       </c>
       <c r="T34">
         <v>374</v>
@@ -3168,7 +3168,7 @@
         <v>400</v>
       </c>
       <c r="I35">
-        <v>17917.62</v>
+        <v>17918.21</v>
       </c>
       <c r="J35">
         <v>175</v>
@@ -3177,13 +3177,13 @@
         <v>52.7</v>
       </c>
       <c r="L35">
-        <v>44.79</v>
+        <v>44.8</v>
       </c>
       <c r="M35">
         <v>596</v>
       </c>
       <c r="N35">
-        <v>20219.27</v>
+        <v>20220.11</v>
       </c>
       <c r="O35">
         <v>245</v>
@@ -3192,13 +3192,13 @@
         <v>73.8</v>
       </c>
       <c r="Q35">
-        <v>33.92</v>
+        <v>33.93</v>
       </c>
       <c r="R35">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="S35">
-        <v>20849</v>
+        <v>20850.49</v>
       </c>
       <c r="T35">
         <v>248</v>
@@ -3207,10 +3207,10 @@
         <v>74.7</v>
       </c>
       <c r="V35">
-        <v>31.93</v>
+        <v>31.98</v>
       </c>
       <c r="W35">
-        <v>61.14</v>
+        <v>61.15</v>
       </c>
       <c r="X35">
         <v>1.91</v>
@@ -3242,52 +3242,52 @@
         <v>1917.6</v>
       </c>
       <c r="H36">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I36">
-        <v>2255.04</v>
+        <v>2256.62</v>
       </c>
       <c r="J36">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K36">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="L36">
-        <v>11.33</v>
+        <v>11.28</v>
       </c>
       <c r="M36">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N36">
-        <v>2255.04</v>
+        <v>2256.62</v>
       </c>
       <c r="O36">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P36">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="Q36">
-        <v>11.33</v>
+        <v>11.28</v>
       </c>
       <c r="R36">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="S36">
-        <v>2255.04</v>
+        <v>2256.62</v>
       </c>
       <c r="T36">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U36">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="V36">
-        <v>11.33</v>
+        <v>11.28</v>
       </c>
       <c r="W36">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
       <c r="X36">
         <v>0.59</v>
@@ -3352,7 +3352,7 @@
         <v>129</v>
       </c>
       <c r="S37">
-        <v>8340.4</v>
+        <v>8340.77</v>
       </c>
       <c r="T37">
         <v>17</v>
@@ -3361,16 +3361,16 @@
         <v>56.7</v>
       </c>
       <c r="V37">
-        <v>64.65000000000001</v>
+        <v>64.66</v>
       </c>
       <c r="W37">
-        <v>278.01</v>
+        <v>278.03</v>
       </c>
       <c r="X37">
         <v>4.3</v>
       </c>
       <c r="Y37">
-        <v>30.99</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3547,52 +3547,52 @@
         <v>2825.55</v>
       </c>
       <c r="H40">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I40">
-        <v>203.09</v>
+        <v>203.36</v>
       </c>
       <c r="J40">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K40">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="L40">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M40">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N40">
-        <v>203.09</v>
+        <v>203.36</v>
       </c>
       <c r="O40">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P40">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="Q40">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R40">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="S40">
-        <v>203.09</v>
+        <v>203.36</v>
       </c>
       <c r="T40">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U40">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="V40">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W40">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="X40">
         <v>0.47</v>
@@ -3716,7 +3716,7 @@
         <v>52</v>
       </c>
       <c r="N42">
-        <v>1093.46</v>
+        <v>1093.54</v>
       </c>
       <c r="O42">
         <v>27</v>
@@ -3731,7 +3731,7 @@
         <v>135</v>
       </c>
       <c r="S42">
-        <v>2734.76</v>
+        <v>2735</v>
       </c>
       <c r="T42">
         <v>37</v>
@@ -3743,7 +3743,7 @@
         <v>20.26</v>
       </c>
       <c r="W42">
-        <v>39.63</v>
+        <v>39.64</v>
       </c>
       <c r="X42">
         <v>1.96</v>
@@ -3793,7 +3793,7 @@
         <v>123</v>
       </c>
       <c r="N43">
-        <v>3563.29</v>
+        <v>3563.34</v>
       </c>
       <c r="O43">
         <v>65</v>
@@ -3808,7 +3808,7 @@
         <v>164</v>
       </c>
       <c r="S43">
-        <v>3852.5</v>
+        <v>3852.55</v>
       </c>
       <c r="T43">
         <v>69</v>
@@ -3820,7 +3820,7 @@
         <v>23.49</v>
       </c>
       <c r="W43">
-        <v>30.33</v>
+        <v>30.34</v>
       </c>
       <c r="X43">
         <v>1.29</v>
@@ -3923,7 +3923,7 @@
         <v>25</v>
       </c>
       <c r="I45">
-        <v>50.07</v>
+        <v>50.12</v>
       </c>
       <c r="J45">
         <v>16</v>
@@ -3938,7 +3938,7 @@
         <v>25</v>
       </c>
       <c r="N45">
-        <v>50.07</v>
+        <v>50.12</v>
       </c>
       <c r="O45">
         <v>16</v>
@@ -3953,7 +3953,7 @@
         <v>25</v>
       </c>
       <c r="S45">
-        <v>50.07</v>
+        <v>50.12</v>
       </c>
       <c r="T45">
         <v>16</v>
@@ -4391,7 +4391,7 @@
         <v>17</v>
       </c>
       <c r="S51">
-        <v>94.11</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="T51">
         <v>10</v>
@@ -4400,10 +4400,10 @@
         <v>41.7</v>
       </c>
       <c r="V51">
-        <v>5.54</v>
+        <v>5.55</v>
       </c>
       <c r="W51">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="X51">
         <v>0.71</v>
@@ -4539,7 +4539,7 @@
         <v>141</v>
       </c>
       <c r="S53">
-        <v>509.15</v>
+        <v>509.21</v>
       </c>
       <c r="T53">
         <v>84</v>
@@ -4583,49 +4583,49 @@
         <v>2974.39</v>
       </c>
       <c r="H54">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I54">
-        <v>209.08</v>
+        <v>209.15</v>
       </c>
       <c r="J54">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K54">
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="L54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="M54">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N54">
-        <v>209.08</v>
+        <v>209.15</v>
       </c>
       <c r="O54">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P54">
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="Q54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="R54">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="S54">
-        <v>209.08</v>
+        <v>209.15</v>
       </c>
       <c r="T54">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="U54">
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="V54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W54">
         <v>0.45</v>
@@ -4693,7 +4693,7 @@
         <v>111</v>
       </c>
       <c r="S55">
-        <v>2669.44</v>
+        <v>2669.56</v>
       </c>
       <c r="T55">
         <v>28</v>
@@ -4755,7 +4755,7 @@
         <v>132</v>
       </c>
       <c r="N56">
-        <v>914.8099999999999</v>
+        <v>914.86</v>
       </c>
       <c r="O56">
         <v>72</v>
@@ -4770,7 +4770,7 @@
         <v>183</v>
       </c>
       <c r="S56">
-        <v>1229.27</v>
+        <v>1229.53</v>
       </c>
       <c r="T56">
         <v>80</v>
@@ -4817,7 +4817,7 @@
         <v>76</v>
       </c>
       <c r="I57">
-        <v>2083.16</v>
+        <v>2083.44</v>
       </c>
       <c r="J57">
         <v>36</v>
@@ -4832,7 +4832,7 @@
         <v>148</v>
       </c>
       <c r="N57">
-        <v>3451.29</v>
+        <v>3452.26</v>
       </c>
       <c r="O57">
         <v>61</v>
@@ -4841,13 +4841,13 @@
         <v>83.59999999999999</v>
       </c>
       <c r="Q57">
-        <v>23.32</v>
+        <v>23.33</v>
       </c>
       <c r="R57">
         <v>158</v>
       </c>
       <c r="S57">
-        <v>3552.83</v>
+        <v>3553.8</v>
       </c>
       <c r="T57">
         <v>61</v>
@@ -4859,13 +4859,13 @@
         <v>22.49</v>
       </c>
       <c r="W57">
-        <v>48.67</v>
+        <v>48.68</v>
       </c>
       <c r="X57">
         <v>2.16</v>
       </c>
       <c r="Y57">
-        <v>10.01</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="58" spans="1:25">
@@ -5676,7 +5676,7 @@
         <v>236</v>
       </c>
       <c r="N68">
-        <v>3422.52</v>
+        <v>3422.78</v>
       </c>
       <c r="O68">
         <v>92</v>
@@ -5691,7 +5691,7 @@
         <v>240</v>
       </c>
       <c r="S68">
-        <v>3442.51</v>
+        <v>3442.77</v>
       </c>
       <c r="T68">
         <v>93</v>
@@ -5738,7 +5738,7 @@
         <v>118</v>
       </c>
       <c r="I69">
-        <v>369.94</v>
+        <v>370.24</v>
       </c>
       <c r="J69">
         <v>90</v>
@@ -5753,7 +5753,7 @@
         <v>118</v>
       </c>
       <c r="N69">
-        <v>369.94</v>
+        <v>370.24</v>
       </c>
       <c r="O69">
         <v>90</v>
@@ -5768,7 +5768,7 @@
         <v>118</v>
       </c>
       <c r="S69">
-        <v>369.94</v>
+        <v>370.24</v>
       </c>
       <c r="T69">
         <v>90</v>

--- a/product_monthly.xlsx
+++ b/product_monthly.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y80"/>
+  <dimension ref="A1:Y87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,80 +556,76 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>683</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>687</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>687</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>4149.48</v>
+        <v>138.92</v>
       </c>
       <c r="H2" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>196.22</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>196.22</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="S2" t="n">
-        <v>196.22</v>
+        <v>42.78</v>
       </c>
       <c r="T2" t="n">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="U2" t="n">
-        <v>9.699999999999999</v>
+        <v>39.1</v>
       </c>
       <c r="V2" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="W2" t="n">
-        <v>0.29</v>
+        <v>1.86</v>
       </c>
       <c r="X2" t="n">
-        <v>0.13</v>
+        <v>0.78</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ashwagandha Capsules</t>
+          <t>Advent Calendar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -639,80 +635,76 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>34.96</v>
+        <v>72.48</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>24.99</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="V3" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.4</v>
+        <v>0.58</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ashwagandha Capsules</t>
+          <t>Advent Calendar</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -722,80 +714,76 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>298.79</v>
+        <v>66.44</v>
       </c>
       <c r="H4" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>94.98</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.79</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>192.61</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.57</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>386.12</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>91.09999999999999</v>
+        <v>27.3</v>
       </c>
       <c r="V4" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>0.45</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ashwagandha Capsules</t>
+          <t>Advent Calendar</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -805,80 +793,76 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>184.99</v>
+        <v>60.4</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>643.77</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>26.82</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>723.1799999999999</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>27.81</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>723.1799999999999</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="V5" t="n">
-        <v>25.83</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>36.16</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ashwagandha Capsules</t>
+          <t>Advent Calendar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -888,80 +872,76 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>46.24</v>
+        <v>48.32</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
-        <v>219.06</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="M6" t="n">
-        <v>8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>219.06</v>
-      </c>
-      <c r="O6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>27.38</v>
-      </c>
-      <c r="R6" t="n">
-        <v>8</v>
-      </c>
-      <c r="S6" t="n">
-        <v>219.06</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
       <c r="U6" t="n">
-        <v>71.40000000000001</v>
+        <v>37.5</v>
       </c>
       <c r="V6" t="n">
-        <v>27.38</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>31.29</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ashwagandha Capsules</t>
+          <t>Advent Calendar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -971,62 +951,58 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>28.7</v>
+        <v>42.28</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>80</v>
+        <v>28.6</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1035,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.4</v>
+        <v>0.29</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1044,7 +1020,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ashwagandha Capsules</t>
+          <t>Advent Calendar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1054,80 +1030,80 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>690</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>694</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>694</v>
       </c>
       <c r="G8" t="n">
-        <v>11.48</v>
+        <v>4191.76</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>196.22</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="K8" t="n">
-        <v>50</v>
+        <v>9.9</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>196.22</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="P8" t="n">
-        <v>50</v>
+        <v>9.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>196.22</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="U8" t="n">
-        <v>50</v>
+        <v>9.9</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>0.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ashwagandha Capsules</t>
+          <t>Advent Calendar</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1137,20 +1113,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>5.74</v>
+        <v>42.28</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1204,7 +1180,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Capsules</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,80 +1190,80 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>415.37</v>
+        <v>34.96</v>
       </c>
       <c r="H10" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2729.59</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>78.59999999999999</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>30.67</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>12152.93</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>81.40000000000001</v>
+        <v>40</v>
       </c>
       <c r="Q10" t="n">
-        <v>117.99</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>388</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>15216.18</v>
+        <v>24.99</v>
       </c>
       <c r="T10" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>82.90000000000001</v>
+        <v>40</v>
       </c>
       <c r="V10" t="n">
-        <v>39.22</v>
+        <v>3.57</v>
       </c>
       <c r="W10" t="n">
-        <v>208.44</v>
+        <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>5.32</v>
+        <v>1.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>36.63</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Capsules</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1297,80 +1273,80 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>45</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>45</v>
+      </c>
+      <c r="G11" t="n">
+        <v>298.79</v>
+      </c>
+      <c r="H11" t="n">
+        <v>53</v>
+      </c>
+      <c r="I11" t="n">
+        <v>94.98</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31</v>
+      </c>
+      <c r="K11" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M11" t="n">
+        <v>75</v>
+      </c>
+      <c r="N11" t="n">
+        <v>192.61</v>
+      </c>
+      <c r="O11" t="n">
+        <v>38</v>
+      </c>
+      <c r="P11" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R11" t="n">
+        <v>90</v>
+      </c>
+      <c r="S11" t="n">
+        <v>386.12</v>
+      </c>
+      <c r="T11" t="n">
         <v>41</v>
       </c>
-      <c r="E11" t="n">
-        <v>42</v>
-      </c>
-      <c r="F11" t="n">
-        <v>42</v>
-      </c>
-      <c r="G11" t="n">
-        <v>242.6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>49</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6899.45</v>
-      </c>
-      <c r="J11" t="n">
-        <v>28</v>
-      </c>
-      <c r="K11" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>140.81</v>
-      </c>
-      <c r="M11" t="n">
-        <v>71</v>
-      </c>
-      <c r="N11" t="n">
-        <v>17624.61</v>
-      </c>
-      <c r="O11" t="n">
-        <v>33</v>
-      </c>
-      <c r="P11" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>248.23</v>
-      </c>
-      <c r="R11" t="n">
-        <v>175</v>
-      </c>
-      <c r="S11" t="n">
-        <v>17857.61</v>
-      </c>
-      <c r="T11" t="n">
-        <v>33</v>
-      </c>
       <c r="U11" t="n">
-        <v>80.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>102.04</v>
+        <v>4.29</v>
       </c>
       <c r="W11" t="n">
-        <v>425.18</v>
+        <v>8.58</v>
       </c>
       <c r="X11" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="n">
-        <v>73.61</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Capsules</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1380,80 +1356,80 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>432</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>441</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>2532.61</v>
+        <v>184.99</v>
       </c>
       <c r="H12" t="n">
-        <v>346</v>
+        <v>24</v>
       </c>
       <c r="I12" t="n">
-        <v>62899.66</v>
+        <v>643.77</v>
       </c>
       <c r="J12" t="n">
-        <v>231</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>53.5</v>
+        <v>55</v>
       </c>
       <c r="L12" t="n">
-        <v>181.79</v>
+        <v>26.82</v>
       </c>
       <c r="M12" t="n">
-        <v>546</v>
+        <v>26</v>
       </c>
       <c r="N12" t="n">
-        <v>69067.03</v>
+        <v>723.1799999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>289</v>
+        <v>13</v>
       </c>
       <c r="P12" t="n">
-        <v>66.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="Q12" t="n">
-        <v>126.5</v>
+        <v>27.81</v>
       </c>
       <c r="R12" t="n">
-        <v>1320</v>
+        <v>28</v>
       </c>
       <c r="S12" t="n">
-        <v>198426.89</v>
+        <v>723.1799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>294</v>
+        <v>13</v>
       </c>
       <c r="U12" t="n">
-        <v>68.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="V12" t="n">
-        <v>150.32</v>
+        <v>25.83</v>
       </c>
       <c r="W12" t="n">
-        <v>449.95</v>
+        <v>36.16</v>
       </c>
       <c r="X12" t="n">
-        <v>2.99</v>
+        <v>1.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>78.34999999999999</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Capsules</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1463,80 +1439,80 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>568</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>581</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>581</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>3323.52</v>
+        <v>46.24</v>
       </c>
       <c r="H13" t="n">
-        <v>575</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>5070.32</v>
+        <v>219.06</v>
       </c>
       <c r="J13" t="n">
-        <v>243</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>42.8</v>
+        <v>28.6</v>
       </c>
       <c r="L13" t="n">
-        <v>8.82</v>
+        <v>73.02</v>
       </c>
       <c r="M13" t="n">
-        <v>966</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>11063.29</v>
+        <v>219.06</v>
       </c>
       <c r="O13" t="n">
-        <v>345</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>60.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.45</v>
+        <v>27.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1652</v>
+        <v>8</v>
       </c>
       <c r="S13" t="n">
-        <v>32925.95</v>
+        <v>219.06</v>
       </c>
       <c r="T13" t="n">
-        <v>353</v>
+        <v>5</v>
       </c>
       <c r="U13" t="n">
-        <v>62.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>19.93</v>
+        <v>27.38</v>
       </c>
       <c r="W13" t="n">
-        <v>56.67</v>
+        <v>31.29</v>
       </c>
       <c r="X13" t="n">
-        <v>2.84</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.91</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Capsules</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1546,80 +1522,80 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>629</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>640</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>640</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>3662.85</v>
+        <v>28.7</v>
       </c>
       <c r="H14" t="n">
-        <v>485</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>11070.71</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>263</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>41.8</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>22.83</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>666</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>12998.81</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>334</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>53.1</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="n">
-        <v>19.52</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1340</v>
+        <v>7</v>
       </c>
       <c r="S14" t="n">
-        <v>56922.42</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>344</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>54.7</v>
+        <v>80</v>
       </c>
       <c r="V14" t="n">
-        <v>42.48</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>88.94</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.09</v>
+        <v>1.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>15.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Capsules</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1629,80 +1605,80 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>429</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>433</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>433</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2484.55</v>
+        <v>11.48</v>
       </c>
       <c r="H15" t="n">
-        <v>418</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>2151.56</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>229</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>53.4</v>
+        <v>50</v>
       </c>
       <c r="L15" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>487</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>2294.51</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>252</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>58.7</v>
+        <v>50</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>713</v>
+        <v>6</v>
       </c>
       <c r="S15" t="n">
-        <v>16978.37</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>257</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>59.9</v>
+        <v>50</v>
       </c>
       <c r="V15" t="n">
-        <v>23.81</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>39.21</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Capsules</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1712,74 +1688,68 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>733</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>743</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>743</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>4234.44</v>
+        <v>5.74</v>
       </c>
       <c r="H16" t="n">
-        <v>522</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>5119.37</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>9.81</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>21935.54</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>31.43</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>937</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>24536.34</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>403</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>55</v>
-      </c>
-      <c r="V16" t="n">
-        <v>26.19</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
-        <v>33.02</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1795,74 +1765,74 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>679</v>
+        <v>70</v>
       </c>
       <c r="E17" t="n">
-        <v>684</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
-        <v>684</v>
+        <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>3912.27</v>
+        <v>415.37</v>
       </c>
       <c r="H17" t="n">
-        <v>690</v>
+        <v>89</v>
       </c>
       <c r="I17" t="n">
-        <v>6534.6</v>
+        <v>2729.59</v>
       </c>
       <c r="J17" t="n">
-        <v>381</v>
+        <v>55</v>
       </c>
       <c r="K17" t="n">
-        <v>56.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>9.470000000000001</v>
+        <v>30.67</v>
       </c>
       <c r="M17" t="n">
-        <v>936</v>
+        <v>103</v>
       </c>
       <c r="N17" t="n">
-        <v>16084.79</v>
+        <v>12152.93</v>
       </c>
       <c r="O17" t="n">
-        <v>467</v>
+        <v>57</v>
       </c>
       <c r="P17" t="n">
-        <v>68.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>17.18</v>
+        <v>117.99</v>
       </c>
       <c r="R17" t="n">
-        <v>1281</v>
+        <v>388</v>
       </c>
       <c r="S17" t="n">
-        <v>29119.55</v>
+        <v>15216.18</v>
       </c>
       <c r="T17" t="n">
-        <v>475</v>
+        <v>58</v>
       </c>
       <c r="U17" t="n">
-        <v>70</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>22.73</v>
+        <v>39.22</v>
       </c>
       <c r="W17" t="n">
-        <v>42.57</v>
+        <v>208.44</v>
       </c>
       <c r="X17" t="n">
-        <v>1.87</v>
+        <v>5.32</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.44</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="18">
@@ -1878,74 +1848,74 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1448</v>
+        <v>41</v>
       </c>
       <c r="E18" t="n">
-        <v>1461</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>1461</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>8323.48</v>
+        <v>242.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1769</v>
+        <v>49</v>
       </c>
       <c r="I18" t="n">
-        <v>73400.73</v>
+        <v>6899.45</v>
       </c>
       <c r="J18" t="n">
-        <v>935</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>64.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="L18" t="n">
-        <v>41.49</v>
+        <v>140.81</v>
       </c>
       <c r="M18" t="n">
-        <v>2730</v>
+        <v>71</v>
       </c>
       <c r="N18" t="n">
-        <v>79348.72</v>
+        <v>17624.61</v>
       </c>
       <c r="O18" t="n">
-        <v>1195</v>
+        <v>33</v>
       </c>
       <c r="P18" t="n">
-        <v>82.5</v>
+        <v>80.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>29.07</v>
+        <v>248.23</v>
       </c>
       <c r="R18" t="n">
-        <v>4035</v>
+        <v>175</v>
       </c>
       <c r="S18" t="n">
-        <v>98287.21000000001</v>
+        <v>17857.61</v>
       </c>
       <c r="T18" t="n">
-        <v>1205</v>
+        <v>33</v>
       </c>
       <c r="U18" t="n">
-        <v>83.2</v>
+        <v>80.5</v>
       </c>
       <c r="V18" t="n">
-        <v>24.36</v>
+        <v>102.04</v>
       </c>
       <c r="W18" t="n">
-        <v>67.27</v>
+        <v>425.18</v>
       </c>
       <c r="X18" t="n">
-        <v>2.76</v>
+        <v>4.17</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.81</v>
+        <v>73.61</v>
       </c>
     </row>
     <row r="19">
@@ -1961,74 +1931,74 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>958</v>
+        <v>432</v>
       </c>
       <c r="E19" t="n">
-        <v>981</v>
+        <v>441</v>
       </c>
       <c r="F19" t="n">
-        <v>981</v>
+        <v>442</v>
       </c>
       <c r="G19" t="n">
-        <v>5585.51</v>
+        <v>2532.61</v>
       </c>
       <c r="H19" t="n">
-        <v>1924</v>
+        <v>346</v>
       </c>
       <c r="I19" t="n">
-        <v>83246.50999999999</v>
+        <v>62899.66</v>
       </c>
       <c r="J19" t="n">
-        <v>757</v>
+        <v>231</v>
       </c>
       <c r="K19" t="n">
-        <v>79</v>
+        <v>53.5</v>
       </c>
       <c r="L19" t="n">
-        <v>43.27</v>
+        <v>181.79</v>
       </c>
       <c r="M19" t="n">
-        <v>2413</v>
+        <v>546</v>
       </c>
       <c r="N19" t="n">
-        <v>91473.21000000001</v>
+        <v>69067.03</v>
       </c>
       <c r="O19" t="n">
-        <v>833</v>
+        <v>289</v>
       </c>
       <c r="P19" t="n">
-        <v>87</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>37.91</v>
+        <v>126.5</v>
       </c>
       <c r="R19" t="n">
-        <v>3098</v>
+        <v>1320</v>
       </c>
       <c r="S19" t="n">
-        <v>98166.2</v>
+        <v>198426.89</v>
       </c>
       <c r="T19" t="n">
-        <v>836</v>
+        <v>294</v>
       </c>
       <c r="U19" t="n">
-        <v>87.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>31.69</v>
+        <v>150.32</v>
       </c>
       <c r="W19" t="n">
-        <v>100.07</v>
+        <v>449.95</v>
       </c>
       <c r="X19" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="Y19" t="n">
-        <v>17.58</v>
+        <v>78.34999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2044,74 +2014,74 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>661</v>
+        <v>568</v>
       </c>
       <c r="E20" t="n">
-        <v>684</v>
+        <v>581</v>
       </c>
       <c r="F20" t="n">
-        <v>684</v>
+        <v>581</v>
       </c>
       <c r="G20" t="n">
-        <v>3891.96</v>
+        <v>3323.52</v>
       </c>
       <c r="H20" t="n">
-        <v>965</v>
+        <v>575</v>
       </c>
       <c r="I20" t="n">
-        <v>14855.14</v>
+        <v>5070.32</v>
       </c>
       <c r="J20" t="n">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="K20" t="n">
-        <v>70.2</v>
+        <v>42.8</v>
       </c>
       <c r="L20" t="n">
-        <v>15.39</v>
+        <v>8.82</v>
       </c>
       <c r="M20" t="n">
-        <v>1484</v>
+        <v>966</v>
       </c>
       <c r="N20" t="n">
-        <v>19351.9</v>
+        <v>11063.29</v>
       </c>
       <c r="O20" t="n">
-        <v>590</v>
+        <v>345</v>
       </c>
       <c r="P20" t="n">
-        <v>89.3</v>
+        <v>60.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.04</v>
+        <v>11.45</v>
       </c>
       <c r="R20" t="n">
-        <v>1987</v>
+        <v>1652</v>
       </c>
       <c r="S20" t="n">
-        <v>32249.45</v>
+        <v>32925.95</v>
       </c>
       <c r="T20" t="n">
-        <v>599</v>
+        <v>353</v>
       </c>
       <c r="U20" t="n">
-        <v>90.59999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="V20" t="n">
-        <v>16.23</v>
+        <v>19.93</v>
       </c>
       <c r="W20" t="n">
-        <v>47.15</v>
+        <v>56.67</v>
       </c>
       <c r="X20" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.289999999999999</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="21">
@@ -2127,74 +2097,74 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3197</v>
+        <v>629</v>
       </c>
       <c r="E21" t="n">
-        <v>3278</v>
+        <v>640</v>
       </c>
       <c r="F21" t="n">
-        <v>3278</v>
+        <v>640</v>
       </c>
       <c r="G21" t="n">
-        <v>18651.82</v>
+        <v>3662.85</v>
       </c>
       <c r="H21" t="n">
-        <v>2840</v>
+        <v>485</v>
       </c>
       <c r="I21" t="n">
-        <v>28289.48</v>
+        <v>11070.71</v>
       </c>
       <c r="J21" t="n">
-        <v>1508</v>
+        <v>263</v>
       </c>
       <c r="K21" t="n">
-        <v>47.2</v>
+        <v>41.8</v>
       </c>
       <c r="L21" t="n">
-        <v>9.960000000000001</v>
+        <v>22.83</v>
       </c>
       <c r="M21" t="n">
-        <v>4959</v>
+        <v>666</v>
       </c>
       <c r="N21" t="n">
-        <v>35202.98</v>
+        <v>12998.81</v>
       </c>
       <c r="O21" t="n">
-        <v>2292</v>
+        <v>334</v>
       </c>
       <c r="P21" t="n">
-        <v>71.7</v>
+        <v>53.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.1</v>
+        <v>19.52</v>
       </c>
       <c r="R21" t="n">
-        <v>5437</v>
+        <v>1340</v>
       </c>
       <c r="S21" t="n">
-        <v>37655.33</v>
+        <v>56922.42</v>
       </c>
       <c r="T21" t="n">
-        <v>2301</v>
+        <v>344</v>
       </c>
       <c r="U21" t="n">
-        <v>72</v>
+        <v>54.7</v>
       </c>
       <c r="V21" t="n">
-        <v>6.93</v>
+        <v>42.48</v>
       </c>
       <c r="W21" t="n">
-        <v>11.49</v>
+        <v>88.94</v>
       </c>
       <c r="X21" t="n">
-        <v>1.66</v>
+        <v>2.09</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.02</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="22">
@@ -2210,74 +2180,74 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2077</v>
+        <v>429</v>
       </c>
       <c r="E22" t="n">
-        <v>2193</v>
+        <v>433</v>
       </c>
       <c r="F22" t="n">
-        <v>2195</v>
+        <v>433</v>
       </c>
       <c r="G22" t="n">
-        <v>12596.48</v>
+        <v>2484.55</v>
       </c>
       <c r="H22" t="n">
-        <v>1539</v>
+        <v>418</v>
       </c>
       <c r="I22" t="n">
-        <v>5951.25</v>
+        <v>2151.56</v>
       </c>
       <c r="J22" t="n">
-        <v>896</v>
+        <v>229</v>
       </c>
       <c r="K22" t="n">
-        <v>43.1</v>
+        <v>53.4</v>
       </c>
       <c r="L22" t="n">
-        <v>3.87</v>
+        <v>5.15</v>
       </c>
       <c r="M22" t="n">
-        <v>1577</v>
+        <v>487</v>
       </c>
       <c r="N22" t="n">
-        <v>6726.99</v>
+        <v>2294.51</v>
       </c>
       <c r="O22" t="n">
-        <v>914</v>
+        <v>252</v>
       </c>
       <c r="P22" t="n">
-        <v>44</v>
+        <v>58.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.27</v>
+        <v>4.71</v>
       </c>
       <c r="R22" t="n">
-        <v>2326</v>
+        <v>713</v>
       </c>
       <c r="S22" t="n">
-        <v>23802.53</v>
+        <v>16978.37</v>
       </c>
       <c r="T22" t="n">
-        <v>1006</v>
+        <v>257</v>
       </c>
       <c r="U22" t="n">
-        <v>48.4</v>
+        <v>59.9</v>
       </c>
       <c r="V22" t="n">
-        <v>10.23</v>
+        <v>23.81</v>
       </c>
       <c r="W22" t="n">
-        <v>10.85</v>
+        <v>39.21</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.65</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.89</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="23">
@@ -2293,74 +2263,74 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>904</v>
+        <v>733</v>
       </c>
       <c r="E23" t="n">
-        <v>982</v>
+        <v>743</v>
       </c>
       <c r="F23" t="n">
-        <v>989</v>
+        <v>743</v>
       </c>
       <c r="G23" t="n">
-        <v>7754.45</v>
+        <v>4234.44</v>
       </c>
       <c r="H23" t="n">
-        <v>784</v>
+        <v>522</v>
       </c>
       <c r="I23" t="n">
-        <v>31854.77</v>
+        <v>5119.37</v>
       </c>
       <c r="J23" t="n">
-        <v>419</v>
+        <v>312</v>
       </c>
       <c r="K23" t="n">
-        <v>46.3</v>
+        <v>42.6</v>
       </c>
       <c r="L23" t="n">
-        <v>40.63</v>
+        <v>9.81</v>
       </c>
       <c r="M23" t="n">
-        <v>1220</v>
+        <v>698</v>
       </c>
       <c r="N23" t="n">
-        <v>40995.79</v>
+        <v>21935.54</v>
       </c>
       <c r="O23" t="n">
-        <v>523</v>
+        <v>395</v>
       </c>
       <c r="P23" t="n">
-        <v>57.9</v>
+        <v>53.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>33.6</v>
+        <v>31.43</v>
       </c>
       <c r="R23" t="n">
-        <v>1941</v>
+        <v>937</v>
       </c>
       <c r="S23" t="n">
-        <v>70282.64</v>
+        <v>24536.34</v>
       </c>
       <c r="T23" t="n">
-        <v>570</v>
+        <v>403</v>
       </c>
       <c r="U23" t="n">
-        <v>63.1</v>
+        <v>55</v>
       </c>
       <c r="V23" t="n">
-        <v>36.21</v>
+        <v>26.19</v>
       </c>
       <c r="W23" t="n">
-        <v>71.56999999999999</v>
+        <v>33.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.98</v>
+        <v>1.26</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.06</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="24">
@@ -2376,74 +2346,74 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>332</v>
+        <v>679</v>
       </c>
       <c r="E24" t="n">
-        <v>365</v>
+        <v>684</v>
       </c>
       <c r="F24" t="n">
-        <v>365</v>
+        <v>684</v>
       </c>
       <c r="G24" t="n">
-        <v>2114.42</v>
+        <v>3912.27</v>
       </c>
       <c r="H24" t="n">
-        <v>477</v>
+        <v>690</v>
       </c>
       <c r="I24" t="n">
-        <v>4197.09</v>
+        <v>6534.6</v>
       </c>
       <c r="J24" t="n">
-        <v>204</v>
+        <v>381</v>
       </c>
       <c r="K24" t="n">
-        <v>61.4</v>
+        <v>56.1</v>
       </c>
       <c r="L24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>665</v>
+        <v>936</v>
       </c>
       <c r="N24" t="n">
-        <v>4992.06</v>
+        <v>16084.79</v>
       </c>
       <c r="O24" t="n">
-        <v>256</v>
+        <v>467</v>
       </c>
       <c r="P24" t="n">
-        <v>77.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.51</v>
+        <v>17.18</v>
       </c>
       <c r="R24" t="n">
-        <v>694</v>
+        <v>1281</v>
       </c>
       <c r="S24" t="n">
-        <v>5277.33</v>
+        <v>29119.55</v>
       </c>
       <c r="T24" t="n">
-        <v>256</v>
+        <v>475</v>
       </c>
       <c r="U24" t="n">
-        <v>77.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="V24" t="n">
-        <v>7.6</v>
+        <v>22.73</v>
       </c>
       <c r="W24" t="n">
-        <v>14.46</v>
+        <v>42.57</v>
       </c>
       <c r="X24" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.5</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="25">
@@ -2459,80 +2429,80 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>710</v>
+        <v>1448</v>
       </c>
       <c r="E25" t="n">
-        <v>792</v>
+        <v>1461</v>
       </c>
       <c r="F25" t="n">
-        <v>797</v>
+        <v>1461</v>
       </c>
       <c r="G25" t="n">
-        <v>5089.81</v>
+        <v>8323.48</v>
       </c>
       <c r="H25" t="n">
-        <v>451</v>
+        <v>1769</v>
       </c>
       <c r="I25" t="n">
-        <v>2315.31</v>
+        <v>73400.73</v>
       </c>
       <c r="J25" t="n">
-        <v>243</v>
+        <v>935</v>
       </c>
       <c r="K25" t="n">
-        <v>34.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>5.13</v>
+        <v>41.49</v>
       </c>
       <c r="M25" t="n">
-        <v>451</v>
+        <v>2730</v>
       </c>
       <c r="N25" t="n">
-        <v>2315.31</v>
+        <v>79348.72</v>
       </c>
       <c r="O25" t="n">
-        <v>243</v>
+        <v>1195</v>
       </c>
       <c r="P25" t="n">
-        <v>34.2</v>
+        <v>82.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.13</v>
+        <v>29.07</v>
       </c>
       <c r="R25" t="n">
-        <v>451</v>
+        <v>4035</v>
       </c>
       <c r="S25" t="n">
-        <v>2315.31</v>
+        <v>98287.21000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>243</v>
+        <v>1205</v>
       </c>
       <c r="U25" t="n">
-        <v>34.2</v>
+        <v>83.2</v>
       </c>
       <c r="V25" t="n">
-        <v>5.13</v>
+        <v>24.36</v>
       </c>
       <c r="W25" t="n">
-        <v>2.92</v>
+        <v>67.27</v>
       </c>
       <c r="X25" t="n">
-        <v>0.57</v>
+        <v>2.76</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.45</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Frother</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2542,76 +2512,80 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>958</v>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>981</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>981</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>5585.51</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1924</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>83246.50999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="L26" t="n">
+        <v>43.27</v>
+      </c>
       <c r="M26" t="n">
-        <v>10</v>
+        <v>2413</v>
       </c>
       <c r="N26" t="n">
-        <v>27.05</v>
+        <v>91473.21000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>8</v>
+        <v>833</v>
       </c>
       <c r="P26" t="n">
-        <v>47.1</v>
+        <v>87</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.71</v>
+        <v>37.91</v>
       </c>
       <c r="R26" t="n">
-        <v>12</v>
+        <v>3098</v>
       </c>
       <c r="S26" t="n">
-        <v>27.05</v>
+        <v>98166.2</v>
       </c>
       <c r="T26" t="n">
-        <v>9</v>
+        <v>836</v>
       </c>
       <c r="U26" t="n">
-        <v>52.9</v>
+        <v>87.3</v>
       </c>
       <c r="V26" t="n">
-        <v>2.25</v>
+        <v>31.69</v>
       </c>
       <c r="W26" t="n">
-        <v>1.59</v>
+        <v>100.07</v>
       </c>
       <c r="X26" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="Y26" t="inlineStr"/>
+        <v>3.16</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>17.58</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2621,74 +2595,80 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>661</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>684</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>684</v>
       </c>
       <c r="G27" t="n">
-        <v>5.64</v>
+        <v>3891.96</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>965</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>14855.14</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>70.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>15.39</v>
+      </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1484</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>19351.9</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+        <v>89.3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>13.04</v>
+      </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1987</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>32249.45</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="inlineStr"/>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="V27" t="n">
+        <v>16.23</v>
+      </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>47.15</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2698,80 +2678,80 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>114</v>
+        <v>3197</v>
       </c>
       <c r="E28" t="n">
-        <v>116</v>
+        <v>3278</v>
       </c>
       <c r="F28" t="n">
-        <v>116</v>
+        <v>3278</v>
       </c>
       <c r="G28" t="n">
-        <v>657.88</v>
+        <v>18651.82</v>
       </c>
       <c r="H28" t="n">
-        <v>84</v>
+        <v>2840</v>
       </c>
       <c r="I28" t="n">
-        <v>1483.66</v>
+        <v>28289.48</v>
       </c>
       <c r="J28" t="n">
-        <v>44</v>
+        <v>1508</v>
       </c>
       <c r="K28" t="n">
-        <v>38.6</v>
+        <v>47.2</v>
       </c>
       <c r="L28" t="n">
-        <v>17.66</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>128</v>
+        <v>4959</v>
       </c>
       <c r="N28" t="n">
-        <v>2174.71</v>
+        <v>35202.98</v>
       </c>
       <c r="O28" t="n">
-        <v>62</v>
+        <v>2292</v>
       </c>
       <c r="P28" t="n">
-        <v>54.4</v>
+        <v>71.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>16.99</v>
+        <v>7.1</v>
       </c>
       <c r="R28" t="n">
-        <v>249</v>
+        <v>5437</v>
       </c>
       <c r="S28" t="n">
-        <v>5133.76</v>
+        <v>37655.33</v>
       </c>
       <c r="T28" t="n">
-        <v>65</v>
+        <v>2301</v>
       </c>
       <c r="U28" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="V28" t="n">
-        <v>20.62</v>
+        <v>6.93</v>
       </c>
       <c r="W28" t="n">
-        <v>44.26</v>
+        <v>11.49</v>
       </c>
       <c r="X28" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.8</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2781,80 +2761,80 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>2077</v>
       </c>
       <c r="E29" t="n">
-        <v>58</v>
+        <v>2193</v>
       </c>
       <c r="F29" t="n">
-        <v>58</v>
+        <v>2195</v>
       </c>
       <c r="G29" t="n">
-        <v>327.12</v>
+        <v>12596.48</v>
       </c>
       <c r="H29" t="n">
-        <v>57</v>
+        <v>1539</v>
       </c>
       <c r="I29" t="n">
-        <v>6155.71</v>
+        <v>5951.25</v>
       </c>
       <c r="J29" t="n">
-        <v>34</v>
+        <v>896</v>
       </c>
       <c r="K29" t="n">
-        <v>58.6</v>
+        <v>43.1</v>
       </c>
       <c r="L29" t="n">
-        <v>107.99</v>
+        <v>3.87</v>
       </c>
       <c r="M29" t="n">
-        <v>80</v>
+        <v>1577</v>
       </c>
       <c r="N29" t="n">
-        <v>7552.59</v>
+        <v>6726.99</v>
       </c>
       <c r="O29" t="n">
-        <v>47</v>
+        <v>914</v>
       </c>
       <c r="P29" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="Q29" t="n">
-        <v>94.41</v>
+        <v>4.27</v>
       </c>
       <c r="R29" t="n">
-        <v>153</v>
+        <v>2326</v>
       </c>
       <c r="S29" t="n">
-        <v>9311.51</v>
+        <v>23802.53</v>
       </c>
       <c r="T29" t="n">
-        <v>47</v>
+        <v>1006</v>
       </c>
       <c r="U29" t="n">
-        <v>81</v>
+        <v>48.4</v>
       </c>
       <c r="V29" t="n">
-        <v>60.86</v>
+        <v>10.23</v>
       </c>
       <c r="W29" t="n">
-        <v>160.54</v>
+        <v>10.85</v>
       </c>
       <c r="X29" t="n">
-        <v>2.64</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>28.47</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2864,80 +2844,80 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>904</v>
       </c>
       <c r="E30" t="n">
-        <v>28</v>
+        <v>982</v>
       </c>
       <c r="F30" t="n">
-        <v>28</v>
+        <v>989</v>
       </c>
       <c r="G30" t="n">
-        <v>157.92</v>
+        <v>7754.45</v>
       </c>
       <c r="H30" t="n">
-        <v>31</v>
+        <v>784</v>
       </c>
       <c r="I30" t="n">
-        <v>1515.84</v>
+        <v>31854.77</v>
       </c>
       <c r="J30" t="n">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="K30" t="n">
-        <v>75</v>
+        <v>46.3</v>
       </c>
       <c r="L30" t="n">
-        <v>48.9</v>
+        <v>40.63</v>
       </c>
       <c r="M30" t="n">
-        <v>43</v>
+        <v>1220</v>
       </c>
       <c r="N30" t="n">
-        <v>2670.93</v>
+        <v>40995.79</v>
       </c>
       <c r="O30" t="n">
-        <v>25</v>
+        <v>523</v>
       </c>
       <c r="P30" t="n">
-        <v>89.3</v>
+        <v>57.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>62.11</v>
+        <v>33.6</v>
       </c>
       <c r="R30" t="n">
-        <v>57</v>
+        <v>1941</v>
       </c>
       <c r="S30" t="n">
-        <v>3065.86</v>
+        <v>70282.64</v>
       </c>
       <c r="T30" t="n">
-        <v>25</v>
+        <v>570</v>
       </c>
       <c r="U30" t="n">
-        <v>89.3</v>
+        <v>63.1</v>
       </c>
       <c r="V30" t="n">
-        <v>53.79</v>
+        <v>36.21</v>
       </c>
       <c r="W30" t="n">
-        <v>109.5</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Y30" t="n">
-        <v>19.41</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2947,80 +2927,80 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>365</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>365</v>
       </c>
       <c r="G31" t="n">
-        <v>11.28</v>
+        <v>2114.42</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>477</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>4197.09</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="K31" t="n">
-        <v>50</v>
+        <v>61.4</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>665</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4992.06</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="P31" t="n">
-        <v>50</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>7.51</v>
       </c>
       <c r="R31" t="n">
-        <v>3</v>
+        <v>694</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>5277.33</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="U31" t="n">
-        <v>100</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>14.46</v>
       </c>
       <c r="X31" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3030,80 +3010,80 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>427</v>
+        <v>710</v>
       </c>
       <c r="E32" t="n">
-        <v>428</v>
+        <v>792</v>
       </c>
       <c r="F32" t="n">
-        <v>428</v>
+        <v>797</v>
       </c>
       <c r="G32" t="n">
-        <v>2467.5</v>
+        <v>5089.81</v>
       </c>
       <c r="H32" t="n">
-        <v>279</v>
+        <v>451</v>
       </c>
       <c r="I32" t="n">
-        <v>14553.27</v>
+        <v>2315.31</v>
       </c>
       <c r="J32" t="n">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="K32" t="n">
-        <v>43.1</v>
+        <v>34.2</v>
       </c>
       <c r="L32" t="n">
-        <v>52.16</v>
+        <v>5.13</v>
       </c>
       <c r="M32" t="n">
-        <v>896</v>
+        <v>451</v>
       </c>
       <c r="N32" t="n">
-        <v>50933.59</v>
+        <v>2315.31</v>
       </c>
       <c r="O32" t="n">
-        <v>378</v>
+        <v>243</v>
       </c>
       <c r="P32" t="n">
-        <v>88.5</v>
+        <v>34.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>56.85</v>
+        <v>5.13</v>
       </c>
       <c r="R32" t="n">
-        <v>1216</v>
+        <v>451</v>
       </c>
       <c r="S32" t="n">
-        <v>64842.26</v>
+        <v>2315.31</v>
       </c>
       <c r="T32" t="n">
-        <v>385</v>
+        <v>243</v>
       </c>
       <c r="U32" t="n">
-        <v>90.2</v>
+        <v>34.2</v>
       </c>
       <c r="V32" t="n">
-        <v>53.32</v>
+        <v>5.13</v>
       </c>
       <c r="W32" t="n">
-        <v>151.5</v>
+        <v>2.92</v>
       </c>
       <c r="X32" t="n">
-        <v>2.84</v>
+        <v>0.57</v>
       </c>
       <c r="Y32" t="n">
-        <v>26.28</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Frother</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3113,75 +3093,71 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>413</v>
+        <v>17</v>
       </c>
       <c r="E33" t="n">
-        <v>417</v>
+        <v>17</v>
       </c>
       <c r="F33" t="n">
-        <v>417</v>
+        <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>2358.65</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>830</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>53790.47</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>86</v>
-      </c>
-      <c r="L33" t="n">
-        <v>64.81</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>971</v>
+        <v>10</v>
       </c>
       <c r="N33" t="n">
-        <v>55864.97</v>
+        <v>27.05</v>
       </c>
       <c r="O33" t="n">
-        <v>371</v>
+        <v>8</v>
       </c>
       <c r="P33" t="n">
-        <v>89.8</v>
+        <v>47.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>57.53</v>
+        <v>2.71</v>
       </c>
       <c r="R33" t="n">
-        <v>1194</v>
+        <v>12</v>
       </c>
       <c r="S33" t="n">
-        <v>64062.1</v>
+        <v>27.05</v>
       </c>
       <c r="T33" t="n">
-        <v>374</v>
+        <v>9</v>
       </c>
       <c r="U33" t="n">
-        <v>90.59999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="V33" t="n">
-        <v>53.65</v>
+        <v>2.25</v>
       </c>
       <c r="W33" t="n">
-        <v>153.63</v>
+        <v>1.59</v>
       </c>
       <c r="X33" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>27.16</v>
-      </c>
+        <v>0.71</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3196,74 +3172,68 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>623</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>626</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>626</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>3530.64</v>
+        <v>5.64</v>
       </c>
       <c r="H34" t="n">
-        <v>481</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>24830.64</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>51.62</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>771</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>35500.57</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>46.04</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="n">
-        <v>1210</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>44602.85</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="V34" t="n">
-        <v>36.86</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="n">
-        <v>71.25</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>12.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3279,74 +3249,74 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>332</v>
+        <v>114</v>
       </c>
       <c r="E35" t="n">
-        <v>341</v>
+        <v>116</v>
       </c>
       <c r="F35" t="n">
-        <v>341</v>
+        <v>116</v>
       </c>
       <c r="G35" t="n">
-        <v>1923.24</v>
+        <v>657.88</v>
       </c>
       <c r="H35" t="n">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="I35" t="n">
-        <v>18138.35</v>
+        <v>1483.66</v>
       </c>
       <c r="J35" t="n">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="K35" t="n">
-        <v>52.7</v>
+        <v>38.6</v>
       </c>
       <c r="L35" t="n">
-        <v>45.35</v>
+        <v>17.66</v>
       </c>
       <c r="M35" t="n">
-        <v>600</v>
+        <v>128</v>
       </c>
       <c r="N35" t="n">
-        <v>20493.93</v>
+        <v>2174.71</v>
       </c>
       <c r="O35" t="n">
-        <v>245</v>
+        <v>62</v>
       </c>
       <c r="P35" t="n">
-        <v>73.8</v>
+        <v>54.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>34.16</v>
+        <v>16.99</v>
       </c>
       <c r="R35" t="n">
-        <v>661</v>
+        <v>249</v>
       </c>
       <c r="S35" t="n">
-        <v>21181.58</v>
+        <v>5133.76</v>
       </c>
       <c r="T35" t="n">
-        <v>248</v>
+        <v>65</v>
       </c>
       <c r="U35" t="n">
-        <v>74.7</v>
+        <v>57</v>
       </c>
       <c r="V35" t="n">
-        <v>32.04</v>
+        <v>20.62</v>
       </c>
       <c r="W35" t="n">
-        <v>62.12</v>
+        <v>44.26</v>
       </c>
       <c r="X35" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="Y35" t="n">
-        <v>11.01</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="36">
@@ -3362,80 +3332,80 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>354</v>
+        <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>362</v>
+        <v>58</v>
       </c>
       <c r="F36" t="n">
-        <v>362</v>
+        <v>58</v>
       </c>
       <c r="G36" t="n">
-        <v>2041.68</v>
+        <v>327.12</v>
       </c>
       <c r="H36" t="n">
-        <v>229</v>
+        <v>57</v>
       </c>
       <c r="I36" t="n">
-        <v>2679.72</v>
+        <v>6155.71</v>
       </c>
       <c r="J36" t="n">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="K36" t="n">
-        <v>41.5</v>
+        <v>58.6</v>
       </c>
       <c r="L36" t="n">
-        <v>11.7</v>
+        <v>107.99</v>
       </c>
       <c r="M36" t="n">
-        <v>229</v>
+        <v>80</v>
       </c>
       <c r="N36" t="n">
-        <v>2679.72</v>
+        <v>7552.59</v>
       </c>
       <c r="O36" t="n">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="P36" t="n">
-        <v>41.5</v>
+        <v>81</v>
       </c>
       <c r="Q36" t="n">
-        <v>11.7</v>
+        <v>94.41</v>
       </c>
       <c r="R36" t="n">
-        <v>229</v>
+        <v>153</v>
       </c>
       <c r="S36" t="n">
-        <v>2679.72</v>
+        <v>9311.51</v>
       </c>
       <c r="T36" t="n">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="U36" t="n">
-        <v>41.5</v>
+        <v>81</v>
       </c>
       <c r="V36" t="n">
-        <v>11.7</v>
+        <v>60.86</v>
       </c>
       <c r="W36" t="n">
-        <v>7.4</v>
+        <v>160.54</v>
       </c>
       <c r="X36" t="n">
-        <v>0.63</v>
+        <v>2.64</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.31</v>
+        <v>28.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gut Shift</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3445,80 +3415,80 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E37" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F37" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G37" t="n">
-        <v>269.1</v>
+        <v>157.92</v>
       </c>
       <c r="H37" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I37" t="n">
-        <v>789.45</v>
+        <v>1515.84</v>
       </c>
       <c r="J37" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>26.7</v>
+        <v>75</v>
       </c>
       <c r="L37" t="n">
-        <v>49.34</v>
+        <v>48.9</v>
       </c>
       <c r="M37" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="N37" t="n">
-        <v>789.45</v>
+        <v>2670.93</v>
       </c>
       <c r="O37" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="P37" t="n">
-        <v>26.7</v>
+        <v>89.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>49.34</v>
+        <v>62.11</v>
       </c>
       <c r="R37" t="n">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="S37" t="n">
-        <v>8073.8</v>
+        <v>3065.86</v>
       </c>
       <c r="T37" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="U37" t="n">
-        <v>56.7</v>
+        <v>89.3</v>
       </c>
       <c r="V37" t="n">
-        <v>61.17</v>
+        <v>53.79</v>
       </c>
       <c r="W37" t="n">
-        <v>269.13</v>
+        <v>109.5</v>
       </c>
       <c r="X37" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>30</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gut Shift</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3528,80 +3498,80 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>516</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>517</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>517</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>4637.49</v>
+        <v>11.28</v>
       </c>
       <c r="H38" t="n">
-        <v>294</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>2872.62</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>216</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>41.9</v>
+        <v>50</v>
       </c>
       <c r="L38" t="n">
-        <v>9.77</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>471</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>17113.88</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>273</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="Q38" t="n">
-        <v>36.34</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>601</v>
+        <v>3</v>
       </c>
       <c r="S38" t="n">
-        <v>18907.97</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>284</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="V38" t="n">
-        <v>31.46</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>36.57</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gut Shift</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3611,78 +3581,80 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16</v>
+        <v>427</v>
       </c>
       <c r="E39" t="n">
-        <v>16</v>
+        <v>428</v>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>428</v>
       </c>
       <c r="G39" t="n">
-        <v>143.52</v>
+        <v>2467.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>14553.27</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
+        <v>43.1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>52.16</v>
+      </c>
       <c r="M39" t="n">
-        <v>28</v>
+        <v>896</v>
       </c>
       <c r="N39" t="n">
-        <v>233.34</v>
+        <v>50933.59</v>
       </c>
       <c r="O39" t="n">
-        <v>11</v>
+        <v>378</v>
       </c>
       <c r="P39" t="n">
-        <v>68.8</v>
+        <v>88.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>8.33</v>
+        <v>56.85</v>
       </c>
       <c r="R39" t="n">
-        <v>29</v>
+        <v>1216</v>
       </c>
       <c r="S39" t="n">
-        <v>233.34</v>
+        <v>64842.26</v>
       </c>
       <c r="T39" t="n">
-        <v>12</v>
+        <v>385</v>
       </c>
       <c r="U39" t="n">
-        <v>75</v>
+        <v>90.2</v>
       </c>
       <c r="V39" t="n">
-        <v>8.050000000000001</v>
+        <v>53.32</v>
       </c>
       <c r="W39" t="n">
-        <v>14.58</v>
+        <v>151.5</v>
       </c>
       <c r="X39" t="n">
-        <v>1.81</v>
+        <v>2.84</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>26.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gut Shift</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3692,80 +3664,80 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>331</v>
+        <v>413</v>
       </c>
       <c r="E40" t="n">
-        <v>333</v>
+        <v>417</v>
       </c>
       <c r="F40" t="n">
-        <v>333</v>
+        <v>417</v>
       </c>
       <c r="G40" t="n">
-        <v>2987.01</v>
+        <v>2358.65</v>
       </c>
       <c r="H40" t="n">
-        <v>168</v>
+        <v>830</v>
       </c>
       <c r="I40" t="n">
-        <v>203.36</v>
+        <v>53790.47</v>
       </c>
       <c r="J40" t="n">
-        <v>131</v>
+        <v>355</v>
       </c>
       <c r="K40" t="n">
-        <v>39.6</v>
+        <v>86</v>
       </c>
       <c r="L40" t="n">
-        <v>1.21</v>
+        <v>64.81</v>
       </c>
       <c r="M40" t="n">
-        <v>168</v>
+        <v>971</v>
       </c>
       <c r="N40" t="n">
-        <v>203.36</v>
+        <v>55864.97</v>
       </c>
       <c r="O40" t="n">
-        <v>131</v>
+        <v>371</v>
       </c>
       <c r="P40" t="n">
-        <v>39.6</v>
+        <v>89.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.21</v>
+        <v>57.53</v>
       </c>
       <c r="R40" t="n">
-        <v>168</v>
+        <v>1194</v>
       </c>
       <c r="S40" t="n">
-        <v>203.36</v>
+        <v>64062.1</v>
       </c>
       <c r="T40" t="n">
-        <v>131</v>
+        <v>374</v>
       </c>
       <c r="U40" t="n">
-        <v>39.6</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V40" t="n">
-        <v>1.21</v>
+        <v>53.65</v>
       </c>
       <c r="W40" t="n">
-        <v>0.61</v>
+        <v>153.63</v>
       </c>
       <c r="X40" t="n">
-        <v>0.5</v>
+        <v>2.86</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.07000000000000001</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Halloween Gift Set</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3775,78 +3747,80 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>623</v>
       </c>
       <c r="E41" t="n">
-        <v>14</v>
+        <v>626</v>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
+        <v>626</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>3530.64</v>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>481</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>24830.64</v>
       </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>271</v>
       </c>
       <c r="K41" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>51.62</v>
       </c>
       <c r="M41" t="n">
-        <v>9</v>
+        <v>771</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>35500.57</v>
       </c>
       <c r="O41" t="n">
-        <v>7</v>
+        <v>345</v>
       </c>
       <c r="P41" t="n">
-        <v>50</v>
+        <v>55.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>46.04</v>
       </c>
       <c r="R41" t="n">
-        <v>9</v>
+        <v>1210</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>44602.85</v>
       </c>
       <c r="T41" t="n">
-        <v>7</v>
+        <v>368</v>
       </c>
       <c r="U41" t="n">
-        <v>50</v>
+        <v>59.1</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>36.86</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>71.25</v>
       </c>
       <c r="X41" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="Y41" t="inlineStr"/>
+        <v>1.93</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>12.63</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3856,80 +3830,80 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>69</v>
+        <v>332</v>
       </c>
       <c r="E42" t="n">
-        <v>69</v>
+        <v>341</v>
       </c>
       <c r="F42" t="n">
-        <v>69</v>
+        <v>341</v>
       </c>
       <c r="G42" t="n">
-        <v>326.37</v>
+        <v>1923.24</v>
       </c>
       <c r="H42" t="n">
-        <v>23</v>
+        <v>400</v>
       </c>
       <c r="I42" t="n">
-        <v>233.08</v>
+        <v>18138.35</v>
       </c>
       <c r="J42" t="n">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="K42" t="n">
-        <v>21.7</v>
+        <v>52.7</v>
       </c>
       <c r="L42" t="n">
-        <v>10.13</v>
+        <v>45.35</v>
       </c>
       <c r="M42" t="n">
-        <v>41</v>
+        <v>600</v>
       </c>
       <c r="N42" t="n">
-        <v>422.37</v>
+        <v>20493.93</v>
       </c>
       <c r="O42" t="n">
-        <v>25</v>
+        <v>245</v>
       </c>
       <c r="P42" t="n">
-        <v>36.2</v>
+        <v>73.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>10.3</v>
+        <v>34.16</v>
       </c>
       <c r="R42" t="n">
-        <v>136</v>
+        <v>661</v>
       </c>
       <c r="S42" t="n">
-        <v>2676.72</v>
+        <v>21181.58</v>
       </c>
       <c r="T42" t="n">
-        <v>37</v>
+        <v>248</v>
       </c>
       <c r="U42" t="n">
-        <v>53.6</v>
+        <v>74.7</v>
       </c>
       <c r="V42" t="n">
-        <v>19.68</v>
+        <v>32.04</v>
       </c>
       <c r="W42" t="n">
-        <v>38.79</v>
+        <v>62.12</v>
       </c>
       <c r="X42" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Y42" t="n">
-        <v>8.199999999999999</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3939,80 +3913,80 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>127</v>
+        <v>354</v>
       </c>
       <c r="E43" t="n">
-        <v>127</v>
+        <v>362</v>
       </c>
       <c r="F43" t="n">
-        <v>127</v>
+        <v>362</v>
       </c>
       <c r="G43" t="n">
-        <v>600.71</v>
+        <v>2041.68</v>
       </c>
       <c r="H43" t="n">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="I43" t="n">
-        <v>2982.93</v>
+        <v>2679.72</v>
       </c>
       <c r="J43" t="n">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="K43" t="n">
-        <v>39.4</v>
+        <v>41.5</v>
       </c>
       <c r="L43" t="n">
-        <v>35.51</v>
+        <v>11.7</v>
       </c>
       <c r="M43" t="n">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="N43" t="n">
-        <v>3411.9</v>
+        <v>2679.72</v>
       </c>
       <c r="O43" t="n">
-        <v>63</v>
+        <v>147</v>
       </c>
       <c r="P43" t="n">
-        <v>49.6</v>
+        <v>41.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>27.74</v>
+        <v>11.7</v>
       </c>
       <c r="R43" t="n">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="S43" t="n">
-        <v>3711.1</v>
+        <v>2679.72</v>
       </c>
       <c r="T43" t="n">
-        <v>67</v>
+        <v>147</v>
       </c>
       <c r="U43" t="n">
-        <v>52.8</v>
+        <v>41.5</v>
       </c>
       <c r="V43" t="n">
-        <v>22.63</v>
+        <v>11.7</v>
       </c>
       <c r="W43" t="n">
-        <v>29.22</v>
+        <v>7.4</v>
       </c>
       <c r="X43" t="n">
-        <v>1.29</v>
+        <v>0.63</v>
       </c>
       <c r="Y43" t="n">
-        <v>6.18</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Gut Shift</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4022,74 +3996,80 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G44" t="n">
-        <v>4.73</v>
+        <v>269.1</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>789.45</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
+        <v>26.7</v>
+      </c>
+      <c r="L44" t="n">
+        <v>49.34</v>
+      </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>789.45</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+        <v>26.7</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>49.34</v>
+      </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>8073.8</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="inlineStr"/>
+        <v>56.7</v>
+      </c>
+      <c r="V44" t="n">
+        <v>61.17</v>
+      </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>269.13</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Gut Shift</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4099,80 +4079,80 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>33</v>
+        <v>516</v>
       </c>
       <c r="E45" t="n">
-        <v>33</v>
+        <v>517</v>
       </c>
       <c r="F45" t="n">
-        <v>33</v>
+        <v>517</v>
       </c>
       <c r="G45" t="n">
-        <v>156.09</v>
+        <v>4637.49</v>
       </c>
       <c r="H45" t="n">
-        <v>28</v>
+        <v>294</v>
       </c>
       <c r="I45" t="n">
-        <v>101.05</v>
+        <v>2872.62</v>
       </c>
       <c r="J45" t="n">
-        <v>19</v>
+        <v>216</v>
       </c>
       <c r="K45" t="n">
-        <v>57.6</v>
+        <v>41.9</v>
       </c>
       <c r="L45" t="n">
-        <v>3.61</v>
+        <v>9.77</v>
       </c>
       <c r="M45" t="n">
-        <v>28</v>
+        <v>471</v>
       </c>
       <c r="N45" t="n">
-        <v>101.05</v>
+        <v>17113.88</v>
       </c>
       <c r="O45" t="n">
-        <v>19</v>
+        <v>273</v>
       </c>
       <c r="P45" t="n">
-        <v>57.6</v>
+        <v>52.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.61</v>
+        <v>36.34</v>
       </c>
       <c r="R45" t="n">
-        <v>28</v>
+        <v>601</v>
       </c>
       <c r="S45" t="n">
-        <v>101.05</v>
+        <v>18907.97</v>
       </c>
       <c r="T45" t="n">
-        <v>19</v>
+        <v>284</v>
       </c>
       <c r="U45" t="n">
-        <v>57.6</v>
+        <v>55</v>
       </c>
       <c r="V45" t="n">
-        <v>3.61</v>
+        <v>31.46</v>
       </c>
       <c r="W45" t="n">
-        <v>3.06</v>
+        <v>36.57</v>
       </c>
       <c r="X45" t="n">
-        <v>0.85</v>
+        <v>1.16</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.65</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Gut Shift</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4186,76 +4166,74 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E46" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G46" t="n">
-        <v>56.72</v>
+        <v>143.52</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>233.34</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P46" t="n">
-        <v>50</v>
+        <v>68.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="R46" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>233.34</v>
       </c>
       <c r="T46" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="U46" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>14.58</v>
       </c>
       <c r="X46" t="n">
-        <v>0.62</v>
+        <v>1.81</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Gut Shift</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4269,76 +4247,76 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>331</v>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>333</v>
       </c>
       <c r="F47" t="n">
-        <v>9</v>
+        <v>333</v>
       </c>
       <c r="G47" t="n">
-        <v>63.81</v>
+        <v>2987.01</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>168</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>203.36</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="K47" t="n">
-        <v>33.3</v>
+        <v>39.6</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>168</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>203.36</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="P47" t="n">
-        <v>33.3</v>
+        <v>39.6</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="R47" t="n">
-        <v>4</v>
+        <v>168</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>203.36</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="U47" t="n">
-        <v>33.3</v>
+        <v>39.6</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="X47" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Moringa</t>
+          <t>Halloween Gift Set</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4348,72 +4326,78 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
       <c r="W48" t="n">
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="Y48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Moringa</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4423,76 +4407,80 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="F49" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>326.37</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>233.08</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
+        <v>21.7</v>
+      </c>
+      <c r="L49" t="n">
+        <v>10.13</v>
+      </c>
       <c r="M49" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>422.37</v>
       </c>
       <c r="O49" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="P49" t="n">
-        <v>27.8</v>
+        <v>36.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="R49" t="n">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2676.72</v>
       </c>
       <c r="T49" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="U49" t="n">
-        <v>38.9</v>
+        <v>53.6</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>19.68</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>38.79</v>
       </c>
       <c r="X49" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="Y49" t="inlineStr"/>
+        <v>1.97</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>8.199999999999999</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Moringa</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4502,78 +4490,80 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="E50" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="F50" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>600.71</v>
       </c>
       <c r="H50" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>2982.93</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="K50" t="n">
-        <v>25</v>
+        <v>39.4</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>35.51</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3411.9</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="P50" t="n">
-        <v>25</v>
+        <v>49.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>27.74</v>
       </c>
       <c r="R50" t="n">
-        <v>4</v>
+        <v>164</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3711.1</v>
       </c>
       <c r="T50" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="U50" t="n">
-        <v>25</v>
+        <v>52.8</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>22.63</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>29.22</v>
       </c>
       <c r="X50" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Y50" t="inlineStr"/>
+        <v>1.29</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>6.18</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Shatavari</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4587,16 +4577,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -4612,47 +4602,45 @@
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>163.25</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="V51" t="n">
-        <v>8.59</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="Y51" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Shatavari</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4666,74 +4654,76 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E52" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F52" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>156.09</v>
       </c>
       <c r="H52" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>101.05</v>
       </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K52" t="n">
-        <v>37.5</v>
+        <v>57.6</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="M52" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>101.05</v>
       </c>
       <c r="O52" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="P52" t="n">
-        <v>37.5</v>
+        <v>57.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R52" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>101.05</v>
       </c>
       <c r="T52" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="U52" t="n">
-        <v>37.5</v>
+        <v>57.6</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="X52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y52" t="inlineStr"/>
+        <v>0.85</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Skin Radiance</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4747,76 +4737,76 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>157</v>
+        <v>8</v>
       </c>
       <c r="E53" t="n">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="F53" t="n">
-        <v>158</v>
+        <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>807.38</v>
+        <v>56.72</v>
       </c>
       <c r="H53" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>150.02</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>8.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="L53" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>140</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
-        <v>495.66</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>53.5</v>
+        <v>50</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>142</v>
+        <v>5</v>
       </c>
       <c r="S53" t="n">
-        <v>509.21</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="U53" t="n">
-        <v>53.5</v>
+        <v>50</v>
       </c>
       <c r="V53" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>0.9</v>
+        <v>0.62</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Skin Radiance</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4830,76 +4820,76 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>492</v>
+        <v>9</v>
       </c>
       <c r="E54" t="n">
-        <v>496</v>
+        <v>9</v>
       </c>
       <c r="F54" t="n">
-        <v>496</v>
+        <v>9</v>
       </c>
       <c r="G54" t="n">
-        <v>3162.76</v>
+        <v>63.81</v>
       </c>
       <c r="H54" t="n">
-        <v>237</v>
+        <v>4</v>
       </c>
       <c r="I54" t="n">
-        <v>233.44</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>177</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>36</v>
+        <v>33.3</v>
       </c>
       <c r="L54" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>237</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>233.44</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>177</v>
+        <v>3</v>
       </c>
       <c r="P54" t="n">
-        <v>36</v>
+        <v>33.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>237</v>
+        <v>4</v>
       </c>
       <c r="S54" t="n">
-        <v>233.44</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>177</v>
+        <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>36</v>
+        <v>33.3</v>
       </c>
       <c r="V54" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Moringa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4909,80 +4899,72 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
-        <v>303.33</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>556.9400000000001</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="L55" t="n">
-        <v>23.21</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1023.05</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>24.36</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2720.56</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="V55" t="n">
-        <v>24.73</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="n">
-        <v>43.88</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>8.970000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Moringa</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4992,80 +4974,76 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="E56" t="n">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>694.98</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>333.39</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="L56" t="n">
-        <v>3.97</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
-        <v>904.87</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="P56" t="n">
-        <v>49</v>
+        <v>27.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>181</v>
+        <v>7</v>
       </c>
       <c r="S56" t="n">
-        <v>1286.77</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="U56" t="n">
-        <v>55.9</v>
+        <v>38.9</v>
       </c>
       <c r="V56" t="n">
-        <v>7.11</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.85</v>
-      </c>
+        <v>0.37</v>
+      </c>
+      <c r="Y56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Moringa</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5075,80 +5053,78 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="E57" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="F57" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="G57" t="n">
-        <v>354.78</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="I57" t="n">
-        <v>2181.91</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>49.3</v>
+        <v>25</v>
       </c>
       <c r="L57" t="n">
-        <v>28.71</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>149</v>
+        <v>4</v>
       </c>
       <c r="N57" t="n">
-        <v>3748.85</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
-        <v>83.59999999999999</v>
+        <v>25</v>
       </c>
       <c r="Q57" t="n">
-        <v>25.16</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="S57" t="n">
-        <v>3869.86</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="U57" t="n">
-        <v>83.59999999999999</v>
+        <v>25</v>
       </c>
       <c r="V57" t="n">
-        <v>24.04</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>53.01</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>10.91</v>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="Y57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Shatavari</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5158,80 +5134,76 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E58" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F58" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G58" t="n">
-        <v>155.52</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>34.66</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2.89</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
         <v>12</v>
       </c>
       <c r="N58" t="n">
-        <v>34.66</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P58" t="n">
-        <v>21.9</v>
+        <v>37.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="S58" t="n">
-        <v>34.66</v>
+        <v>163.25</v>
       </c>
       <c r="T58" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U58" t="n">
-        <v>21.9</v>
+        <v>45.8</v>
       </c>
       <c r="V58" t="n">
-        <v>2.89</v>
+        <v>8.59</v>
       </c>
       <c r="W58" t="n">
-        <v>1.08</v>
+        <v>6.8</v>
       </c>
       <c r="X58" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>0.22</v>
-      </c>
+        <v>0.79</v>
+      </c>
+      <c r="Y58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Triphala</t>
+          <t>Shatavari</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5245,58 +5217,58 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F59" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>57.1</v>
+        <v>37.5</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P59" t="n">
-        <v>57.1</v>
+        <v>37.5</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U59" t="n">
-        <v>57.1</v>
+        <v>37.5</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
@@ -5305,14 +5277,14 @@
         <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="Y59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Skin Radiance</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5322,80 +5294,80 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="E60" t="n">
-        <v>55</v>
+        <v>158</v>
       </c>
       <c r="F60" t="n">
-        <v>55</v>
+        <v>158</v>
       </c>
       <c r="G60" t="n">
-        <v>359.15</v>
+        <v>807.38</v>
       </c>
       <c r="H60" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I60" t="n">
-        <v>201.44</v>
+        <v>150.02</v>
       </c>
       <c r="J60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K60" t="n">
-        <v>21.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>16.79</v>
+        <v>6.25</v>
       </c>
       <c r="M60" t="n">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="N60" t="n">
-        <v>201.44</v>
+        <v>495.66</v>
       </c>
       <c r="O60" t="n">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="P60" t="n">
-        <v>29.1</v>
+        <v>53.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>11.85</v>
+        <v>3.54</v>
       </c>
       <c r="R60" t="n">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="S60" t="n">
-        <v>245.42</v>
+        <v>509.21</v>
       </c>
       <c r="T60" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="U60" t="n">
-        <v>34.5</v>
+        <v>53.5</v>
       </c>
       <c r="V60" t="n">
-        <v>9.09</v>
+        <v>3.59</v>
       </c>
       <c r="W60" t="n">
-        <v>4.46</v>
+        <v>3.22</v>
       </c>
       <c r="X60" t="n">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Skin Radiance</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5405,80 +5377,80 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>279</v>
+        <v>492</v>
       </c>
       <c r="E61" t="n">
-        <v>280</v>
+        <v>496</v>
       </c>
       <c r="F61" t="n">
-        <v>280</v>
+        <v>496</v>
       </c>
       <c r="G61" t="n">
-        <v>1866.55</v>
+        <v>3162.76</v>
       </c>
       <c r="H61" t="n">
-        <v>287</v>
+        <v>237</v>
       </c>
       <c r="I61" t="n">
-        <v>1281.51</v>
+        <v>233.44</v>
       </c>
       <c r="J61" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="K61" t="n">
-        <v>57.3</v>
+        <v>36</v>
       </c>
       <c r="L61" t="n">
-        <v>4.47</v>
+        <v>0.98</v>
       </c>
       <c r="M61" t="n">
-        <v>422</v>
+        <v>237</v>
       </c>
       <c r="N61" t="n">
-        <v>1432.42</v>
+        <v>233.44</v>
       </c>
       <c r="O61" t="n">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="P61" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.39</v>
+        <v>0.98</v>
       </c>
       <c r="R61" t="n">
-        <v>585</v>
+        <v>237</v>
       </c>
       <c r="S61" t="n">
-        <v>2363.63</v>
+        <v>233.44</v>
       </c>
       <c r="T61" t="n">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="U61" t="n">
-        <v>76.7</v>
+        <v>36</v>
       </c>
       <c r="V61" t="n">
-        <v>4.04</v>
+        <v>0.98</v>
       </c>
       <c r="W61" t="n">
-        <v>8.44</v>
+        <v>0.47</v>
       </c>
       <c r="X61" t="n">
-        <v>2.09</v>
+        <v>0.48</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.27</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5488,80 +5460,80 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="E62" t="n">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="F62" t="n">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="G62" t="n">
-        <v>1033.26</v>
+        <v>303.33</v>
       </c>
       <c r="H62" t="n">
-        <v>193</v>
+        <v>24</v>
       </c>
       <c r="I62" t="n">
-        <v>3090.93</v>
+        <v>556.9400000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="K62" t="n">
-        <v>79.8</v>
+        <v>16.4</v>
       </c>
       <c r="L62" t="n">
-        <v>16.02</v>
+        <v>23.21</v>
       </c>
       <c r="M62" t="n">
-        <v>208</v>
+        <v>42</v>
       </c>
       <c r="N62" t="n">
-        <v>3136.31</v>
+        <v>1023.05</v>
       </c>
       <c r="O62" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="P62" t="n">
-        <v>83.3</v>
+        <v>23</v>
       </c>
       <c r="Q62" t="n">
-        <v>15.08</v>
+        <v>24.36</v>
       </c>
       <c r="R62" t="n">
-        <v>294</v>
+        <v>110</v>
       </c>
       <c r="S62" t="n">
-        <v>5479.43</v>
+        <v>2720.56</v>
       </c>
       <c r="T62" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="U62" t="n">
-        <v>84.2</v>
+        <v>45.9</v>
       </c>
       <c r="V62" t="n">
-        <v>18.64</v>
+        <v>24.73</v>
       </c>
       <c r="W62" t="n">
-        <v>47.65</v>
+        <v>43.88</v>
       </c>
       <c r="X62" t="n">
-        <v>2.56</v>
+        <v>1.77</v>
       </c>
       <c r="Y62" t="n">
-        <v>5.3</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5571,80 +5543,80 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="E63" t="n">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="F63" t="n">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="G63" t="n">
-        <v>71.83</v>
+        <v>694.98</v>
       </c>
       <c r="H63" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="I63" t="n">
-        <v>86.59999999999999</v>
+        <v>333.39</v>
       </c>
       <c r="J63" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="K63" t="n">
-        <v>63.6</v>
+        <v>38.5</v>
       </c>
       <c r="L63" t="n">
-        <v>2.89</v>
+        <v>3.97</v>
       </c>
       <c r="M63" t="n">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="N63" t="n">
-        <v>86.59999999999999</v>
+        <v>904.87</v>
       </c>
       <c r="O63" t="n">
+        <v>70</v>
+      </c>
+      <c r="P63" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="R63" t="n">
+        <v>181</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1286.77</v>
+      </c>
+      <c r="T63" t="n">
+        <v>80</v>
+      </c>
+      <c r="U63" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="V63" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="W63" t="n">
         <v>9</v>
       </c>
-      <c r="P63" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="R63" t="n">
-        <v>47</v>
-      </c>
-      <c r="S63" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="T63" t="n">
-        <v>9</v>
-      </c>
-      <c r="U63" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="W63" t="n">
-        <v>7.87</v>
-      </c>
       <c r="X63" t="n">
-        <v>4.27</v>
+        <v>1.27</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5654,80 +5626,80 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="F64" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="G64" t="n">
-        <v>135.61</v>
+        <v>354.78</v>
       </c>
       <c r="H64" t="n">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="I64" t="n">
-        <v>24.99</v>
+        <v>2181.91</v>
       </c>
       <c r="J64" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="K64" t="n">
-        <v>36.8</v>
+        <v>49.3</v>
       </c>
       <c r="L64" t="n">
-        <v>3.57</v>
+        <v>28.71</v>
       </c>
       <c r="M64" t="n">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="N64" t="n">
-        <v>176.72</v>
+        <v>3748.85</v>
       </c>
       <c r="O64" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="P64" t="n">
-        <v>89.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.36</v>
+        <v>25.16</v>
       </c>
       <c r="R64" t="n">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="S64" t="n">
-        <v>176.72</v>
+        <v>3869.86</v>
       </c>
       <c r="T64" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="U64" t="n">
-        <v>89.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="V64" t="n">
-        <v>5.36</v>
+        <v>24.04</v>
       </c>
       <c r="W64" t="n">
-        <v>9.300000000000001</v>
+        <v>53.01</v>
       </c>
       <c r="X64" t="n">
-        <v>1.74</v>
+        <v>2.21</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.3</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5737,80 +5709,80 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="E65" t="n">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="F65" t="n">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="G65" t="n">
-        <v>916.9400000000001</v>
+        <v>155.52</v>
       </c>
       <c r="H65" t="n">
-        <v>113</v>
+        <v>12</v>
       </c>
       <c r="I65" t="n">
-        <v>888.63</v>
+        <v>34.66</v>
       </c>
       <c r="J65" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="K65" t="n">
-        <v>65.7</v>
+        <v>21.9</v>
       </c>
       <c r="L65" t="n">
-        <v>7.86</v>
+        <v>2.89</v>
       </c>
       <c r="M65" t="n">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="N65" t="n">
-        <v>1193.8</v>
+        <v>34.66</v>
       </c>
       <c r="O65" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="P65" t="n">
-        <v>78.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q65" t="n">
-        <v>7.7</v>
+        <v>2.89</v>
       </c>
       <c r="R65" t="n">
-        <v>257</v>
+        <v>12</v>
       </c>
       <c r="S65" t="n">
-        <v>4492.9</v>
+        <v>34.66</v>
       </c>
       <c r="T65" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="U65" t="n">
-        <v>78.8</v>
+        <v>21.9</v>
       </c>
       <c r="V65" t="n">
-        <v>17.48</v>
+        <v>2.89</v>
       </c>
       <c r="W65" t="n">
-        <v>44.48</v>
+        <v>1.08</v>
       </c>
       <c r="X65" t="n">
-        <v>2.54</v>
+        <v>0.38</v>
       </c>
       <c r="Y65" t="n">
-        <v>4.9</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Triphala</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5820,75 +5792,73 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="E66" t="n">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="F66" t="n">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="G66" t="n">
-        <v>792.16</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>3735.87</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
-        <v>51.1</v>
+        <v>57.1</v>
       </c>
       <c r="L66" t="n">
-        <v>53.37</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="N66" t="n">
-        <v>4040.16</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="P66" t="n">
-        <v>53.3</v>
+        <v>57.1</v>
       </c>
       <c r="Q66" t="n">
-        <v>51.8</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="S66" t="n">
-        <v>4806.38</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="U66" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="V66" t="n">
-        <v>36.14</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>50.59</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>6.07</v>
-      </c>
+        <v>0.57</v>
+      </c>
+      <c r="Y66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5903,74 +5873,74 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E67" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="F67" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="G67" t="n">
-        <v>235.08</v>
+        <v>359.15</v>
       </c>
       <c r="H67" t="n">
+        <v>12</v>
+      </c>
+      <c r="I67" t="n">
+        <v>201.44</v>
+      </c>
+      <c r="J67" t="n">
+        <v>12</v>
+      </c>
+      <c r="K67" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="L67" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="M67" t="n">
+        <v>17</v>
+      </c>
+      <c r="N67" t="n">
+        <v>201.44</v>
+      </c>
+      <c r="O67" t="n">
         <v>16</v>
       </c>
-      <c r="I67" t="n">
-        <v>55.21</v>
-      </c>
-      <c r="J67" t="n">
-        <v>9</v>
-      </c>
-      <c r="K67" t="n">
-        <v>25</v>
-      </c>
-      <c r="L67" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="M67" t="n">
-        <v>21</v>
-      </c>
-      <c r="N67" t="n">
-        <v>132.09</v>
-      </c>
-      <c r="O67" t="n">
-        <v>12</v>
-      </c>
       <c r="P67" t="n">
-        <v>33.3</v>
+        <v>29.1</v>
       </c>
       <c r="Q67" t="n">
-        <v>6.29</v>
+        <v>11.85</v>
       </c>
       <c r="R67" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="S67" t="n">
-        <v>187.07</v>
+        <v>245.42</v>
       </c>
       <c r="T67" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="U67" t="n">
-        <v>41.7</v>
+        <v>34.5</v>
       </c>
       <c r="V67" t="n">
-        <v>5.34</v>
+        <v>9.09</v>
       </c>
       <c r="W67" t="n">
-        <v>5.2</v>
+        <v>4.46</v>
       </c>
       <c r="X67" t="n">
-        <v>0.97</v>
+        <v>0.49</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="68">
@@ -5986,74 +5956,74 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>128</v>
+        <v>279</v>
       </c>
       <c r="E68" t="n">
-        <v>132</v>
+        <v>280</v>
       </c>
       <c r="F68" t="n">
-        <v>132</v>
+        <v>280</v>
       </c>
       <c r="G68" t="n">
-        <v>869.59</v>
+        <v>1866.55</v>
       </c>
       <c r="H68" t="n">
-        <v>97</v>
+        <v>287</v>
       </c>
       <c r="I68" t="n">
-        <v>2275.61</v>
+        <v>1281.51</v>
       </c>
       <c r="J68" t="n">
-        <v>51</v>
+        <v>160</v>
       </c>
       <c r="K68" t="n">
-        <v>39.8</v>
+        <v>57.3</v>
       </c>
       <c r="L68" t="n">
-        <v>23.46</v>
+        <v>4.47</v>
       </c>
       <c r="M68" t="n">
-        <v>238</v>
+        <v>422</v>
       </c>
       <c r="N68" t="n">
-        <v>3522.75</v>
+        <v>1432.42</v>
       </c>
       <c r="O68" t="n">
-        <v>93</v>
+        <v>212</v>
       </c>
       <c r="P68" t="n">
-        <v>72.7</v>
+        <v>76</v>
       </c>
       <c r="Q68" t="n">
-        <v>14.8</v>
+        <v>3.39</v>
       </c>
       <c r="R68" t="n">
-        <v>243</v>
+        <v>585</v>
       </c>
       <c r="S68" t="n">
-        <v>3542.74</v>
+        <v>2363.63</v>
       </c>
       <c r="T68" t="n">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="U68" t="n">
-        <v>73.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="V68" t="n">
-        <v>14.58</v>
+        <v>4.04</v>
       </c>
       <c r="W68" t="n">
-        <v>26.84</v>
+        <v>8.44</v>
       </c>
       <c r="X68" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="Y68" t="n">
-        <v>4.07</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="69">
@@ -6069,80 +6039,80 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>272</v>
+        <v>114</v>
       </c>
       <c r="E69" t="n">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="F69" t="n">
-        <v>279</v>
+        <v>115</v>
       </c>
       <c r="G69" t="n">
-        <v>1821.87</v>
+        <v>1033.26</v>
       </c>
       <c r="H69" t="n">
-        <v>127</v>
+        <v>193</v>
       </c>
       <c r="I69" t="n">
-        <v>403.73</v>
+        <v>3090.93</v>
       </c>
       <c r="J69" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K69" t="n">
-        <v>35.3</v>
+        <v>79.8</v>
       </c>
       <c r="L69" t="n">
-        <v>3.18</v>
+        <v>16.02</v>
       </c>
       <c r="M69" t="n">
-        <v>127</v>
+        <v>208</v>
       </c>
       <c r="N69" t="n">
-        <v>403.73</v>
+        <v>3136.31</v>
       </c>
       <c r="O69" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P69" t="n">
-        <v>35.3</v>
+        <v>83.3</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.18</v>
+        <v>15.08</v>
       </c>
       <c r="R69" t="n">
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="S69" t="n">
-        <v>403.73</v>
+        <v>5479.43</v>
       </c>
       <c r="T69" t="n">
         <v>96</v>
       </c>
       <c r="U69" t="n">
-        <v>35.3</v>
+        <v>84.2</v>
       </c>
       <c r="V69" t="n">
-        <v>3.18</v>
+        <v>18.64</v>
       </c>
       <c r="W69" t="n">
-        <v>1.45</v>
+        <v>47.65</v>
       </c>
       <c r="X69" t="n">
-        <v>0.46</v>
+        <v>2.56</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.22</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Turmeric Ginger</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6152,78 +6122,80 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G70" t="n">
-        <v>6.68</v>
+        <v>71.83</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="inlineStr"/>
+        <v>63.6</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2.89</v>
+      </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P70" t="n">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R70" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="T70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U70" t="n">
-        <v>100</v>
+        <v>81.8</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>7.87</v>
       </c>
       <c r="X70" t="n">
-        <v>1</v>
+        <v>4.27</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Turmeric Ginger</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6233,80 +6205,80 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="E71" t="n">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="F71" t="n">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="G71" t="n">
-        <v>541.08</v>
+        <v>135.61</v>
       </c>
       <c r="H71" t="n">
-        <v>125</v>
+        <v>7</v>
       </c>
       <c r="I71" t="n">
-        <v>3354.03</v>
+        <v>24.99</v>
       </c>
       <c r="J71" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="K71" t="n">
-        <v>83.8</v>
+        <v>36.8</v>
       </c>
       <c r="L71" t="n">
-        <v>26.83</v>
+        <v>3.57</v>
       </c>
       <c r="M71" t="n">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="N71" t="n">
-        <v>3369.01</v>
+        <v>176.72</v>
       </c>
       <c r="O71" t="n">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="P71" t="n">
-        <v>86.2</v>
+        <v>89.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>24.06</v>
+        <v>5.36</v>
       </c>
       <c r="R71" t="n">
-        <v>176</v>
+        <v>33</v>
       </c>
       <c r="S71" t="n">
-        <v>3533</v>
+        <v>176.72</v>
       </c>
       <c r="T71" t="n">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="U71" t="n">
-        <v>86.2</v>
+        <v>89.5</v>
       </c>
       <c r="V71" t="n">
-        <v>20.07</v>
+        <v>5.36</v>
       </c>
       <c r="W71" t="n">
-        <v>43.62</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X71" t="n">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="Y71" t="n">
-        <v>6.53</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Turmeric Ginger</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6316,80 +6288,80 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="E72" t="n">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="F72" t="n">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G72" t="n">
-        <v>835</v>
+        <v>916.9400000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I72" t="n">
-        <v>241.54</v>
+        <v>888.63</v>
       </c>
       <c r="J72" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="K72" t="n">
-        <v>45.2</v>
+        <v>65.7</v>
       </c>
       <c r="L72" t="n">
-        <v>2.68</v>
+        <v>7.86</v>
       </c>
       <c r="M72" t="n">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="N72" t="n">
-        <v>365.69</v>
+        <v>1193.8</v>
       </c>
       <c r="O72" t="n">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="P72" t="n">
-        <v>83.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.89</v>
+        <v>7.7</v>
       </c>
       <c r="R72" t="n">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="S72" t="n">
-        <v>435.55</v>
+        <v>4492.9</v>
       </c>
       <c r="T72" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="U72" t="n">
-        <v>83.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="V72" t="n">
-        <v>1.62</v>
+        <v>17.48</v>
       </c>
       <c r="W72" t="n">
-        <v>3.48</v>
+        <v>44.48</v>
       </c>
       <c r="X72" t="n">
-        <v>2.15</v>
+        <v>2.54</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.52</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Turmeric Ginger</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6399,80 +6371,80 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D73" t="n">
+        <v>90</v>
+      </c>
+      <c r="E73" t="n">
         <v>95</v>
       </c>
-      <c r="E73" t="n">
-        <v>97</v>
-      </c>
       <c r="F73" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G73" t="n">
-        <v>647.96</v>
+        <v>792.16</v>
       </c>
       <c r="H73" t="n">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="I73" t="n">
-        <v>611.8200000000001</v>
+        <v>3735.87</v>
       </c>
       <c r="J73" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K73" t="n">
-        <v>77.90000000000001</v>
+        <v>51.1</v>
       </c>
       <c r="L73" t="n">
-        <v>4.19</v>
+        <v>53.37</v>
       </c>
       <c r="M73" t="n">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="N73" t="n">
-        <v>738.9</v>
+        <v>4040.16</v>
       </c>
       <c r="O73" t="n">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="P73" t="n">
-        <v>90.5</v>
+        <v>53.3</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.59</v>
+        <v>51.8</v>
       </c>
       <c r="R73" t="n">
-        <v>250</v>
+        <v>133</v>
       </c>
       <c r="S73" t="n">
-        <v>839.27</v>
+        <v>4806.38</v>
       </c>
       <c r="T73" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="U73" t="n">
-        <v>90.5</v>
+        <v>66.7</v>
       </c>
       <c r="V73" t="n">
-        <v>3.36</v>
+        <v>36.14</v>
       </c>
       <c r="W73" t="n">
-        <v>8.65</v>
+        <v>50.59</v>
       </c>
       <c r="X73" t="n">
-        <v>2.58</v>
+        <v>1.4</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.3</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Turmeric Ginger</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6482,80 +6454,80 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>188</v>
+        <v>36</v>
       </c>
       <c r="E74" t="n">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="F74" t="n">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="G74" t="n">
-        <v>1302.6</v>
+        <v>235.08</v>
       </c>
       <c r="H74" t="n">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="I74" t="n">
-        <v>54.37</v>
+        <v>55.21</v>
       </c>
       <c r="J74" t="n">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="K74" t="n">
-        <v>45.7</v>
+        <v>25</v>
       </c>
       <c r="L74" t="n">
-        <v>0.39</v>
+        <v>3.45</v>
       </c>
       <c r="M74" t="n">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="N74" t="n">
-        <v>369.15</v>
+        <v>132.09</v>
       </c>
       <c r="O74" t="n">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="P74" t="n">
-        <v>69.09999999999999</v>
+        <v>33.3</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.6</v>
+        <v>6.29</v>
       </c>
       <c r="R74" t="n">
-        <v>275</v>
+        <v>35</v>
       </c>
       <c r="S74" t="n">
-        <v>404.4</v>
+        <v>187.07</v>
       </c>
       <c r="T74" t="n">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="U74" t="n">
-        <v>70.2</v>
+        <v>41.7</v>
       </c>
       <c r="V74" t="n">
-        <v>1.47</v>
+        <v>5.34</v>
       </c>
       <c r="W74" t="n">
-        <v>2.07</v>
+        <v>5.2</v>
       </c>
       <c r="X74" t="n">
-        <v>1.41</v>
+        <v>0.97</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.31</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Turmeric Ginger</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6565,80 +6537,80 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>485</v>
+        <v>128</v>
       </c>
       <c r="E75" t="n">
-        <v>486</v>
+        <v>132</v>
       </c>
       <c r="F75" t="n">
-        <v>486</v>
+        <v>132</v>
       </c>
       <c r="G75" t="n">
-        <v>3246.48</v>
+        <v>869.59</v>
       </c>
       <c r="H75" t="n">
-        <v>400</v>
+        <v>97</v>
       </c>
       <c r="I75" t="n">
-        <v>415.33</v>
+        <v>2275.61</v>
       </c>
       <c r="J75" t="n">
-        <v>270</v>
+        <v>51</v>
       </c>
       <c r="K75" t="n">
-        <v>55.7</v>
+        <v>39.8</v>
       </c>
       <c r="L75" t="n">
-        <v>1.04</v>
+        <v>23.46</v>
       </c>
       <c r="M75" t="n">
-        <v>558</v>
+        <v>238</v>
       </c>
       <c r="N75" t="n">
-        <v>415.33</v>
+        <v>3522.75</v>
       </c>
       <c r="O75" t="n">
-        <v>339</v>
+        <v>93</v>
       </c>
       <c r="P75" t="n">
-        <v>69.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.74</v>
+        <v>14.8</v>
       </c>
       <c r="R75" t="n">
-        <v>633</v>
+        <v>243</v>
       </c>
       <c r="S75" t="n">
-        <v>483.73</v>
+        <v>3542.74</v>
       </c>
       <c r="T75" t="n">
-        <v>347</v>
+        <v>94</v>
       </c>
       <c r="U75" t="n">
-        <v>71.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="V75" t="n">
-        <v>0.76</v>
+        <v>14.58</v>
       </c>
       <c r="W75" t="n">
-        <v>1</v>
+        <v>26.84</v>
       </c>
       <c r="X75" t="n">
-        <v>1.3</v>
+        <v>1.84</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.15</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Turmeric Ginger</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6648,74 +6620,74 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>169</v>
+        <v>272</v>
       </c>
       <c r="E76" t="n">
-        <v>169</v>
+        <v>279</v>
       </c>
       <c r="F76" t="n">
-        <v>169</v>
+        <v>279</v>
       </c>
       <c r="G76" t="n">
-        <v>1145.04</v>
+        <v>1821.87</v>
       </c>
       <c r="H76" t="n">
-        <v>294</v>
+        <v>127</v>
       </c>
       <c r="I76" t="n">
-        <v>29.83</v>
+        <v>403.73</v>
       </c>
       <c r="J76" t="n">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="K76" t="n">
-        <v>77.5</v>
+        <v>35.3</v>
       </c>
       <c r="L76" t="n">
-        <v>0.1</v>
+        <v>3.18</v>
       </c>
       <c r="M76" t="n">
-        <v>320</v>
+        <v>127</v>
       </c>
       <c r="N76" t="n">
-        <v>69.73999999999999</v>
+        <v>403.73</v>
       </c>
       <c r="O76" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="P76" t="n">
-        <v>80.5</v>
+        <v>35.3</v>
       </c>
       <c r="Q76" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R76" t="n">
+        <v>127</v>
+      </c>
+      <c r="S76" t="n">
+        <v>403.73</v>
+      </c>
+      <c r="T76" t="n">
+        <v>96</v>
+      </c>
+      <c r="U76" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V76" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Y76" t="n">
         <v>0.22</v>
-      </c>
-      <c r="R76" t="n">
-        <v>383</v>
-      </c>
-      <c r="S76" t="n">
-        <v>89.72</v>
-      </c>
-      <c r="T76" t="n">
-        <v>138</v>
-      </c>
-      <c r="U76" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="V76" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="X76" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="77">
@@ -6731,74 +6703,72 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>116.43</v>
+        <v>6.68</v>
       </c>
       <c r="H77" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>47.89</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="L77" t="n">
-        <v>2.82</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="N77" t="n">
-        <v>47.89</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P77" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="S77" t="n">
-        <v>47.89</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V77" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>1.92</v>
+        <v>1</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6814,74 +6784,74 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="E78" t="n">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="F78" t="n">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="G78" t="n">
-        <v>80.27</v>
+        <v>541.08</v>
       </c>
       <c r="H78" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>3354.03</v>
       </c>
       <c r="J78" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="K78" t="n">
-        <v>25</v>
+        <v>83.8</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>26.83</v>
       </c>
       <c r="M78" t="n">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3369.01</v>
       </c>
       <c r="O78" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="P78" t="n">
-        <v>25</v>
+        <v>86.2</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>24.06</v>
       </c>
       <c r="R78" t="n">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>3533</v>
       </c>
       <c r="T78" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="U78" t="n">
-        <v>25</v>
+        <v>86.2</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>20.07</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>43.62</v>
       </c>
       <c r="X78" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="79">
@@ -6897,72 +6867,74 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>125</v>
       </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>125</v>
       </c>
       <c r="G79" t="n">
-        <v>53.44</v>
+        <v>835</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>241.54</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="inlineStr"/>
+        <v>45.2</v>
+      </c>
+      <c r="L79" t="n">
+        <v>2.68</v>
+      </c>
       <c r="M79" t="n">
-        <v>6</v>
+        <v>194</v>
       </c>
       <c r="N79" t="n">
-        <v>14.29</v>
+        <v>365.69</v>
       </c>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="P79" t="n">
-        <v>50</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="R79" t="n">
-        <v>6</v>
+        <v>269</v>
       </c>
       <c r="S79" t="n">
-        <v>14.29</v>
+        <v>435.55</v>
       </c>
       <c r="T79" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="U79" t="n">
-        <v>50</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="V79" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="W79" t="n">
-        <v>1.79</v>
+        <v>3.48</v>
       </c>
       <c r="X79" t="n">
-        <v>0.75</v>
+        <v>2.15</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="80">
@@ -6978,73 +6950,652 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>95</v>
+      </c>
+      <c r="E80" t="n">
+        <v>97</v>
+      </c>
+      <c r="F80" t="n">
+        <v>97</v>
+      </c>
+      <c r="G80" t="n">
+        <v>647.96</v>
+      </c>
+      <c r="H80" t="n">
+        <v>146</v>
+      </c>
+      <c r="I80" t="n">
+        <v>611.8200000000001</v>
+      </c>
+      <c r="J80" t="n">
+        <v>74</v>
+      </c>
+      <c r="K80" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="L80" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="M80" t="n">
+        <v>206</v>
+      </c>
+      <c r="N80" t="n">
+        <v>738.9</v>
+      </c>
+      <c r="O80" t="n">
+        <v>86</v>
+      </c>
+      <c r="P80" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="R80" t="n">
+        <v>250</v>
+      </c>
+      <c r="S80" t="n">
+        <v>839.27</v>
+      </c>
+      <c r="T80" t="n">
+        <v>86</v>
+      </c>
+      <c r="U80" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="V80" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="W80" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="X80" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Turmeric Ginger</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>All segments</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>188</v>
+      </c>
+      <c r="E81" t="n">
+        <v>195</v>
+      </c>
+      <c r="F81" t="n">
+        <v>195</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1302.6</v>
+      </c>
+      <c r="H81" t="n">
+        <v>139</v>
+      </c>
+      <c r="I81" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="J81" t="n">
+        <v>86</v>
+      </c>
+      <c r="K81" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M81" t="n">
+        <v>231</v>
+      </c>
+      <c r="N81" t="n">
+        <v>369.15</v>
+      </c>
+      <c r="O81" t="n">
+        <v>130</v>
+      </c>
+      <c r="P81" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R81" t="n">
+        <v>275</v>
+      </c>
+      <c r="S81" t="n">
+        <v>404.4</v>
+      </c>
+      <c r="T81" t="n">
+        <v>132</v>
+      </c>
+      <c r="U81" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W81" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="X81" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Turmeric Ginger</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>All segments</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>485</v>
+      </c>
+      <c r="E82" t="n">
+        <v>486</v>
+      </c>
+      <c r="F82" t="n">
+        <v>486</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3246.48</v>
+      </c>
+      <c r="H82" t="n">
+        <v>400</v>
+      </c>
+      <c r="I82" t="n">
+        <v>415.33</v>
+      </c>
+      <c r="J82" t="n">
+        <v>270</v>
+      </c>
+      <c r="K82" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M82" t="n">
+        <v>558</v>
+      </c>
+      <c r="N82" t="n">
+        <v>415.33</v>
+      </c>
+      <c r="O82" t="n">
+        <v>339</v>
+      </c>
+      <c r="P82" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="R82" t="n">
+        <v>633</v>
+      </c>
+      <c r="S82" t="n">
+        <v>483.73</v>
+      </c>
+      <c r="T82" t="n">
+        <v>347</v>
+      </c>
+      <c r="U82" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1</v>
+      </c>
+      <c r="X82" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Turmeric Ginger</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>All segments</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>169</v>
+      </c>
+      <c r="E83" t="n">
+        <v>169</v>
+      </c>
+      <c r="F83" t="n">
+        <v>169</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1145.04</v>
+      </c>
+      <c r="H83" t="n">
+        <v>294</v>
+      </c>
+      <c r="I83" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="J83" t="n">
+        <v>131</v>
+      </c>
+      <c r="K83" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>320</v>
+      </c>
+      <c r="N83" t="n">
+        <v>69.73999999999999</v>
+      </c>
+      <c r="O83" t="n">
+        <v>136</v>
+      </c>
+      <c r="P83" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="R83" t="n">
+        <v>383</v>
+      </c>
+      <c r="S83" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="T83" t="n">
+        <v>138</v>
+      </c>
+      <c r="U83" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="X83" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Turmeric Ginger</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>All segments</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>12</v>
+      </c>
+      <c r="E84" t="n">
+        <v>12</v>
+      </c>
+      <c r="F84" t="n">
+        <v>12</v>
+      </c>
+      <c r="G84" t="n">
+        <v>116.43</v>
+      </c>
+      <c r="H84" t="n">
+        <v>17</v>
+      </c>
+      <c r="I84" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="J84" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M84" t="n">
+        <v>23</v>
+      </c>
+      <c r="N84" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="O84" t="n">
+        <v>8</v>
+      </c>
+      <c r="P84" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R84" t="n">
+        <v>23</v>
+      </c>
+      <c r="S84" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="T84" t="n">
+        <v>8</v>
+      </c>
+      <c r="U84" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="V84" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W84" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="X84" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Turmeric Ginger</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>All segments</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>8</v>
+      </c>
+      <c r="E85" t="n">
+        <v>9</v>
+      </c>
+      <c r="F85" t="n">
+        <v>9</v>
+      </c>
+      <c r="G85" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="H85" t="n">
+        <v>5</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" t="n">
+        <v>25</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>5</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2</v>
+      </c>
+      <c r="P85" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>5</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>25</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Turmeric Ginger</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>All segments</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>8</v>
+      </c>
+      <c r="E86" t="n">
+        <v>8</v>
+      </c>
+      <c r="F86" t="n">
+        <v>8</v>
+      </c>
+      <c r="G86" t="n">
+        <v>53.44</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="n">
+        <v>6</v>
+      </c>
+      <c r="N86" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="O86" t="n">
+        <v>4</v>
+      </c>
+      <c r="P86" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6</v>
+      </c>
+      <c r="S86" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="T86" t="n">
+        <v>4</v>
+      </c>
+      <c r="U86" t="n">
+        <v>50</v>
+      </c>
+      <c r="V86" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W86" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Turmeric Ginger</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>All segments</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D87" t="n">
         <v>4</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E87" t="n">
         <v>4</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F87" t="n">
         <v>4</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G87" t="n">
         <v>26.72</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H87" t="n">
         <v>5</v>
       </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="n">
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
         <v>3</v>
       </c>
-      <c r="K80" t="n">
+      <c r="K87" t="n">
         <v>75</v>
       </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
         <v>5</v>
       </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
         <v>3</v>
       </c>
-      <c r="P80" t="n">
+      <c r="P87" t="n">
         <v>75</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
         <v>5</v>
       </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
         <v>3</v>
       </c>
-      <c r="U80" t="n">
+      <c r="U87" t="n">
         <v>75</v>
       </c>
-      <c r="V80" t="n">
-        <v>0</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" t="n">
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
         <v>1.25</v>
       </c>
-      <c r="Y80" t="n">
+      <c r="Y87" t="n">
         <v>0</v>
       </c>
     </row>

--- a/product_monthly.xlsx
+++ b/product_monthly.xlsx
@@ -648,58 +648,58 @@
         <v>5211.19</v>
       </c>
       <c r="H2">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="I2">
-        <v>196.22</v>
+        <v>441.17</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K2">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="L2">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="M2">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="N2">
-        <v>196.22</v>
+        <v>441.17</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="P2">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="Q2">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="R2">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="S2">
-        <v>196.22</v>
+        <v>441.17</v>
       </c>
       <c r="T2">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="U2">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="V2">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="W2">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="X2">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
       <c r="Y2">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1288,7 +1288,7 @@
         <v>388</v>
       </c>
       <c r="S10">
-        <v>15216.18</v>
+        <v>15201.9</v>
       </c>
       <c r="T10">
         <v>58</v>
@@ -1297,16 +1297,16 @@
         <v>82.90000000000001</v>
       </c>
       <c r="V10">
-        <v>39.22</v>
+        <v>39.18</v>
       </c>
       <c r="W10">
-        <v>208.44</v>
+        <v>208.25</v>
       </c>
       <c r="X10">
         <v>5.32</v>
       </c>
       <c r="Y10">
-        <v>36.63</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1439,10 +1439,10 @@
         <v>126.5</v>
       </c>
       <c r="R12">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="S12">
-        <v>198426.89</v>
+        <v>198403.05</v>
       </c>
       <c r="T12">
         <v>294</v>
@@ -1451,16 +1451,16 @@
         <v>68.09999999999999</v>
       </c>
       <c r="V12">
-        <v>150.32</v>
+        <v>150.53</v>
       </c>
       <c r="W12">
-        <v>449.95</v>
+        <v>449.89</v>
       </c>
       <c r="X12">
         <v>2.99</v>
       </c>
       <c r="Y12">
-        <v>78.34999999999999</v>
+        <v>78.34</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1516,7 +1516,7 @@
         <v>11.45</v>
       </c>
       <c r="R13">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="S13">
         <v>32925.95</v>
@@ -1528,7 +1528,7 @@
         <v>62.1</v>
       </c>
       <c r="V13">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="W13">
         <v>56.67</v>
@@ -1593,28 +1593,28 @@
         <v>19.52</v>
       </c>
       <c r="R14">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="S14">
-        <v>56922.42</v>
+        <v>56952.75</v>
       </c>
       <c r="T14">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U14">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="V14">
-        <v>42.48</v>
+        <v>42.47</v>
       </c>
       <c r="W14">
-        <v>88.94</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="X14">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Y14">
-        <v>15.54</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1670,10 +1670,10 @@
         <v>4.71</v>
       </c>
       <c r="R15">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="S15">
-        <v>16978.37</v>
+        <v>17033.4</v>
       </c>
       <c r="T15">
         <v>257</v>
@@ -1682,16 +1682,16 @@
         <v>59.9</v>
       </c>
       <c r="V15">
-        <v>23.81</v>
+        <v>23.86</v>
       </c>
       <c r="W15">
-        <v>39.21</v>
+        <v>39.34</v>
       </c>
       <c r="X15">
         <v>1.65</v>
       </c>
       <c r="Y15">
-        <v>6.83</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1797,7 +1797,7 @@
         <v>690</v>
       </c>
       <c r="I17">
-        <v>6534.6</v>
+        <v>6562.6</v>
       </c>
       <c r="J17">
         <v>381</v>
@@ -1806,13 +1806,13 @@
         <v>56.1</v>
       </c>
       <c r="L17">
-        <v>9.470000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="M17">
         <v>936</v>
       </c>
       <c r="N17">
-        <v>16084.79</v>
+        <v>16112.79</v>
       </c>
       <c r="O17">
         <v>467</v>
@@ -1821,13 +1821,13 @@
         <v>68.8</v>
       </c>
       <c r="Q17">
-        <v>17.18</v>
+        <v>17.21</v>
       </c>
       <c r="R17">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="S17">
-        <v>29119.55</v>
+        <v>29147.55</v>
       </c>
       <c r="T17">
         <v>475</v>
@@ -1836,16 +1836,16 @@
         <v>70</v>
       </c>
       <c r="V17">
-        <v>22.73</v>
+        <v>22.74</v>
       </c>
       <c r="W17">
-        <v>42.57</v>
+        <v>42.61</v>
       </c>
       <c r="X17">
         <v>1.87</v>
       </c>
       <c r="Y17">
-        <v>7.44</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1901,10 +1901,10 @@
         <v>29.07</v>
       </c>
       <c r="R18">
-        <v>4035</v>
+        <v>4029</v>
       </c>
       <c r="S18">
-        <v>98287.21000000001</v>
+        <v>98145.05</v>
       </c>
       <c r="T18">
         <v>1205</v>
@@ -1916,13 +1916,13 @@
         <v>24.36</v>
       </c>
       <c r="W18">
-        <v>67.27</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="X18">
         <v>2.76</v>
       </c>
       <c r="Y18">
-        <v>11.81</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1978,7 +1978,7 @@
         <v>37.91</v>
       </c>
       <c r="R19">
-        <v>3098</v>
+        <v>3093</v>
       </c>
       <c r="S19">
         <v>98166.2</v>
@@ -1990,13 +1990,13 @@
         <v>87.3</v>
       </c>
       <c r="V19">
-        <v>31.69</v>
+        <v>31.74</v>
       </c>
       <c r="W19">
         <v>100.07</v>
       </c>
       <c r="X19">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="Y19">
         <v>17.58</v>
@@ -2043,7 +2043,7 @@
         <v>1484</v>
       </c>
       <c r="N20">
-        <v>19351.9</v>
+        <v>19327.14</v>
       </c>
       <c r="O20">
         <v>590</v>
@@ -2052,31 +2052,31 @@
         <v>89.3</v>
       </c>
       <c r="Q20">
-        <v>13.04</v>
+        <v>13.02</v>
       </c>
       <c r="R20">
-        <v>1987</v>
+        <v>1983</v>
       </c>
       <c r="S20">
-        <v>32249.45</v>
+        <v>32811.79</v>
       </c>
       <c r="T20">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="U20">
-        <v>90.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="V20">
-        <v>16.23</v>
+        <v>16.55</v>
       </c>
       <c r="W20">
-        <v>47.15</v>
+        <v>47.97</v>
       </c>
       <c r="X20">
         <v>2.9</v>
       </c>
       <c r="Y20">
-        <v>8.289999999999999</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2105,7 +2105,7 @@
         <v>2840</v>
       </c>
       <c r="I21">
-        <v>28289.48</v>
+        <v>28315.49</v>
       </c>
       <c r="J21">
         <v>1508</v>
@@ -2114,13 +2114,13 @@
         <v>47.2</v>
       </c>
       <c r="L21">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M21">
         <v>4959</v>
       </c>
       <c r="N21">
-        <v>35202.98</v>
+        <v>35064.66</v>
       </c>
       <c r="O21">
         <v>2292</v>
@@ -2129,25 +2129,25 @@
         <v>71.7</v>
       </c>
       <c r="Q21">
-        <v>7.1</v>
+        <v>7.07</v>
       </c>
       <c r="R21">
-        <v>5437</v>
+        <v>5444</v>
       </c>
       <c r="S21">
-        <v>37655.33</v>
+        <v>37592.9</v>
       </c>
       <c r="T21">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="U21">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="V21">
-        <v>6.93</v>
+        <v>6.91</v>
       </c>
       <c r="W21">
-        <v>11.49</v>
+        <v>11.47</v>
       </c>
       <c r="X21">
         <v>1.66</v>
@@ -2182,7 +2182,7 @@
         <v>1539</v>
       </c>
       <c r="I22">
-        <v>5951.25</v>
+        <v>5824.57</v>
       </c>
       <c r="J22">
         <v>896</v>
@@ -2191,46 +2191,46 @@
         <v>43.1</v>
       </c>
       <c r="L22">
+        <v>3.78</v>
+      </c>
+      <c r="M22">
+        <v>1559</v>
+      </c>
+      <c r="N22">
+        <v>6037.15</v>
+      </c>
+      <c r="O22">
+        <v>906</v>
+      </c>
+      <c r="P22">
+        <v>43.6</v>
+      </c>
+      <c r="Q22">
         <v>3.87</v>
       </c>
-      <c r="M22">
-        <v>1577</v>
-      </c>
-      <c r="N22">
-        <v>6726.99</v>
-      </c>
-      <c r="O22">
-        <v>914</v>
-      </c>
-      <c r="P22">
-        <v>44</v>
-      </c>
-      <c r="Q22">
-        <v>4.27</v>
-      </c>
       <c r="R22">
-        <v>2326</v>
+        <v>2315</v>
       </c>
       <c r="S22">
-        <v>23802.53</v>
+        <v>23918.41</v>
       </c>
       <c r="T22">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="U22">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
       <c r="V22">
-        <v>10.23</v>
+        <v>10.33</v>
       </c>
       <c r="W22">
-        <v>10.85</v>
+        <v>10.91</v>
       </c>
       <c r="X22">
         <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2256,58 +2256,58 @@
         <v>7754.45</v>
       </c>
       <c r="H23">
-        <v>784</v>
+        <v>595</v>
       </c>
       <c r="I23">
-        <v>31854.77</v>
+        <v>27431.21</v>
       </c>
       <c r="J23">
-        <v>419</v>
+        <v>348</v>
       </c>
       <c r="K23">
-        <v>46.3</v>
+        <v>38.5</v>
       </c>
       <c r="L23">
-        <v>40.63</v>
+        <v>46.1</v>
       </c>
       <c r="M23">
-        <v>1220</v>
+        <v>1054</v>
       </c>
       <c r="N23">
-        <v>40995.79</v>
+        <v>37182.04</v>
       </c>
       <c r="O23">
-        <v>523</v>
+        <v>462</v>
       </c>
       <c r="P23">
-        <v>57.9</v>
+        <v>51.1</v>
       </c>
       <c r="Q23">
-        <v>33.6</v>
+        <v>35.28</v>
       </c>
       <c r="R23">
-        <v>1941</v>
+        <v>1829</v>
       </c>
       <c r="S23">
-        <v>70282.64</v>
+        <v>68807.3</v>
       </c>
       <c r="T23">
-        <v>570</v>
+        <v>525</v>
       </c>
       <c r="U23">
-        <v>63.1</v>
+        <v>58.1</v>
       </c>
       <c r="V23">
-        <v>36.21</v>
+        <v>37.62</v>
       </c>
       <c r="W23">
-        <v>71.56999999999999</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="X23">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="Y23">
-        <v>9.06</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2333,10 +2333,10 @@
         <v>2114.42</v>
       </c>
       <c r="H24">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I24">
-        <v>4197.09</v>
+        <v>4335.15</v>
       </c>
       <c r="J24">
         <v>204</v>
@@ -2345,13 +2345,13 @@
         <v>61.4</v>
       </c>
       <c r="L24">
-        <v>8.800000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M24">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="N24">
-        <v>4992.06</v>
+        <v>5130.12</v>
       </c>
       <c r="O24">
         <v>256</v>
@@ -2360,13 +2360,13 @@
         <v>77.09999999999999</v>
       </c>
       <c r="Q24">
-        <v>7.51</v>
+        <v>7.67</v>
       </c>
       <c r="R24">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="S24">
-        <v>5277.33</v>
+        <v>5560.22</v>
       </c>
       <c r="T24">
         <v>256</v>
@@ -2375,16 +2375,16 @@
         <v>77.09999999999999</v>
       </c>
       <c r="V24">
-        <v>7.6</v>
+        <v>7.85</v>
       </c>
       <c r="W24">
-        <v>14.46</v>
+        <v>15.23</v>
       </c>
       <c r="X24">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Y24">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2410,58 +2410,58 @@
         <v>5801.06</v>
       </c>
       <c r="H25">
-        <v>451</v>
+        <v>678</v>
       </c>
       <c r="I25">
-        <v>2315.31</v>
+        <v>4085.54</v>
       </c>
       <c r="J25">
-        <v>243</v>
+        <v>344</v>
       </c>
       <c r="K25">
-        <v>29.5</v>
+        <v>41.7</v>
       </c>
       <c r="L25">
-        <v>5.13</v>
+        <v>6.03</v>
       </c>
       <c r="M25">
-        <v>451</v>
+        <v>678</v>
       </c>
       <c r="N25">
-        <v>2315.31</v>
+        <v>4085.54</v>
       </c>
       <c r="O25">
-        <v>243</v>
+        <v>344</v>
       </c>
       <c r="P25">
-        <v>29.5</v>
+        <v>41.7</v>
       </c>
       <c r="Q25">
-        <v>5.13</v>
+        <v>6.03</v>
       </c>
       <c r="R25">
-        <v>451</v>
+        <v>678</v>
       </c>
       <c r="S25">
-        <v>2315.31</v>
+        <v>4085.54</v>
       </c>
       <c r="T25">
-        <v>243</v>
+        <v>344</v>
       </c>
       <c r="U25">
-        <v>29.5</v>
+        <v>41.7</v>
       </c>
       <c r="V25">
-        <v>5.13</v>
+        <v>6.03</v>
       </c>
       <c r="W25">
-        <v>2.52</v>
+        <v>4.46</v>
       </c>
       <c r="X25">
-        <v>0.49</v>
+        <v>0.74</v>
       </c>
       <c r="Y25">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2502,7 +2502,7 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>27.05</v>
+        <v>37.02</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -2511,13 +2511,13 @@
         <v>47.1</v>
       </c>
       <c r="Q26">
-        <v>2.71</v>
+        <v>3.7</v>
       </c>
       <c r="R26">
         <v>12</v>
       </c>
       <c r="S26">
-        <v>27.05</v>
+        <v>37.02</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2526,10 +2526,10 @@
         <v>52.9</v>
       </c>
       <c r="V26">
-        <v>2.25</v>
+        <v>3.09</v>
       </c>
       <c r="W26">
-        <v>1.59</v>
+        <v>2.18</v>
       </c>
       <c r="X26">
         <v>0.71</v>
@@ -3017,7 +3017,7 @@
         <v>896</v>
       </c>
       <c r="N33">
-        <v>50933.59</v>
+        <v>50726.28</v>
       </c>
       <c r="O33">
         <v>378</v>
@@ -3026,13 +3026,13 @@
         <v>88.5</v>
       </c>
       <c r="Q33">
-        <v>56.85</v>
+        <v>56.61</v>
       </c>
       <c r="R33">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="S33">
-        <v>64842.26</v>
+        <v>64164.93</v>
       </c>
       <c r="T33">
         <v>385</v>
@@ -3041,16 +3041,16 @@
         <v>90.2</v>
       </c>
       <c r="V33">
-        <v>53.32</v>
+        <v>52.9</v>
       </c>
       <c r="W33">
-        <v>151.5</v>
+        <v>149.92</v>
       </c>
       <c r="X33">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="Y33">
-        <v>26.28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3079,7 +3079,7 @@
         <v>830</v>
       </c>
       <c r="I34">
-        <v>53790.47</v>
+        <v>53769.34</v>
       </c>
       <c r="J34">
         <v>355</v>
@@ -3088,13 +3088,13 @@
         <v>86</v>
       </c>
       <c r="L34">
-        <v>64.81</v>
+        <v>64.78</v>
       </c>
       <c r="M34">
         <v>971</v>
       </c>
       <c r="N34">
-        <v>55864.97</v>
+        <v>55843.84</v>
       </c>
       <c r="O34">
         <v>371</v>
@@ -3103,13 +3103,13 @@
         <v>89.8</v>
       </c>
       <c r="Q34">
-        <v>57.53</v>
+        <v>57.51</v>
       </c>
       <c r="R34">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="S34">
-        <v>64062.1</v>
+        <v>63597.33</v>
       </c>
       <c r="T34">
         <v>374</v>
@@ -3118,16 +3118,16 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V34">
-        <v>53.65</v>
+        <v>53.44</v>
       </c>
       <c r="W34">
-        <v>153.63</v>
+        <v>152.51</v>
       </c>
       <c r="X34">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="Y34">
-        <v>27.16</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3153,58 +3153,58 @@
         <v>3530.64</v>
       </c>
       <c r="H35">
-        <v>481</v>
+        <v>384</v>
       </c>
       <c r="I35">
-        <v>24830.64</v>
+        <v>22164.87</v>
       </c>
       <c r="J35">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="K35">
-        <v>43.5</v>
+        <v>36.4</v>
       </c>
       <c r="L35">
-        <v>51.62</v>
+        <v>57.72</v>
       </c>
       <c r="M35">
-        <v>771</v>
+        <v>690</v>
       </c>
       <c r="N35">
-        <v>35500.57</v>
+        <v>33183.04</v>
       </c>
       <c r="O35">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="P35">
-        <v>55.4</v>
+        <v>50.1</v>
       </c>
       <c r="Q35">
-        <v>46.04</v>
+        <v>48.09</v>
       </c>
       <c r="R35">
-        <v>1210</v>
+        <v>1153</v>
       </c>
       <c r="S35">
-        <v>44602.85</v>
+        <v>43168.75</v>
       </c>
       <c r="T35">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="U35">
-        <v>59.1</v>
+        <v>55.5</v>
       </c>
       <c r="V35">
-        <v>36.86</v>
+        <v>37.44</v>
       </c>
       <c r="W35">
-        <v>71.25</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="X35">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="Y35">
-        <v>12.63</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3230,10 +3230,10 @@
         <v>1923.24</v>
       </c>
       <c r="H36">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I36">
-        <v>18138.35</v>
+        <v>18390.77</v>
       </c>
       <c r="J36">
         <v>175</v>
@@ -3242,46 +3242,46 @@
         <v>52.7</v>
       </c>
       <c r="L36">
-        <v>45.35</v>
+        <v>45.75</v>
       </c>
       <c r="M36">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="N36">
-        <v>20493.93</v>
+        <v>20813.87</v>
       </c>
       <c r="O36">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P36">
-        <v>73.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Q36">
-        <v>34.16</v>
+        <v>34.35</v>
       </c>
       <c r="R36">
-        <v>661</v>
+        <v>680</v>
       </c>
       <c r="S36">
-        <v>21181.58</v>
+        <v>21676.35</v>
       </c>
       <c r="T36">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="U36">
-        <v>74.7</v>
+        <v>75.3</v>
       </c>
       <c r="V36">
-        <v>32.04</v>
+        <v>31.88</v>
       </c>
       <c r="W36">
-        <v>62.12</v>
+        <v>63.57</v>
       </c>
       <c r="X36">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="Y36">
-        <v>11.01</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3307,58 +3307,58 @@
         <v>2205.24</v>
       </c>
       <c r="H37">
-        <v>229</v>
+        <v>291</v>
       </c>
       <c r="I37">
-        <v>2679.72</v>
+        <v>3180.48</v>
       </c>
       <c r="J37">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="K37">
-        <v>38.4</v>
+        <v>47</v>
       </c>
       <c r="L37">
-        <v>11.7</v>
+        <v>10.93</v>
       </c>
       <c r="M37">
-        <v>229</v>
+        <v>291</v>
       </c>
       <c r="N37">
-        <v>2679.72</v>
+        <v>3180.48</v>
       </c>
       <c r="O37">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="P37">
-        <v>38.4</v>
+        <v>47</v>
       </c>
       <c r="Q37">
-        <v>11.7</v>
+        <v>10.93</v>
       </c>
       <c r="R37">
-        <v>229</v>
+        <v>291</v>
       </c>
       <c r="S37">
-        <v>2679.72</v>
+        <v>3180.48</v>
       </c>
       <c r="T37">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="U37">
-        <v>38.4</v>
+        <v>47</v>
       </c>
       <c r="V37">
-        <v>11.7</v>
+        <v>10.93</v>
       </c>
       <c r="W37">
-        <v>6.85</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="X37">
-        <v>0.59</v>
+        <v>0.74</v>
       </c>
       <c r="Y37">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3387,7 +3387,7 @@
         <v>16</v>
       </c>
       <c r="I38">
-        <v>789.45</v>
+        <v>780.78</v>
       </c>
       <c r="J38">
         <v>8</v>
@@ -3396,13 +3396,13 @@
         <v>26.7</v>
       </c>
       <c r="L38">
-        <v>49.34</v>
+        <v>48.8</v>
       </c>
       <c r="M38">
         <v>16</v>
       </c>
       <c r="N38">
-        <v>789.45</v>
+        <v>780.78</v>
       </c>
       <c r="O38">
         <v>8</v>
@@ -3411,31 +3411,31 @@
         <v>26.7</v>
       </c>
       <c r="Q38">
-        <v>49.34</v>
+        <v>48.8</v>
       </c>
       <c r="R38">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="S38">
-        <v>8073.8</v>
+        <v>7891.75</v>
       </c>
       <c r="T38">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U38">
-        <v>56.7</v>
+        <v>53.3</v>
       </c>
       <c r="V38">
-        <v>61.17</v>
+        <v>62.63</v>
       </c>
       <c r="W38">
-        <v>269.13</v>
+        <v>263.06</v>
       </c>
       <c r="X38">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Y38">
-        <v>30</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3461,58 +3461,58 @@
         <v>4637.49</v>
       </c>
       <c r="H39">
-        <v>294</v>
+        <v>202</v>
       </c>
       <c r="I39">
-        <v>2872.62</v>
+        <v>2398.41</v>
       </c>
       <c r="J39">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="K39">
-        <v>41.9</v>
+        <v>30.2</v>
       </c>
       <c r="L39">
-        <v>9.77</v>
+        <v>11.87</v>
       </c>
       <c r="M39">
-        <v>471</v>
+        <v>395</v>
       </c>
       <c r="N39">
-        <v>17113.88</v>
+        <v>16672.47</v>
       </c>
       <c r="O39">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="P39">
-        <v>52.9</v>
+        <v>43.8</v>
       </c>
       <c r="Q39">
-        <v>36.34</v>
+        <v>42.21</v>
       </c>
       <c r="R39">
-        <v>601</v>
+        <v>532</v>
       </c>
       <c r="S39">
-        <v>18907.97</v>
+        <v>18579.68</v>
       </c>
       <c r="T39">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="U39">
-        <v>55</v>
+        <v>46.9</v>
       </c>
       <c r="V39">
-        <v>31.46</v>
+        <v>34.92</v>
       </c>
       <c r="W39">
-        <v>36.57</v>
+        <v>35.94</v>
       </c>
       <c r="X39">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3550,40 +3550,40 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N40">
         <v>233.34</v>
       </c>
       <c r="O40">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P40">
-        <v>68.8</v>
+        <v>75</v>
       </c>
       <c r="Q40">
-        <v>8.33</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R40">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S40">
         <v>233.34</v>
       </c>
       <c r="T40">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U40">
-        <v>75</v>
+        <v>81.2</v>
       </c>
       <c r="V40">
-        <v>8.050000000000001</v>
+        <v>7.78</v>
       </c>
       <c r="W40">
         <v>14.58</v>
       </c>
       <c r="X40">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="Y40">
         <v>1.63</v>
@@ -3612,58 +3612,58 @@
         <v>3130.53</v>
       </c>
       <c r="H41">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="I41">
-        <v>203.36</v>
+        <v>297.37</v>
       </c>
       <c r="J41">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="K41">
-        <v>37.8</v>
+        <v>45</v>
       </c>
       <c r="L41">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="M41">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="N41">
-        <v>203.36</v>
+        <v>297.37</v>
       </c>
       <c r="O41">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="P41">
-        <v>37.8</v>
+        <v>45</v>
       </c>
       <c r="Q41">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="R41">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="S41">
-        <v>203.36</v>
+        <v>297.37</v>
       </c>
       <c r="T41">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="U41">
-        <v>37.8</v>
+        <v>45</v>
       </c>
       <c r="V41">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="W41">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="X41">
-        <v>0.48</v>
+        <v>0.6</v>
       </c>
       <c r="Y41">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3766,7 +3766,7 @@
         <v>23</v>
       </c>
       <c r="I43">
-        <v>233.08</v>
+        <v>233.12</v>
       </c>
       <c r="J43">
         <v>15</v>
@@ -3775,28 +3775,28 @@
         <v>21.7</v>
       </c>
       <c r="L43">
-        <v>10.13</v>
+        <v>10.14</v>
       </c>
       <c r="M43">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="N43">
-        <v>422.37</v>
+        <v>312.49</v>
       </c>
       <c r="O43">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="P43">
-        <v>36.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q43">
-        <v>10.3</v>
+        <v>10.08</v>
       </c>
       <c r="R43">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S43">
-        <v>2676.72</v>
+        <v>2458.74</v>
       </c>
       <c r="T43">
         <v>37</v>
@@ -3805,16 +3805,16 @@
         <v>53.6</v>
       </c>
       <c r="V43">
-        <v>19.68</v>
+        <v>18.35</v>
       </c>
       <c r="W43">
-        <v>38.79</v>
+        <v>35.63</v>
       </c>
       <c r="X43">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Y43">
-        <v>8.199999999999999</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3840,58 +3840,58 @@
         <v>600.71</v>
       </c>
       <c r="H44">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="I44">
-        <v>2982.93</v>
+        <v>2090.5</v>
       </c>
       <c r="J44">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="K44">
-        <v>39.4</v>
+        <v>32.3</v>
       </c>
       <c r="L44">
-        <v>35.51</v>
+        <v>36.04</v>
       </c>
       <c r="M44">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="N44">
-        <v>3411.9</v>
+        <v>2589.94</v>
       </c>
       <c r="O44">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="P44">
-        <v>49.6</v>
+        <v>42.5</v>
       </c>
       <c r="Q44">
-        <v>27.74</v>
+        <v>26.43</v>
       </c>
       <c r="R44">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="S44">
-        <v>3711.1</v>
+        <v>2903.58</v>
       </c>
       <c r="T44">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="U44">
-        <v>52.8</v>
+        <v>45.7</v>
       </c>
       <c r="V44">
-        <v>22.63</v>
+        <v>20.02</v>
       </c>
       <c r="W44">
-        <v>29.22</v>
+        <v>22.86</v>
       </c>
       <c r="X44">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Y44">
-        <v>6.18</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -3985,58 +3985,58 @@
         <v>184.47</v>
       </c>
       <c r="H46">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I46">
-        <v>101.05</v>
+        <v>130.55</v>
       </c>
       <c r="J46">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K46">
-        <v>48.7</v>
+        <v>59</v>
       </c>
       <c r="L46">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
       <c r="M46">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="N46">
-        <v>101.05</v>
+        <v>130.55</v>
       </c>
       <c r="O46">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="P46">
-        <v>48.7</v>
+        <v>59</v>
       </c>
       <c r="Q46">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
       <c r="R46">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="S46">
-        <v>101.05</v>
+        <v>130.55</v>
       </c>
       <c r="T46">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="U46">
-        <v>48.7</v>
+        <v>59</v>
       </c>
       <c r="V46">
-        <v>3.61</v>
+        <v>3.73</v>
       </c>
       <c r="W46">
-        <v>2.59</v>
+        <v>3.35</v>
       </c>
       <c r="X46">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="Y46">
-        <v>0.55</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -4352,46 +4352,46 @@
         <v>0</v>
       </c>
       <c r="H51">
+        <v>5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
         <v>4</v>
       </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>3</v>
-      </c>
       <c r="K51">
-        <v>18.8</v>
+        <v>25</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
       <c r="M51">
+        <v>5</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
         <v>4</v>
       </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>3</v>
-      </c>
       <c r="P51">
-        <v>18.8</v>
+        <v>25</v>
       </c>
       <c r="Q51">
         <v>0</v>
       </c>
       <c r="R51">
+        <v>5</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
         <v>4</v>
       </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
-        <v>3</v>
-      </c>
       <c r="U51">
-        <v>18.8</v>
+        <v>25</v>
       </c>
       <c r="V51">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="X51">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="52" spans="1:25">
@@ -4441,7 +4441,7 @@
         <v>12</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="O52">
         <v>9</v>
@@ -4450,13 +4450,13 @@
         <v>37.5</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="R52">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S52">
-        <v>163.25</v>
+        <v>352.27</v>
       </c>
       <c r="T52">
         <v>11</v>
@@ -4465,13 +4465,13 @@
         <v>45.8</v>
       </c>
       <c r="V52">
-        <v>8.59</v>
+        <v>17.61</v>
       </c>
       <c r="W52">
-        <v>6.8</v>
+        <v>14.68</v>
       </c>
       <c r="X52">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="53" spans="1:25">
@@ -4497,55 +4497,55 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>28.94</v>
       </c>
       <c r="J53">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K53">
-        <v>37.5</v>
+        <v>68.8</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M53">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>28.94</v>
       </c>
       <c r="O53">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P53">
-        <v>37.5</v>
+        <v>68.8</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R53">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>28.94</v>
       </c>
       <c r="T53">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="U53">
-        <v>37.5</v>
+        <v>68.8</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="X53">
-        <v>0.5</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:25">
@@ -4574,7 +4574,7 @@
         <v>24</v>
       </c>
       <c r="I54">
-        <v>150.02</v>
+        <v>160.02</v>
       </c>
       <c r="J54">
         <v>13</v>
@@ -4583,46 +4583,46 @@
         <v>8.300000000000001</v>
       </c>
       <c r="L54">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="M54">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N54">
-        <v>495.66</v>
+        <v>519.96</v>
       </c>
       <c r="O54">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P54">
-        <v>53.5</v>
+        <v>54.1</v>
       </c>
       <c r="Q54">
-        <v>3.54</v>
+        <v>3.66</v>
       </c>
       <c r="R54">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="S54">
-        <v>509.21</v>
+        <v>533.51</v>
       </c>
       <c r="T54">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U54">
-        <v>53.5</v>
+        <v>54.8</v>
       </c>
       <c r="V54">
-        <v>3.59</v>
+        <v>3.68</v>
       </c>
       <c r="W54">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="X54">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="Y54">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="55" spans="1:25">
@@ -4648,58 +4648,58 @@
         <v>3321.69</v>
       </c>
       <c r="H55">
-        <v>237</v>
+        <v>329</v>
       </c>
       <c r="I55">
-        <v>233.44</v>
+        <v>548.37</v>
       </c>
       <c r="J55">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="K55">
-        <v>34.4</v>
+        <v>43.9</v>
       </c>
       <c r="L55">
-        <v>0.98</v>
+        <v>1.67</v>
       </c>
       <c r="M55">
-        <v>237</v>
+        <v>329</v>
       </c>
       <c r="N55">
-        <v>233.44</v>
+        <v>548.37</v>
       </c>
       <c r="O55">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="P55">
-        <v>34.4</v>
+        <v>43.9</v>
       </c>
       <c r="Q55">
-        <v>0.98</v>
+        <v>1.67</v>
       </c>
       <c r="R55">
-        <v>237</v>
+        <v>329</v>
       </c>
       <c r="S55">
-        <v>233.44</v>
+        <v>548.37</v>
       </c>
       <c r="T55">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="U55">
-        <v>34.4</v>
+        <v>43.9</v>
       </c>
       <c r="V55">
-        <v>0.98</v>
+        <v>1.67</v>
       </c>
       <c r="W55">
-        <v>0.45</v>
+        <v>1.06</v>
       </c>
       <c r="X55">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="Y55">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="56" spans="1:25">
@@ -4740,25 +4740,25 @@
         <v>23.21</v>
       </c>
       <c r="M56">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N56">
-        <v>1023.05</v>
+        <v>596.78</v>
       </c>
       <c r="O56">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P56">
-        <v>23</v>
+        <v>19.7</v>
       </c>
       <c r="Q56">
-        <v>24.36</v>
+        <v>19.25</v>
       </c>
       <c r="R56">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="S56">
-        <v>2720.56</v>
+        <v>2632.63</v>
       </c>
       <c r="T56">
         <v>28</v>
@@ -4767,16 +4767,16 @@
         <v>45.9</v>
       </c>
       <c r="V56">
-        <v>24.73</v>
+        <v>24.84</v>
       </c>
       <c r="W56">
-        <v>43.88</v>
+        <v>42.46</v>
       </c>
       <c r="X56">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Y56">
-        <v>8.970000000000001</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="57" spans="1:25">
@@ -4802,55 +4802,55 @@
         <v>694.98</v>
       </c>
       <c r="H57">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="I57">
-        <v>333.39</v>
+        <v>215.44</v>
       </c>
       <c r="J57">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="K57">
-        <v>38.5</v>
+        <v>28.7</v>
       </c>
       <c r="L57">
-        <v>3.97</v>
+        <v>3.78</v>
       </c>
       <c r="M57">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="N57">
-        <v>904.87</v>
+        <v>826.91</v>
       </c>
       <c r="O57">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="P57">
-        <v>49</v>
+        <v>39.9</v>
       </c>
       <c r="Q57">
-        <v>7.12</v>
+        <v>8.19</v>
       </c>
       <c r="R57">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="S57">
-        <v>1286.77</v>
+        <v>1288.82</v>
       </c>
       <c r="T57">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U57">
-        <v>55.9</v>
+        <v>49.7</v>
       </c>
       <c r="V57">
-        <v>7.11</v>
+        <v>8.06</v>
       </c>
       <c r="W57">
-        <v>9</v>
+        <v>9.01</v>
       </c>
       <c r="X57">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="Y57">
         <v>1.85</v>
@@ -4882,7 +4882,7 @@
         <v>76</v>
       </c>
       <c r="I58">
-        <v>2181.91</v>
+        <v>2301.42</v>
       </c>
       <c r="J58">
         <v>36</v>
@@ -4891,13 +4891,13 @@
         <v>49.3</v>
       </c>
       <c r="L58">
-        <v>28.71</v>
+        <v>30.28</v>
       </c>
       <c r="M58">
         <v>149</v>
       </c>
       <c r="N58">
-        <v>3748.85</v>
+        <v>4135.91</v>
       </c>
       <c r="O58">
         <v>61</v>
@@ -4906,13 +4906,13 @@
         <v>83.59999999999999</v>
       </c>
       <c r="Q58">
-        <v>25.16</v>
+        <v>27.76</v>
       </c>
       <c r="R58">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="S58">
-        <v>3869.86</v>
+        <v>4274.16</v>
       </c>
       <c r="T58">
         <v>61</v>
@@ -4921,16 +4921,16 @@
         <v>83.59999999999999</v>
       </c>
       <c r="V58">
-        <v>24.04</v>
+        <v>26.22</v>
       </c>
       <c r="W58">
-        <v>53.01</v>
+        <v>58.55</v>
       </c>
       <c r="X58">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="Y58">
-        <v>10.91</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="59" spans="1:25">
@@ -4956,58 +4956,58 @@
         <v>194.4</v>
       </c>
       <c r="H59">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I59">
-        <v>34.66</v>
+        <v>63.43</v>
       </c>
       <c r="J59">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K59">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="L59">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="M59">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N59">
-        <v>34.66</v>
+        <v>63.43</v>
       </c>
       <c r="O59">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P59">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="Q59">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="R59">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S59">
-        <v>34.66</v>
+        <v>63.43</v>
       </c>
       <c r="T59">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U59">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="V59">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="W59">
-        <v>0.87</v>
+        <v>1.59</v>
       </c>
       <c r="X59">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Y59">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="60" spans="1:25">
@@ -5033,46 +5033,46 @@
         <v>0</v>
       </c>
       <c r="H60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K60">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N60">
         <v>0</v>
       </c>
       <c r="O60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P60">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="Q60">
         <v>0</v>
       </c>
       <c r="R60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60">
         <v>0</v>
       </c>
       <c r="T60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U60">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -5081,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="X60">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="61" spans="1:25">
@@ -5214,10 +5214,10 @@
         <v>3.39</v>
       </c>
       <c r="R62">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="S62">
-        <v>2363.63</v>
+        <v>2382.73</v>
       </c>
       <c r="T62">
         <v>214</v>
@@ -5226,16 +5226,16 @@
         <v>76.7</v>
       </c>
       <c r="V62">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="W62">
-        <v>8.44</v>
+        <v>8.51</v>
       </c>
       <c r="X62">
         <v>2.09</v>
       </c>
       <c r="Y62">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="63" spans="1:25">
@@ -5291,7 +5291,7 @@
         <v>15.08</v>
       </c>
       <c r="R63">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S63">
         <v>5479.43</v>
@@ -5303,13 +5303,13 @@
         <v>84.2</v>
       </c>
       <c r="V63">
-        <v>18.64</v>
+        <v>18.77</v>
       </c>
       <c r="W63">
         <v>47.65</v>
       </c>
       <c r="X63">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Y63">
         <v>5.3</v>
@@ -5495,7 +5495,7 @@
         <v>113</v>
       </c>
       <c r="I66">
-        <v>888.63</v>
+        <v>869.5700000000001</v>
       </c>
       <c r="J66">
         <v>65</v>
@@ -5504,13 +5504,13 @@
         <v>65.7</v>
       </c>
       <c r="L66">
-        <v>7.86</v>
+        <v>7.7</v>
       </c>
       <c r="M66">
         <v>155</v>
       </c>
       <c r="N66">
-        <v>1193.8</v>
+        <v>1174.74</v>
       </c>
       <c r="O66">
         <v>78</v>
@@ -5519,13 +5519,13 @@
         <v>78.8</v>
       </c>
       <c r="Q66">
-        <v>7.7</v>
+        <v>7.58</v>
       </c>
       <c r="R66">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S66">
-        <v>4492.9</v>
+        <v>4433.84</v>
       </c>
       <c r="T66">
         <v>78</v>
@@ -5534,16 +5534,16 @@
         <v>78.8</v>
       </c>
       <c r="V66">
-        <v>17.48</v>
+        <v>17.32</v>
       </c>
       <c r="W66">
-        <v>44.48</v>
+        <v>43.9</v>
       </c>
       <c r="X66">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="Y66">
-        <v>4.9</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="67" spans="1:25">
@@ -5572,7 +5572,7 @@
         <v>70</v>
       </c>
       <c r="I67">
-        <v>3735.87</v>
+        <v>3673</v>
       </c>
       <c r="J67">
         <v>46</v>
@@ -5581,28 +5581,28 @@
         <v>51.1</v>
       </c>
       <c r="L67">
-        <v>53.37</v>
+        <v>52.47</v>
       </c>
       <c r="M67">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N67">
-        <v>4040.16</v>
+        <v>3673</v>
       </c>
       <c r="O67">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P67">
-        <v>53.3</v>
+        <v>51.1</v>
       </c>
       <c r="Q67">
-        <v>51.8</v>
+        <v>52.47</v>
       </c>
       <c r="R67">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S67">
-        <v>4806.38</v>
+        <v>4970.32</v>
       </c>
       <c r="T67">
         <v>60</v>
@@ -5611,16 +5611,16 @@
         <v>66.7</v>
       </c>
       <c r="V67">
-        <v>36.14</v>
+        <v>37.65</v>
       </c>
       <c r="W67">
-        <v>50.59</v>
+        <v>52.32</v>
       </c>
       <c r="X67">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Y67">
-        <v>6.07</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="68" spans="1:25">
@@ -5646,58 +5646,58 @@
         <v>235.08</v>
       </c>
       <c r="H68">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I68">
-        <v>55.21</v>
+        <v>17.11</v>
       </c>
       <c r="J68">
+        <v>6</v>
+      </c>
+      <c r="K68">
+        <v>16.7</v>
+      </c>
+      <c r="L68">
+        <v>1.71</v>
+      </c>
+      <c r="M68">
+        <v>15</v>
+      </c>
+      <c r="N68">
+        <v>93.98999999999999</v>
+      </c>
+      <c r="O68">
         <v>9</v>
       </c>
-      <c r="K68">
+      <c r="P68">
         <v>25</v>
       </c>
-      <c r="L68">
-        <v>3.45</v>
-      </c>
-      <c r="M68">
-        <v>21</v>
-      </c>
-      <c r="N68">
-        <v>132.09</v>
-      </c>
-      <c r="O68">
-        <v>12</v>
-      </c>
-      <c r="P68">
-        <v>33.3</v>
-      </c>
       <c r="Q68">
-        <v>6.29</v>
+        <v>6.27</v>
       </c>
       <c r="R68">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S68">
-        <v>187.07</v>
+        <v>148.97</v>
       </c>
       <c r="T68">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U68">
-        <v>41.7</v>
+        <v>38.9</v>
       </c>
       <c r="V68">
-        <v>5.34</v>
+        <v>4.66</v>
       </c>
       <c r="W68">
-        <v>5.2</v>
+        <v>4.14</v>
       </c>
       <c r="X68">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="Y68">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="69" spans="1:25">
@@ -5726,7 +5726,7 @@
         <v>97</v>
       </c>
       <c r="I69">
-        <v>2275.61</v>
+        <v>2374.36</v>
       </c>
       <c r="J69">
         <v>51</v>
@@ -5735,13 +5735,13 @@
         <v>39.8</v>
       </c>
       <c r="L69">
-        <v>23.46</v>
+        <v>24.48</v>
       </c>
       <c r="M69">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N69">
-        <v>3522.75</v>
+        <v>3686.49</v>
       </c>
       <c r="O69">
         <v>93</v>
@@ -5750,31 +5750,31 @@
         <v>72.7</v>
       </c>
       <c r="Q69">
-        <v>14.8</v>
+        <v>15.42</v>
       </c>
       <c r="R69">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="S69">
-        <v>3542.74</v>
+        <v>3823.06</v>
       </c>
       <c r="T69">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="U69">
-        <v>73.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="V69">
-        <v>14.58</v>
+        <v>15.23</v>
       </c>
       <c r="W69">
-        <v>26.84</v>
+        <v>28.96</v>
       </c>
       <c r="X69">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Y69">
-        <v>4.07</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="70" spans="1:25">
@@ -5800,55 +5800,55 @@
         <v>1939.41</v>
       </c>
       <c r="H70">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="I70">
-        <v>403.73</v>
+        <v>403.79</v>
       </c>
       <c r="J70">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="K70">
-        <v>33.1</v>
+        <v>40.3</v>
       </c>
       <c r="L70">
-        <v>3.18</v>
+        <v>2.49</v>
       </c>
       <c r="M70">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="N70">
-        <v>403.73</v>
+        <v>403.79</v>
       </c>
       <c r="O70">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="P70">
-        <v>33.1</v>
+        <v>40.3</v>
       </c>
       <c r="Q70">
-        <v>3.18</v>
+        <v>2.49</v>
       </c>
       <c r="R70">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="S70">
-        <v>403.73</v>
+        <v>403.79</v>
       </c>
       <c r="T70">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="U70">
-        <v>33.1</v>
+        <v>40.3</v>
       </c>
       <c r="V70">
-        <v>3.18</v>
+        <v>2.49</v>
       </c>
       <c r="W70">
         <v>1.36</v>
       </c>
       <c r="X70">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="Y70">
         <v>0.21</v>
@@ -6366,7 +6366,7 @@
         <v>0.22</v>
       </c>
       <c r="R77">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="S77">
         <v>89.72</v>

--- a/product_monthly.xlsx
+++ b/product_monthly.xlsx
@@ -636,70 +636,70 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>958</v>
+        <v>1112</v>
       </c>
       <c r="E2">
-        <v>986</v>
+        <v>1150</v>
       </c>
       <c r="F2">
-        <v>986</v>
+        <v>1150</v>
       </c>
       <c r="G2">
-        <v>6252.53</v>
+        <v>7356.93</v>
       </c>
       <c r="H2">
-        <v>258</v>
+        <v>381</v>
       </c>
       <c r="I2">
-        <v>646.6</v>
+        <v>780.8</v>
       </c>
       <c r="J2">
-        <v>183</v>
+        <v>259</v>
       </c>
       <c r="K2">
-        <v>19.1</v>
+        <v>23.3</v>
       </c>
       <c r="L2">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="M2">
-        <v>258</v>
+        <v>381</v>
       </c>
       <c r="N2">
-        <v>646.6</v>
+        <v>780.8</v>
       </c>
       <c r="O2">
-        <v>183</v>
+        <v>259</v>
       </c>
       <c r="P2">
-        <v>19.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q2">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="R2">
-        <v>258</v>
+        <v>381</v>
       </c>
       <c r="S2">
-        <v>646.6</v>
+        <v>780.8</v>
       </c>
       <c r="T2">
-        <v>183</v>
+        <v>259</v>
       </c>
       <c r="U2">
-        <v>19.1</v>
+        <v>23.3</v>
       </c>
       <c r="V2">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="W2">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="X2">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="Y2">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1519,7 +1519,7 @@
         <v>1651</v>
       </c>
       <c r="S13">
-        <v>32925.95</v>
+        <v>32897.3</v>
       </c>
       <c r="T13">
         <v>353</v>
@@ -1528,16 +1528,16 @@
         <v>62.1</v>
       </c>
       <c r="V13">
-        <v>19.94</v>
+        <v>19.93</v>
       </c>
       <c r="W13">
-        <v>56.67</v>
+        <v>56.62</v>
       </c>
       <c r="X13">
         <v>2.84</v>
       </c>
       <c r="Y13">
-        <v>9.91</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1593,10 +1593,10 @@
         <v>19.52</v>
       </c>
       <c r="R14">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="S14">
-        <v>56977.05</v>
+        <v>57045.03</v>
       </c>
       <c r="T14">
         <v>345</v>
@@ -1605,16 +1605,16 @@
         <v>54.8</v>
       </c>
       <c r="V14">
-        <v>42.52</v>
+        <v>42.54</v>
       </c>
       <c r="W14">
-        <v>89.03</v>
+        <v>89.13</v>
       </c>
       <c r="X14">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Y14">
-        <v>15.56</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1670,7 +1670,7 @@
         <v>4.71</v>
       </c>
       <c r="R15">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="S15">
         <v>17033.4</v>
@@ -1682,7 +1682,7 @@
         <v>59.9</v>
       </c>
       <c r="V15">
-        <v>23.86</v>
+        <v>23.82</v>
       </c>
       <c r="W15">
         <v>39.34</v>
@@ -1812,7 +1812,7 @@
         <v>936</v>
       </c>
       <c r="N17">
-        <v>16112.79</v>
+        <v>16138.78</v>
       </c>
       <c r="O17">
         <v>467</v>
@@ -1821,13 +1821,13 @@
         <v>68.8</v>
       </c>
       <c r="Q17">
-        <v>17.21</v>
+        <v>17.24</v>
       </c>
       <c r="R17">
         <v>1282</v>
       </c>
       <c r="S17">
-        <v>29147.55</v>
+        <v>29173.54</v>
       </c>
       <c r="T17">
         <v>475</v>
@@ -1836,16 +1836,16 @@
         <v>70</v>
       </c>
       <c r="V17">
-        <v>22.74</v>
+        <v>22.76</v>
       </c>
       <c r="W17">
-        <v>42.61</v>
+        <v>42.65</v>
       </c>
       <c r="X17">
         <v>1.87</v>
       </c>
       <c r="Y17">
-        <v>7.45</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1901,10 +1901,10 @@
         <v>29.07</v>
       </c>
       <c r="R18">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="S18">
-        <v>98108.85000000001</v>
+        <v>97928.75999999999</v>
       </c>
       <c r="T18">
         <v>1205</v>
@@ -1913,16 +1913,16 @@
         <v>83.2</v>
       </c>
       <c r="V18">
-        <v>24.34</v>
+        <v>24.31</v>
       </c>
       <c r="W18">
-        <v>67.15000000000001</v>
+        <v>67.03</v>
       </c>
       <c r="X18">
         <v>2.76</v>
       </c>
       <c r="Y18">
-        <v>11.79</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1978,10 +1978,10 @@
         <v>37.9</v>
       </c>
       <c r="R19">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="S19">
-        <v>98141.46000000001</v>
+        <v>98198.60000000001</v>
       </c>
       <c r="T19">
         <v>836</v>
@@ -1990,16 +1990,16 @@
         <v>87.3</v>
       </c>
       <c r="V19">
-        <v>31.73</v>
+        <v>31.76</v>
       </c>
       <c r="W19">
-        <v>100.04</v>
+        <v>100.1</v>
       </c>
       <c r="X19">
         <v>3.15</v>
       </c>
       <c r="Y19">
-        <v>17.57</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2055,28 +2055,28 @@
         <v>13.02</v>
       </c>
       <c r="R20">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="S20">
-        <v>32678.15</v>
+        <v>32403.51</v>
       </c>
       <c r="T20">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="U20">
-        <v>90.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V20">
-        <v>16.49</v>
+        <v>16.37</v>
       </c>
       <c r="W20">
-        <v>47.78</v>
+        <v>47.37</v>
       </c>
       <c r="X20">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="Y20">
-        <v>8.4</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2105,7 +2105,7 @@
         <v>2840</v>
       </c>
       <c r="I21">
-        <v>28315.49</v>
+        <v>28250.11</v>
       </c>
       <c r="J21">
         <v>1508</v>
@@ -2114,13 +2114,13 @@
         <v>47.2</v>
       </c>
       <c r="L21">
-        <v>9.970000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M21">
         <v>4959</v>
       </c>
       <c r="N21">
-        <v>35044.74</v>
+        <v>34908.75</v>
       </c>
       <c r="O21">
         <v>2292</v>
@@ -2129,13 +2129,13 @@
         <v>71.7</v>
       </c>
       <c r="Q21">
-        <v>7.07</v>
+        <v>7.04</v>
       </c>
       <c r="R21">
-        <v>5445</v>
+        <v>5435</v>
       </c>
       <c r="S21">
-        <v>37572.98</v>
+        <v>37394.75</v>
       </c>
       <c r="T21">
         <v>2300</v>
@@ -2144,16 +2144,16 @@
         <v>71.90000000000001</v>
       </c>
       <c r="V21">
-        <v>6.9</v>
+        <v>6.88</v>
       </c>
       <c r="W21">
-        <v>11.46</v>
+        <v>11.41</v>
       </c>
       <c r="X21">
         <v>1.66</v>
       </c>
       <c r="Y21">
-        <v>2.01</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2182,7 +2182,7 @@
         <v>1539</v>
       </c>
       <c r="I22">
-        <v>5845.36</v>
+        <v>5831.1</v>
       </c>
       <c r="J22">
         <v>896</v>
@@ -2191,28 +2191,28 @@
         <v>43.1</v>
       </c>
       <c r="L22">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="M22">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="N22">
-        <v>5938.13</v>
+        <v>5831.1</v>
       </c>
       <c r="O22">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="P22">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="Q22">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="R22">
-        <v>2316</v>
+        <v>2311</v>
       </c>
       <c r="S22">
-        <v>24134.93</v>
+        <v>24461.06</v>
       </c>
       <c r="T22">
         <v>1001</v>
@@ -2221,16 +2221,16 @@
         <v>48.2</v>
       </c>
       <c r="V22">
-        <v>10.42</v>
+        <v>10.58</v>
       </c>
       <c r="W22">
-        <v>11.01</v>
+        <v>11.15</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2256,58 +2256,58 @@
         <v>7754.45</v>
       </c>
       <c r="H23">
-        <v>533</v>
+        <v>470</v>
       </c>
       <c r="I23">
-        <v>25515.1</v>
+        <v>21726.47</v>
       </c>
       <c r="J23">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="K23">
-        <v>35.7</v>
+        <v>32</v>
       </c>
       <c r="L23">
-        <v>47.87</v>
+        <v>46.23</v>
       </c>
       <c r="M23">
-        <v>1000</v>
+        <v>945</v>
       </c>
       <c r="N23">
-        <v>35417.63</v>
+        <v>31779.95</v>
       </c>
       <c r="O23">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="P23">
-        <v>49.1</v>
+        <v>46.2</v>
       </c>
       <c r="Q23">
-        <v>35.42</v>
+        <v>33.63</v>
       </c>
       <c r="R23">
-        <v>1788</v>
+        <v>1743</v>
       </c>
       <c r="S23">
-        <v>68319.94</v>
+        <v>66554.3</v>
       </c>
       <c r="T23">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="U23">
-        <v>56.6</v>
+        <v>54.4</v>
       </c>
       <c r="V23">
-        <v>38.21</v>
+        <v>38.18</v>
       </c>
       <c r="W23">
-        <v>69.56999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="X23">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="Y23">
-        <v>8.81</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2336,7 +2336,7 @@
         <v>479</v>
       </c>
       <c r="I24">
-        <v>4335.15</v>
+        <v>4390.14</v>
       </c>
       <c r="J24">
         <v>204</v>
@@ -2345,13 +2345,13 @@
         <v>61.4</v>
       </c>
       <c r="L24">
-        <v>9.050000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="M24">
         <v>669</v>
       </c>
       <c r="N24">
-        <v>5130.12</v>
+        <v>5185.11</v>
       </c>
       <c r="O24">
         <v>256</v>
@@ -2360,13 +2360,13 @@
         <v>77.09999999999999</v>
       </c>
       <c r="Q24">
-        <v>7.67</v>
+        <v>7.75</v>
       </c>
       <c r="R24">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="S24">
-        <v>5650.21</v>
+        <v>5785.2</v>
       </c>
       <c r="T24">
         <v>256</v>
@@ -2375,16 +2375,16 @@
         <v>77.09999999999999</v>
       </c>
       <c r="V24">
-        <v>7.96</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="W24">
-        <v>15.48</v>
+        <v>15.85</v>
       </c>
       <c r="X24">
         <v>1.95</v>
       </c>
       <c r="Y24">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2398,70 +2398,70 @@
         <v>42</v>
       </c>
       <c r="D25">
-        <v>876</v>
+        <v>909</v>
       </c>
       <c r="E25">
-        <v>977</v>
+        <v>1018</v>
       </c>
       <c r="F25">
-        <v>982</v>
+        <v>1023</v>
       </c>
       <c r="G25">
-        <v>6142.46</v>
+        <v>6379.37</v>
       </c>
       <c r="H25">
-        <v>719</v>
+        <v>775</v>
       </c>
       <c r="I25">
-        <v>4628.13</v>
+        <v>5019.34</v>
       </c>
       <c r="J25">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="K25">
-        <v>40.6</v>
+        <v>42.6</v>
       </c>
       <c r="L25">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
       <c r="M25">
-        <v>719</v>
+        <v>775</v>
       </c>
       <c r="N25">
-        <v>4628.13</v>
+        <v>5019.34</v>
       </c>
       <c r="O25">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="P25">
-        <v>40.6</v>
+        <v>42.6</v>
       </c>
       <c r="Q25">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
       <c r="R25">
-        <v>719</v>
+        <v>775</v>
       </c>
       <c r="S25">
-        <v>4628.13</v>
+        <v>5019.34</v>
       </c>
       <c r="T25">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="U25">
-        <v>40.6</v>
+        <v>42.6</v>
       </c>
       <c r="V25">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
       <c r="W25">
-        <v>4.74</v>
+        <v>4.93</v>
       </c>
       <c r="X25">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="Y25">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -3017,7 +3017,7 @@
         <v>896</v>
       </c>
       <c r="N33">
-        <v>50688.68</v>
+        <v>50669.59</v>
       </c>
       <c r="O33">
         <v>378</v>
@@ -3026,13 +3026,13 @@
         <v>88.5</v>
       </c>
       <c r="Q33">
-        <v>56.57</v>
+        <v>56.55</v>
       </c>
       <c r="R33">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="S33">
-        <v>64012.44</v>
+        <v>64102.17</v>
       </c>
       <c r="T33">
         <v>385</v>
@@ -3041,16 +3041,16 @@
         <v>90.2</v>
       </c>
       <c r="V33">
-        <v>52.86</v>
+        <v>52.85</v>
       </c>
       <c r="W33">
-        <v>149.56</v>
+        <v>149.77</v>
       </c>
       <c r="X33">
         <v>2.83</v>
       </c>
       <c r="Y33">
-        <v>25.94</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3079,7 +3079,7 @@
         <v>830</v>
       </c>
       <c r="I34">
-        <v>53731.43</v>
+        <v>53712.39</v>
       </c>
       <c r="J34">
         <v>355</v>
@@ -3088,13 +3088,13 @@
         <v>86</v>
       </c>
       <c r="L34">
-        <v>64.73999999999999</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="M34">
         <v>971</v>
       </c>
       <c r="N34">
-        <v>55805.93</v>
+        <v>55786.89</v>
       </c>
       <c r="O34">
         <v>371</v>
@@ -3103,13 +3103,13 @@
         <v>89.8</v>
       </c>
       <c r="Q34">
-        <v>57.47</v>
+        <v>57.45</v>
       </c>
       <c r="R34">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="S34">
-        <v>63515.22</v>
+        <v>63122.18</v>
       </c>
       <c r="T34">
         <v>374</v>
@@ -3118,16 +3118,16 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V34">
-        <v>53.28</v>
+        <v>53.04</v>
       </c>
       <c r="W34">
-        <v>152.31</v>
+        <v>151.37</v>
       </c>
       <c r="X34">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="Y34">
-        <v>26.93</v>
+        <v>26.76</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3153,58 +3153,58 @@
         <v>3530.64</v>
       </c>
       <c r="H35">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="I35">
-        <v>21006.21</v>
+        <v>20137.84</v>
       </c>
       <c r="J35">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="K35">
-        <v>34.2</v>
+        <v>31.8</v>
       </c>
       <c r="L35">
-        <v>57.87</v>
+        <v>59.58</v>
       </c>
       <c r="M35">
-        <v>672</v>
+        <v>652</v>
       </c>
       <c r="N35">
-        <v>32389.58</v>
+        <v>31694.76</v>
       </c>
       <c r="O35">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="P35">
-        <v>48.3</v>
+        <v>46.4</v>
       </c>
       <c r="Q35">
-        <v>48.2</v>
+        <v>48.61</v>
       </c>
       <c r="R35">
-        <v>1146</v>
+        <v>1135</v>
       </c>
       <c r="S35">
-        <v>42872.39</v>
+        <v>42607.05</v>
       </c>
       <c r="T35">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="U35">
-        <v>54.4</v>
+        <v>52.5</v>
       </c>
       <c r="V35">
-        <v>37.41</v>
+        <v>37.54</v>
       </c>
       <c r="W35">
-        <v>68.48999999999999</v>
+        <v>68.06</v>
       </c>
       <c r="X35">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Y35">
-        <v>12.14</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3233,7 +3233,7 @@
         <v>402</v>
       </c>
       <c r="I36">
-        <v>18562.9</v>
+        <v>18737.54</v>
       </c>
       <c r="J36">
         <v>175</v>
@@ -3242,13 +3242,13 @@
         <v>52.7</v>
       </c>
       <c r="L36">
-        <v>46.18</v>
+        <v>46.61</v>
       </c>
       <c r="M36">
         <v>606</v>
       </c>
       <c r="N36">
-        <v>21076.17</v>
+        <v>21344.15</v>
       </c>
       <c r="O36">
         <v>246</v>
@@ -3257,13 +3257,13 @@
         <v>74.09999999999999</v>
       </c>
       <c r="Q36">
-        <v>34.78</v>
+        <v>35.22</v>
       </c>
       <c r="R36">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="S36">
-        <v>21938.65</v>
+        <v>22206.63</v>
       </c>
       <c r="T36">
         <v>250</v>
@@ -3272,16 +3272,16 @@
         <v>75.3</v>
       </c>
       <c r="V36">
-        <v>31.98</v>
+        <v>32.32</v>
       </c>
       <c r="W36">
-        <v>64.34</v>
+        <v>65.12</v>
       </c>
       <c r="X36">
         <v>2.01</v>
       </c>
       <c r="Y36">
-        <v>11.41</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3295,70 +3295,70 @@
         <v>42</v>
       </c>
       <c r="D37">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E37">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="F37">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="G37">
-        <v>2261.64</v>
+        <v>2312.4</v>
       </c>
       <c r="H37">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="I37">
-        <v>3410.16</v>
+        <v>3780.87</v>
       </c>
       <c r="J37">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="K37">
-        <v>49.1</v>
+        <v>49.9</v>
       </c>
       <c r="L37">
-        <v>11.07</v>
+        <v>11.82</v>
       </c>
       <c r="M37">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="N37">
-        <v>3410.16</v>
+        <v>3780.87</v>
       </c>
       <c r="O37">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="P37">
-        <v>49.1</v>
+        <v>49.9</v>
       </c>
       <c r="Q37">
-        <v>11.07</v>
+        <v>11.82</v>
       </c>
       <c r="R37">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="S37">
-        <v>3410.16</v>
+        <v>3780.87</v>
       </c>
       <c r="T37">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="U37">
-        <v>49.1</v>
+        <v>49.9</v>
       </c>
       <c r="V37">
-        <v>11.07</v>
+        <v>11.82</v>
       </c>
       <c r="W37">
-        <v>8.5</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="X37">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="Y37">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3414,10 +3414,10 @@
         <v>48.8</v>
       </c>
       <c r="R38">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="S38">
-        <v>7947.06</v>
+        <v>7904.33</v>
       </c>
       <c r="T38">
         <v>15</v>
@@ -3426,16 +3426,16 @@
         <v>50</v>
       </c>
       <c r="V38">
-        <v>64.61</v>
+        <v>66.42</v>
       </c>
       <c r="W38">
-        <v>264.9</v>
+        <v>263.48</v>
       </c>
       <c r="X38">
-        <v>4.1</v>
+        <v>3.97</v>
       </c>
       <c r="Y38">
-        <v>29.53</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3461,58 +3461,58 @@
         <v>4637.49</v>
       </c>
       <c r="H39">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="I39">
-        <v>2130.71</v>
+        <v>1713.33</v>
       </c>
       <c r="J39">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="K39">
-        <v>26.2</v>
+        <v>22.7</v>
       </c>
       <c r="L39">
-        <v>12.18</v>
+        <v>11.5</v>
       </c>
       <c r="M39">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="N39">
-        <v>16612.22</v>
+        <v>16497.27</v>
       </c>
       <c r="O39">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="P39">
-        <v>41.1</v>
+        <v>39</v>
       </c>
       <c r="Q39">
-        <v>44.3</v>
+        <v>46.73</v>
       </c>
       <c r="R39">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="S39">
-        <v>18590.86</v>
+        <v>18522.86</v>
       </c>
       <c r="T39">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="U39">
-        <v>45.3</v>
+        <v>43.4</v>
       </c>
       <c r="V39">
-        <v>36.03</v>
+        <v>37.19</v>
       </c>
       <c r="W39">
-        <v>35.96</v>
+        <v>35.83</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="Y39">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3600,70 +3600,70 @@
         <v>42</v>
       </c>
       <c r="D41">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E41">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F41">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G41">
-        <v>3202.29</v>
+        <v>3229.2</v>
       </c>
       <c r="H41">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="I41">
-        <v>338.04</v>
+        <v>338.05</v>
       </c>
       <c r="J41">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="K41">
-        <v>46.9</v>
+        <v>48.2</v>
       </c>
       <c r="L41">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="M41">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="N41">
-        <v>338.04</v>
+        <v>338.05</v>
       </c>
       <c r="O41">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="P41">
-        <v>46.9</v>
+        <v>48.2</v>
       </c>
       <c r="Q41">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="R41">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="S41">
-        <v>338.04</v>
+        <v>338.05</v>
       </c>
       <c r="T41">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="U41">
-        <v>46.9</v>
+        <v>48.2</v>
       </c>
       <c r="V41">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="W41">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="X41">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="Y41">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3677,19 +3677,19 @@
         <v>42</v>
       </c>
       <c r="D42">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E42">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F42">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3698,13 +3698,13 @@
         <v>8</v>
       </c>
       <c r="K42">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -3713,13 +3713,13 @@
         <v>8</v>
       </c>
       <c r="P42">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="Q42">
         <v>0</v>
       </c>
       <c r="R42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -3728,7 +3728,7 @@
         <v>8</v>
       </c>
       <c r="U42">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="V42">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="X42">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3793,10 +3793,10 @@
         <v>10.14</v>
       </c>
       <c r="R43">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="S43">
-        <v>2327.94</v>
+        <v>2574.33</v>
       </c>
       <c r="T43">
         <v>37</v>
@@ -3805,16 +3805,16 @@
         <v>53.6</v>
       </c>
       <c r="V43">
-        <v>17.77</v>
+        <v>19.36</v>
       </c>
       <c r="W43">
-        <v>33.74</v>
+        <v>37.31</v>
       </c>
       <c r="X43">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Y43">
-        <v>7.13</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3840,58 +3840,58 @@
         <v>600.71</v>
       </c>
       <c r="H44">
+        <v>40</v>
+      </c>
+      <c r="I44">
+        <v>1753.91</v>
+      </c>
+      <c r="J44">
+        <v>30</v>
+      </c>
+      <c r="K44">
+        <v>23.6</v>
+      </c>
+      <c r="L44">
+        <v>43.85</v>
+      </c>
+      <c r="M44">
+        <v>81</v>
+      </c>
+      <c r="N44">
+        <v>2311.29</v>
+      </c>
+      <c r="O44">
         <v>46</v>
       </c>
-      <c r="I44">
-        <v>1787.36</v>
-      </c>
-      <c r="J44">
-        <v>35</v>
-      </c>
-      <c r="K44">
-        <v>27.6</v>
-      </c>
-      <c r="L44">
-        <v>38.86</v>
-      </c>
-      <c r="M44">
-        <v>86</v>
-      </c>
-      <c r="N44">
-        <v>2304.78</v>
-      </c>
-      <c r="O44">
-        <v>50</v>
-      </c>
       <c r="P44">
-        <v>39.4</v>
+        <v>36.2</v>
       </c>
       <c r="Q44">
-        <v>26.8</v>
+        <v>28.53</v>
       </c>
       <c r="R44">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="S44">
-        <v>2638.69</v>
+        <v>2655.19</v>
       </c>
       <c r="T44">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="U44">
-        <v>43.3</v>
+        <v>40.2</v>
       </c>
       <c r="V44">
-        <v>19.26</v>
+        <v>20.12</v>
       </c>
       <c r="W44">
-        <v>20.78</v>
+        <v>20.91</v>
       </c>
       <c r="X44">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -3973,70 +3973,70 @@
         <v>42</v>
       </c>
       <c r="D46">
+        <v>45</v>
+      </c>
+      <c r="E46">
+        <v>45</v>
+      </c>
+      <c r="F46">
+        <v>45</v>
+      </c>
+      <c r="G46">
+        <v>212.85</v>
+      </c>
+      <c r="H46">
         <v>39</v>
       </c>
-      <c r="E46">
+      <c r="I46">
+        <v>161.11</v>
+      </c>
+      <c r="J46">
+        <v>24</v>
+      </c>
+      <c r="K46">
+        <v>53.3</v>
+      </c>
+      <c r="L46">
+        <v>4.13</v>
+      </c>
+      <c r="M46">
         <v>39</v>
       </c>
-      <c r="F46">
+      <c r="N46">
+        <v>161.11</v>
+      </c>
+      <c r="O46">
+        <v>24</v>
+      </c>
+      <c r="P46">
+        <v>53.3</v>
+      </c>
+      <c r="Q46">
+        <v>4.13</v>
+      </c>
+      <c r="R46">
         <v>39</v>
       </c>
-      <c r="G46">
-        <v>184.47</v>
-      </c>
-      <c r="H46">
-        <v>35</v>
-      </c>
-      <c r="I46">
-        <v>130.55</v>
-      </c>
-      <c r="J46">
-        <v>23</v>
-      </c>
-      <c r="K46">
-        <v>59</v>
-      </c>
-      <c r="L46">
-        <v>3.73</v>
-      </c>
-      <c r="M46">
-        <v>35</v>
-      </c>
-      <c r="N46">
-        <v>130.55</v>
-      </c>
-      <c r="O46">
-        <v>23</v>
-      </c>
-      <c r="P46">
-        <v>59</v>
-      </c>
-      <c r="Q46">
-        <v>3.73</v>
-      </c>
-      <c r="R46">
-        <v>35</v>
-      </c>
       <c r="S46">
-        <v>130.55</v>
+        <v>161.11</v>
       </c>
       <c r="T46">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U46">
-        <v>59</v>
+        <v>53.3</v>
       </c>
       <c r="V46">
-        <v>3.73</v>
+        <v>4.13</v>
       </c>
       <c r="W46">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="X46">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="Y46">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -4127,16 +4127,16 @@
         <v>42</v>
       </c>
       <c r="D48">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E48">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F48">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G48">
-        <v>77.98999999999999</v>
+        <v>92.17</v>
       </c>
       <c r="H48">
         <v>4</v>
@@ -4148,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="K48">
-        <v>27.3</v>
+        <v>23.1</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>3</v>
       </c>
       <c r="P48">
-        <v>27.3</v>
+        <v>23.1</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -4178,7 +4178,7 @@
         <v>3</v>
       </c>
       <c r="U48">
-        <v>27.3</v>
+        <v>23.1</v>
       </c>
       <c r="V48">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="X48">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="Y48">
         <v>0</v>
@@ -4340,58 +4340,58 @@
         <v>42</v>
       </c>
       <c r="D51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51">
+        <v>4</v>
+      </c>
+      <c r="K51">
+        <v>23.5</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
         <v>5</v>
       </c>
-      <c r="K51">
-        <v>31.2</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>6</v>
-      </c>
       <c r="N51">
         <v>0</v>
       </c>
       <c r="O51">
+        <v>4</v>
+      </c>
+      <c r="P51">
+        <v>23.5</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
         <v>5</v>
       </c>
-      <c r="P51">
-        <v>31.2</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>6</v>
-      </c>
       <c r="S51">
         <v>0</v>
       </c>
       <c r="T51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>31.2</v>
+        <v>23.5</v>
       </c>
       <c r="V51">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="X51">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="52" spans="1:25">
@@ -4456,7 +4456,7 @@
         <v>20</v>
       </c>
       <c r="S52">
-        <v>390.37</v>
+        <v>549.74</v>
       </c>
       <c r="T52">
         <v>11</v>
@@ -4465,10 +4465,10 @@
         <v>45.8</v>
       </c>
       <c r="V52">
-        <v>19.52</v>
+        <v>27.49</v>
       </c>
       <c r="W52">
-        <v>16.27</v>
+        <v>22.91</v>
       </c>
       <c r="X52">
         <v>0.83</v>
@@ -4485,13 +4485,13 @@
         <v>42</v>
       </c>
       <c r="D53">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E53">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F53">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -4506,7 +4506,7 @@
         <v>10</v>
       </c>
       <c r="K53">
-        <v>62.5</v>
+        <v>58.8</v>
       </c>
       <c r="L53">
         <v>2.41</v>
@@ -4521,7 +4521,7 @@
         <v>10</v>
       </c>
       <c r="P53">
-        <v>62.5</v>
+        <v>58.8</v>
       </c>
       <c r="Q53">
         <v>2.41</v>
@@ -4536,16 +4536,16 @@
         <v>10</v>
       </c>
       <c r="U53">
-        <v>62.5</v>
+        <v>58.8</v>
       </c>
       <c r="V53">
         <v>2.41</v>
       </c>
       <c r="W53">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="X53">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="54" spans="1:25">
@@ -4636,70 +4636,70 @@
         <v>42</v>
       </c>
       <c r="D55">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="E55">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="F55">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="G55">
-        <v>3383.88</v>
+        <v>3442.47</v>
       </c>
       <c r="H55">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="I55">
-        <v>698.42</v>
+        <v>850.5</v>
       </c>
       <c r="J55">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="K55">
-        <v>45.2</v>
+        <v>47.6</v>
       </c>
       <c r="L55">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="M55">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="N55">
-        <v>698.42</v>
+        <v>850.5</v>
       </c>
       <c r="O55">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="P55">
-        <v>45.2</v>
+        <v>47.6</v>
       </c>
       <c r="Q55">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="R55">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="S55">
-        <v>698.42</v>
+        <v>850.5</v>
       </c>
       <c r="T55">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="U55">
-        <v>45.2</v>
+        <v>47.6</v>
       </c>
       <c r="V55">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="W55">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="X55">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="Y55">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="56" spans="1:25">
@@ -4728,7 +4728,7 @@
         <v>24</v>
       </c>
       <c r="I56">
-        <v>575.96</v>
+        <v>561.86</v>
       </c>
       <c r="J56">
         <v>10</v>
@@ -4737,28 +4737,28 @@
         <v>16.4</v>
       </c>
       <c r="L56">
-        <v>24</v>
+        <v>23.41</v>
       </c>
       <c r="M56">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N56">
-        <v>605.85</v>
+        <v>561.86</v>
       </c>
       <c r="O56">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P56">
-        <v>19.7</v>
+        <v>18</v>
       </c>
       <c r="Q56">
-        <v>20.89</v>
+        <v>21.61</v>
       </c>
       <c r="R56">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S56">
-        <v>2641.7</v>
+        <v>2647.58</v>
       </c>
       <c r="T56">
         <v>28</v>
@@ -4767,16 +4767,16 @@
         <v>45.9</v>
       </c>
       <c r="V56">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="W56">
-        <v>42.61</v>
+        <v>42.7</v>
       </c>
       <c r="X56">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Y56">
-        <v>8.710000000000001</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="57" spans="1:25">
@@ -4802,58 +4802,58 @@
         <v>694.98</v>
       </c>
       <c r="H57">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="I57">
-        <v>195.5</v>
+        <v>150.84</v>
       </c>
       <c r="J57">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K57">
-        <v>28.7</v>
+        <v>23.8</v>
       </c>
       <c r="L57">
-        <v>3.55</v>
+        <v>3.77</v>
       </c>
       <c r="M57">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="N57">
-        <v>816.96</v>
+        <v>782.29</v>
       </c>
       <c r="O57">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="P57">
-        <v>39.9</v>
+        <v>36.4</v>
       </c>
       <c r="Q57">
-        <v>8.25</v>
+        <v>9.1</v>
       </c>
       <c r="R57">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="S57">
-        <v>1278.87</v>
+        <v>1274.16</v>
       </c>
       <c r="T57">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="U57">
-        <v>50.3</v>
+        <v>46.9</v>
       </c>
       <c r="V57">
-        <v>8.039999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="W57">
-        <v>8.94</v>
+        <v>8.91</v>
       </c>
       <c r="X57">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y57">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="58" spans="1:25">
@@ -4882,7 +4882,7 @@
         <v>76</v>
       </c>
       <c r="I58">
-        <v>2321.4</v>
+        <v>2351.37</v>
       </c>
       <c r="J58">
         <v>36</v>
@@ -4891,13 +4891,13 @@
         <v>49.3</v>
       </c>
       <c r="L58">
-        <v>30.54</v>
+        <v>30.94</v>
       </c>
       <c r="M58">
         <v>149</v>
       </c>
       <c r="N58">
-        <v>4222.97</v>
+        <v>4399.96</v>
       </c>
       <c r="O58">
         <v>61</v>
@@ -4906,13 +4906,13 @@
         <v>83.59999999999999</v>
       </c>
       <c r="Q58">
-        <v>28.34</v>
+        <v>29.53</v>
       </c>
       <c r="R58">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S58">
-        <v>4361.22</v>
+        <v>4574.31</v>
       </c>
       <c r="T58">
         <v>61</v>
@@ -4921,16 +4921,16 @@
         <v>83.59999999999999</v>
       </c>
       <c r="V58">
-        <v>26.59</v>
+        <v>27.72</v>
       </c>
       <c r="W58">
-        <v>59.74</v>
+        <v>62.66</v>
       </c>
       <c r="X58">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Y58">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="59" spans="1:25">
@@ -4944,70 +4944,70 @@
         <v>42</v>
       </c>
       <c r="D59">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E59">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F59">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G59">
-        <v>213.84</v>
+        <v>243</v>
       </c>
       <c r="H59">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I59">
-        <v>103.68</v>
+        <v>144.03</v>
       </c>
       <c r="J59">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K59">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L59">
-        <v>4.94</v>
+        <v>6.26</v>
       </c>
       <c r="M59">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N59">
-        <v>103.68</v>
+        <v>144.03</v>
       </c>
       <c r="O59">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P59">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q59">
-        <v>4.94</v>
+        <v>6.26</v>
       </c>
       <c r="R59">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="S59">
-        <v>103.68</v>
+        <v>144.03</v>
       </c>
       <c r="T59">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U59">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V59">
-        <v>4.94</v>
+        <v>6.26</v>
       </c>
       <c r="W59">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="X59">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="Y59">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="60" spans="1:25">
@@ -5522,10 +5522,10 @@
         <v>7.58</v>
       </c>
       <c r="R66">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S66">
-        <v>4433.84</v>
+        <v>4489.94</v>
       </c>
       <c r="T66">
         <v>78</v>
@@ -5534,16 +5534,16 @@
         <v>78.8</v>
       </c>
       <c r="V66">
-        <v>17.39</v>
+        <v>17.68</v>
       </c>
       <c r="W66">
-        <v>43.9</v>
+        <v>44.45</v>
       </c>
       <c r="X66">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="Y66">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="67" spans="1:25">
@@ -5572,7 +5572,7 @@
         <v>70</v>
       </c>
       <c r="I67">
-        <v>3654.01</v>
+        <v>3635.02</v>
       </c>
       <c r="J67">
         <v>46</v>
@@ -5581,13 +5581,13 @@
         <v>51.1</v>
       </c>
       <c r="L67">
-        <v>52.2</v>
+        <v>51.93</v>
       </c>
       <c r="M67">
         <v>70</v>
       </c>
       <c r="N67">
-        <v>3654.01</v>
+        <v>3635.02</v>
       </c>
       <c r="O67">
         <v>46</v>
@@ -5596,13 +5596,13 @@
         <v>51.1</v>
       </c>
       <c r="Q67">
-        <v>52.2</v>
+        <v>51.93</v>
       </c>
       <c r="R67">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S67">
-        <v>4932.37</v>
+        <v>4876.4</v>
       </c>
       <c r="T67">
         <v>60</v>
@@ -5611,16 +5611,16 @@
         <v>66.7</v>
       </c>
       <c r="V67">
-        <v>37.94</v>
+        <v>37.8</v>
       </c>
       <c r="W67">
-        <v>51.92</v>
+        <v>51.33</v>
       </c>
       <c r="X67">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Y67">
-        <v>6.23</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="68" spans="1:25">
@@ -5646,10 +5646,10 @@
         <v>235.08</v>
       </c>
       <c r="H68">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I68">
-        <v>17.11</v>
+        <v>0</v>
       </c>
       <c r="J68">
         <v>5</v>
@@ -5658,13 +5658,13 @@
         <v>13.9</v>
       </c>
       <c r="L68">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M68">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N68">
-        <v>93.98999999999999</v>
+        <v>76.88</v>
       </c>
       <c r="O68">
         <v>8</v>
@@ -5673,13 +5673,13 @@
         <v>22.2</v>
       </c>
       <c r="Q68">
-        <v>6.71</v>
+        <v>6.41</v>
       </c>
       <c r="R68">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S68">
-        <v>148.97</v>
+        <v>131.86</v>
       </c>
       <c r="T68">
         <v>13</v>
@@ -5688,16 +5688,16 @@
         <v>36.1</v>
       </c>
       <c r="V68">
-        <v>4.81</v>
+        <v>4.55</v>
       </c>
       <c r="W68">
-        <v>4.14</v>
+        <v>3.66</v>
       </c>
       <c r="X68">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y68">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:25">
@@ -5741,7 +5741,7 @@
         <v>240</v>
       </c>
       <c r="N69">
-        <v>3737.47</v>
+        <v>3777.46</v>
       </c>
       <c r="O69">
         <v>94</v>
@@ -5750,13 +5750,13 @@
         <v>73.40000000000001</v>
       </c>
       <c r="Q69">
-        <v>15.57</v>
+        <v>15.74</v>
       </c>
       <c r="R69">
         <v>252</v>
       </c>
       <c r="S69">
-        <v>3874.04</v>
+        <v>3914.03</v>
       </c>
       <c r="T69">
         <v>96</v>
@@ -5765,16 +5765,16 @@
         <v>75</v>
       </c>
       <c r="V69">
-        <v>15.37</v>
+        <v>15.53</v>
       </c>
       <c r="W69">
-        <v>29.35</v>
+        <v>29.65</v>
       </c>
       <c r="X69">
         <v>1.91</v>
       </c>
       <c r="Y69">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="70" spans="1:25">
@@ -5788,70 +5788,70 @@
         <v>42</v>
       </c>
       <c r="D70">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="E70">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F70">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="G70">
-        <v>1985.12</v>
+        <v>2037.36</v>
       </c>
       <c r="H70">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="I70">
-        <v>551.5</v>
+        <v>581.75</v>
       </c>
       <c r="J70">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="K70">
-        <v>41.4</v>
+        <v>43.6</v>
       </c>
       <c r="L70">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="M70">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="N70">
-        <v>551.5</v>
+        <v>581.75</v>
       </c>
       <c r="O70">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="P70">
-        <v>41.4</v>
+        <v>43.6</v>
       </c>
       <c r="Q70">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="R70">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="S70">
-        <v>551.5</v>
+        <v>581.75</v>
       </c>
       <c r="T70">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="U70">
-        <v>41.4</v>
+        <v>43.6</v>
       </c>
       <c r="V70">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="W70">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="X70">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="Y70">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="71" spans="1:25">
@@ -6058,7 +6058,7 @@
         <v>1.89</v>
       </c>
       <c r="R73">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="S73">
         <v>435.55</v>
@@ -6070,13 +6070,13 @@
         <v>83.90000000000001</v>
       </c>
       <c r="V73">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W73">
         <v>3.48</v>
       </c>
       <c r="X73">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Y73">
         <v>0.52</v>
@@ -6366,7 +6366,7 @@
         <v>0.22</v>
       </c>
       <c r="R77">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="S77">
         <v>89.72</v>
